--- a/data/DU_LICH_TRI_TON_PHAN_NHOM_2026.xlsx
+++ b/data/DU_LICH_TRI_TON_PHAN_NHOM_2026.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏛️ Chùa &amp; Di Tích'!$A$2:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'🍲 Ẩm Thực Đặc Sản'!$A$2:$P$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🏞️ Danh Thắng Núi Hồ'!$A$2:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'🏞️ Danh Thắng Núi Hồ'!$A$2:$P$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'📸 Điểm Check-in'!$A$2:$P$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'☕ Cà Phê &amp; Đêm'!$A$2:$P$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'🏡 Lưu Trú Homestay'!$A$2:$P$9</definedName>
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P153"/>
+  <dimension ref="A1:P154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
@@ -5317,7 +5317,7 @@
     <row r="77" ht="32" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>🏞️ III. DANH THẮNG THIÊN NHIÊN, NÚI &amp; HỒ NƯỚC — TỔNG SỐ: 38 ĐỊA ĐIỂM</t>
+          <t>🏞️ III. DANH THẮNG THIÊN NHIÊN, NÚI &amp; HỒ NƯỚC — TỔNG SỐ: 39 ĐỊA ĐIỂM</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>nha-trung-bay-van-hoa-khmer-tri-ton</t>
+          <t>nha-thieu-nhi</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Nhà Trưng Bày Văn Hóa Dân Tộc Khmer Tri Tôn</t>
+          <t>Nhà Thiếu Nhi Huyện Tri Tôn</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
@@ -6207,45 +6207,49 @@
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F91" s="4" t="n"/>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Trung tâm Văn hóa &amp; Vui chơi</t>
+        </is>
+      </c>
       <c r="G91" s="3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>10.4285, 104.998</t>
+          <t>10.4230431, 105.0014886</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>Trung tâm Văn hóa Thể thao, Thị trấn Tri Tôn, An Giang</t>
+          <t>Số 89 Đường Trần Hưng Đạo, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Miễn phí vé vào cổng</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>07:00 - 18:00</t>
+          <t>07:00 - 21:00</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>Không gian bảo tồn và trưng bày hàng trăm hiện vật quý giá về đời sống, tín ngưỡng, nông cụ, trang phục cưới và nhạc cụ cổ truyền của đồng bào Khmer Bảy Núi.</t>
+          <t>Trung tâm sinh hoạt văn hóa, vui chơi giải trí và rèn luyện năng khiếu rộng hơn 1,5 ha tại trung tâm thị trấn Tri Tôn. Điểm đến dạo chơi lý tưởng cho các gia đình có trẻ nhỏ và thanh thiếu niên vào buổi chiều tối.</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>Nơi đây lưu giữ trọn vẹn bộ sưu tập Dàn nhạc Ngũ Âm (Pinpeat), trống Chhay-dăm, các bộ trang phục sân khấu Dù Kê (Robam), mô hình thuyền đua Ngo, nông cụ bừa cày cổ truyền và tư liệu về các kỳ Lễ hội Đua bò Bảy Núi qua nhiều thập kỷ.</t>
+          <t>Khám Phá Nhà Thiếu Nhi Huyện Tri Tôn – Không Gian Văn Hóa &amp; Vui Chơi Năng Động Xứ Bảy Núi  1. Lịch Sử &amp; Quy Mô Công Trình: • Địa chỉ: Số 89, đường Trần Hưng Đạo, Khóm 1, Thị trấn Tri Tôn, An Giang. • Khánh thành ngày 20/9/2013, đây là công trình Nhà thiếu nhi cấp huyện đầu tiên được xây dựng tại tỉnh An Giang với tổng diện tích khuôn viên hơn 15.280 m². • Quy mô bao gồm khu hành chính, hệ thống phòng học năng khiếu (võ thuật Taekwondo, Karatedo, Vovinam, thể dục nhịp điệu, âm nhạc, hội họa), hội trường lớn, sân khấu biểu diễn và khu vui chơi ngoài trời rộng rãi.  2. Hoạt Động &amp; Trải Nghiệm Thực Địa: • Không gian vui chơi rộng rãi, thoáng mát rợp bóng cây xanh, là điểm hẹn quen thuộc của các gia đình địa phương và du khách đưa con em đến vui chơi, chạy nhảy thư giãn mỗi buổi chiều tà. • Nơi thường xuyên diễn ra các hội thi văn nghệ, giao lưu văn hóa thiếu nhi Khmer - Kinh, các giải thi đấu thể thao phong trào và chương trình Tết Trung Thu, Quốc tế Thiếu nhi rộn rã.</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr"/>
       <c r="P91" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.998</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4230431,105.0014886</t>
         </is>
       </c>
     </row>
@@ -6255,12 +6259,12 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>nui-dai</t>
+          <t>nha-trung-bay-van-hoa-khmer-tri-ton</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Núi Dài</t>
+          <t>Nhà Trưng Bày Văn Hóa Dân Tộc Khmer Tri Tôn</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr"/>
@@ -6269,22 +6273,18 @@
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="n"/>
       <c r="G92" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>10.4759134, 104.942797</t>
+          <t>10.4285, 104.998</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>Núi Dài, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Trung tâm Văn hóa Thể thao, Thị trấn Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J92" s="7" t="inlineStr"/>
@@ -6300,18 +6300,18 @@
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Núi Dài, điểm đến kỳ vĩ tại Bảy Núi An Giang</t>
+          <t>Không gian bảo tồn và trưng bày hàng trăm hiện vật quý giá về đời sống, tín ngưỡng, nông cụ, trang phục cưới và nhạc cụ cổ truyền của đồng bào Khmer Bảy Núi.</t>
         </is>
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Khám Phá Núi Dài (Ngọa Long Sơn) – Dải "Rồng Nằm" Hùng Vĩ Xứ Bảy Núi Trong quần thể Thất Sơn (Bảy Núi) của An Giang, nếu Núi Cấm (Thiên Cấm Sơn) được mệnh danh là ngọn núi cao nhất thì Núi Dài chính là ngọn núi có chiều dài đồ sộ nhất. Với dáng hình uốn lượn tựa như một con rồng khổng lồ đang nằm phục giữa đồng bằng, núi được đặt tên chữ là Ngọa Long Sơn.  1. Vị Trí &amp; • Đặc Điểm Địa LýVị trí hành ch  ính: Nằm chạy dọc theo tuyến Tỉnh lộ 955B, trải dài qua địa phận 3 xã là Châu Lăng, Lương Phi, Lê Trì và một phần thị trấn Ba Chúc thuộc huyện Tri Tôn, tỉnh An Giang. • Quy mô: Chiều dài lên tới khoảng 8.000 m (8 km) – dài nhất trong vùng Thất Sơn. Độ cao đỉnh núi đạt khoảng 580 m. • Lưu ý phân biệt: Trong hệ thống Thất Sơn có hai ngọn núi mang tên "Núi Dài": • Núi Dài Lớn (Ngọa Long Sơn): Ngọn núi dài 8km tại Tri Tôn. Núi Dài • Nhỏ (Ngũ Hồ Sơn / Núi Dài Năm Giếng): Ngọn núi cao 265m nằm bên thị xã Tịnh Biên.  2. Cảnh Quan Sinh Thái &amp; Đời Sống Sơn • Dân • Rừng tầm vông &amp; Vườn cây ăn trái: Men theo các triền dốc lên núi Dài là những cánh rừng tầm vông xanh ngắt bạt ngàn, đan xen cùng những vườn xoài cổ thụ, mít, chuối, bưởi, hồng quân và sầu riêng của bà con người Kinh và Khmer. Hệ thống suối &amp; • Điểm tập kết nông sản: Núi có nhiều dòng suối tự nhiên len lỏi qua các khe đá như Ô Sình, Ô Vàng (dưới chân có dòng suối Vàng, suối Bạc). Vào mùa mưa, núi rừng khoác lên màu xanh mướt mát mắt, suối chảy róc rách và người dân lên núi thu hoạch măng le, nấm rừng cùng hoa quả.  3. Di Tích Lịch Sử &amp; Điểm Đến Tâm Linh  Núi Dài không chỉ có thiên nhiên trù phú mà còn là vùng đất thiêng liêng gắn liền với lịch sử cách mạng hào hùng:Khu • Căn cứ Cách mạng Ô Tà Sóc: Tọa lạc bên sườn núi thuộc xã Lương Phi. Nơi đây là căn cứ địa kiên cố của Tỉnh ủy An Giang thời kháng chiến chống Mỹ, đã được xếp hạng là Di tích lịch sử cách mạng cấp quốc gia. Đồi Ma Thiên Lãnh &amp; Hang Quân Y, • Điện Trời Gầm: Những hang đá granite hiểm trở ghi dấu sự hy sinh anh dũng của các chiến sĩ và thanh niên xung phong tuyến đường 1C. • Hồ Ô Tà Sóc: Hồ nước ngọt phẳng lặng, trong xanh tựa lưng vào vách núi Dài, là điểm cắm trại và check-in dã ngoại rất được yêu thích. • Điện Tàu Cau &amp; Các am cốc tu tập: Nằm rải rác trên sườn núi, là chốn tu thiền thanh tịnh giữa thiên nhiên thâm u của miền biên viễn.  4. Hướng Dẫn • Trải Nghiệm &amp; Khám Phá • Phương tiện: Du khách có thể chạy xe máy men theo các cung đường bê tông dốc thoai thoải từ chân núi (hướng Ô Tà Sóc - Lương Phi hoặc hướng Ba Chúc), hoặc thuê xe ôm bản địa chở lên các điện thờ lưng chừng núi. • Trekking khám phá: Cung đường mòn xuyên qua rừng tầm vông và vườn xoài rất thích hợp cho những ai đam mê trekking nhẹ nhàng, vừa đi bộ vừa hít thở không khí thanh sạch. • Thưởng thức ẩm thực: Dưới chân núi có nhiều hàng quán phục vụ gỏi sầu đâu khô cá lóc/cá sặc, bánh xèo rau rừng, gà đốt đất và nước thốt nốt tươi mát lạnh.  5. • Lưu Ý Khi Tham Quan • An toàn: Đường dốc núi quanh co, nếu tự lái xe máy cần kiểm tra phanh kỹ lưỡng và đi số thấp (số 1, số 2). • Tôn nghiêm &amp; Môi trường: Giữ trật tự khi ghé thăm các khu vực di tích lịch sử, am điện thờ cúng và tuyệt đối không vứt rác, không tự ý đốt lửa gây nguy cơ cháy rừng trên sườn núi.</t>
+          <t>Nơi đây lưu giữ trọn vẹn bộ sưu tập Dàn nhạc Ngũ Âm (Pinpeat), trống Chhay-dăm, các bộ trang phục sân khấu Dù Kê (Robam), mô hình thuyền đua Ngo, nông cụ bừa cày cổ truyền và tư liệu về các kỳ Lễ hội Đua bò Bảy Núi qua nhiều thập kỷ.</t>
         </is>
       </c>
       <c r="O92" s="7" t="inlineStr"/>
       <c r="P92" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4759134,104.942797</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.998</t>
         </is>
       </c>
     </row>
@@ -6321,12 +6321,12 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>nui-nuoc</t>
+          <t>nui-dai</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Núi Nước</t>
+          <t>Núi Dài</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>10.492604, 104.8905659</t>
+          <t>10.4759134, 104.942797</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>Núi Nước, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Núi Dài, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
@@ -6366,18 +6366,18 @@
       </c>
       <c r="M93" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Nước - điểm tham quan độc đáo tại Bảy Núi</t>
+          <t>Khám phá Núi Dài, điểm đến kỳ vĩ tại Bảy Núi An Giang</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>Núi • Nước: Điểm Hẹn Độc Đáo tại Bảy Núi  Trong dãy Thất Sơn hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa và những dải núi đá granite trùng điệp, Núi Nước là một điểm tham quan đặc biệt không thể bỏ qua. Vùng đất này mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương.  Khi đến đây, du khách có thể thưởng thức đặc sản nước thốt nốt tươi và bánh bò thốt nốt, được biết đến qua các đánh giá thực tế của du khách đã đến đây. Những trải nghiệm này không chỉ giúp bạn hiểu hơn về văn hóa phong phú của đồng bào Khmer mà còn là cơ hội để bạn khám phá bản sắc của vùng đất này.  Tìm Kiếm Cảnh Sắc Yên Bình và Phong Hóa Văn Hóa  Núi Nước là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn. Với sự kết hợp hài hòa giữa thiên nhiên và văn hóa, Núi Nước mang đến cho du khách những trải nghiệm đáng nhớ và một cảm giác thư giãn tuyệt vời.</t>
+          <t>Khám Phá Núi Dài (Ngọa Long Sơn) – Dải "Rồng Nằm" Hùng Vĩ Xứ Bảy Núi Trong quần thể Thất Sơn (Bảy Núi) của An Giang, nếu Núi Cấm (Thiên Cấm Sơn) được mệnh danh là ngọn núi cao nhất thì Núi Dài chính là ngọn núi có chiều dài đồ sộ nhất. Với dáng hình uốn lượn tựa như một con rồng khổng lồ đang nằm phục giữa đồng bằng, núi được đặt tên chữ là Ngọa Long Sơn.  1. Vị Trí &amp; • Đặc Điểm Địa LýVị trí hành ch  ính: Nằm chạy dọc theo tuyến Tỉnh lộ 955B, trải dài qua địa phận 3 xã là Châu Lăng, Lương Phi, Lê Trì và một phần thị trấn Ba Chúc thuộc huyện Tri Tôn, tỉnh An Giang. • Quy mô: Chiều dài lên tới khoảng 8.000 m (8 km) – dài nhất trong vùng Thất Sơn. Độ cao đỉnh núi đạt khoảng 580 m. • Lưu ý phân biệt: Trong hệ thống Thất Sơn có hai ngọn núi mang tên "Núi Dài": • Núi Dài Lớn (Ngọa Long Sơn): Ngọn núi dài 8km tại Tri Tôn. Núi Dài • Nhỏ (Ngũ Hồ Sơn / Núi Dài Năm Giếng): Ngọn núi cao 265m nằm bên thị xã Tịnh Biên.  2. Cảnh Quan Sinh Thái &amp; Đời Sống Sơn • Dân • Rừng tầm vông &amp; Vườn cây ăn trái: Men theo các triền dốc lên núi Dài là những cánh rừng tầm vông xanh ngắt bạt ngàn, đan xen cùng những vườn xoài cổ thụ, mít, chuối, bưởi, hồng quân và sầu riêng của bà con người Kinh và Khmer. Hệ thống suối &amp; • Điểm tập kết nông sản: Núi có nhiều dòng suối tự nhiên len lỏi qua các khe đá như Ô Sình, Ô Vàng (dưới chân có dòng suối Vàng, suối Bạc). Vào mùa mưa, núi rừng khoác lên màu xanh mướt mát mắt, suối chảy róc rách và người dân lên núi thu hoạch măng le, nấm rừng cùng hoa quả.  3. Di Tích Lịch Sử &amp; Điểm Đến Tâm Linh  Núi Dài không chỉ có thiên nhiên trù phú mà còn là vùng đất thiêng liêng gắn liền với lịch sử cách mạng hào hùng:Khu • Căn cứ Cách mạng Ô Tà Sóc: Tọa lạc bên sườn núi thuộc xã Lương Phi. Nơi đây là căn cứ địa kiên cố của Tỉnh ủy An Giang thời kháng chiến chống Mỹ, đã được xếp hạng là Di tích lịch sử cách mạng cấp quốc gia. Đồi Ma Thiên Lãnh &amp; Hang Quân Y, • Điện Trời Gầm: Những hang đá granite hiểm trở ghi dấu sự hy sinh anh dũng của các chiến sĩ và thanh niên xung phong tuyến đường 1C. • Hồ Ô Tà Sóc: Hồ nước ngọt phẳng lặng, trong xanh tựa lưng vào vách núi Dài, là điểm cắm trại và check-in dã ngoại rất được yêu thích. • Điện Tàu Cau &amp; Các am cốc tu tập: Nằm rải rác trên sườn núi, là chốn tu thiền thanh tịnh giữa thiên nhiên thâm u của miền biên viễn.  4. Hướng Dẫn • Trải Nghiệm &amp; Khám Phá • Phương tiện: Du khách có thể chạy xe máy men theo các cung đường bê tông dốc thoai thoải từ chân núi (hướng Ô Tà Sóc - Lương Phi hoặc hướng Ba Chúc), hoặc thuê xe ôm bản địa chở lên các điện thờ lưng chừng núi. • Trekking khám phá: Cung đường mòn xuyên qua rừng tầm vông và vườn xoài rất thích hợp cho những ai đam mê trekking nhẹ nhàng, vừa đi bộ vừa hít thở không khí thanh sạch. • Thưởng thức ẩm thực: Dưới chân núi có nhiều hàng quán phục vụ gỏi sầu đâu khô cá lóc/cá sặc, bánh xèo rau rừng, gà đốt đất và nước thốt nốt tươi mát lạnh.  5. • Lưu Ý Khi Tham Quan • An toàn: Đường dốc núi quanh co, nếu tự lái xe máy cần kiểm tra phanh kỹ lưỡng và đi số thấp (số 1, số 2). • Tôn nghiêm &amp; Môi trường: Giữ trật tự khi ghé thăm các khu vực di tích lịch sử, am điện thờ cúng và tuyệt đối không vứt rác, không tự ý đốt lửa gây nguy cơ cháy rừng trên sườn núi.</t>
         </is>
       </c>
       <c r="O93" s="4" t="inlineStr"/>
       <c r="P93" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.492604,104.8905659</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4759134,104.942797</t>
         </is>
       </c>
     </row>
@@ -6387,12 +6387,12 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>c7d6fabf-rồng-vàng-resort-tri</t>
+          <t>nui-nuoc</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Rồng Vàng Resort Tri Tôn</t>
+          <t>Núi Nước</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr"/>
@@ -6403,20 +6403,20 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Resort</t>
+          <t>place</t>
         </is>
       </c>
       <c r="G94" s="6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>10.41, 105.01</t>
+          <t>10.492604, 104.8905659</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Núi Nước, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr"/>
@@ -6432,18 +6432,18 @@
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>Rồng Vàng Resort Tri Tôn - Nơi Hấp Dẫn Của Bảy Núi</t>
+          <t>Khám phá Núi Nước - điểm tham quan độc đáo tại Bảy Núi</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Rồng Vàng Resort Tri Tôn - Một điểm du lịch lý tưởng nằm ở trung tâm thị trấn Tri Tôn, tỉnh An Giang. Resort này tọa lạc ở 19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang. Đây là một điểm đến lý tưởng để thư giãn và khám phá vẻ đẹp của vùng đất Bảy Núi.  Rồng Vàng Resort Tri Tôn mở cửa 24/7, với mức giá khoảng 500k - 900k. Đây là một lựa chọn tuyệt vời cho những ai muốn khám phá vẻ đẹp của Bảy Núi mà không cần lo lắng về chi phí.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng một số du khách đã chia sẻ về những trải nghiệm của mình. "Rồng Vàng Resort Tri Tôn là một nơi tuyệt vời để nghỉ ngơi và thư giãn. Tôi đã có một thời gian tuyệt vời tại đây và tôi chắc chắn sẽ trở lại."  3. Lời khuyên • Hãy đặt phòng trước để đảm bảo có chỗ ở. • Hãy khám phá vẻ đẹp của Bảy Núi bằng nhiều cách khác nhau, chẳng hạn như đi bộ, đạp xe, hoặc tham gia tour du lịch. • Hãy thử các món ăn địa phương và thưởng thức không khí mát mẻ của vùng đất Bảy Núi.</t>
+          <t>Núi • Nước: Điểm Hẹn Độc Đáo tại Bảy Núi  Trong dãy Thất Sơn hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa và những dải núi đá granite trùng điệp, Núi Nước là một điểm tham quan đặc biệt không thể bỏ qua. Vùng đất này mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương.  Khi đến đây, du khách có thể thưởng thức đặc sản nước thốt nốt tươi và bánh bò thốt nốt, được biết đến qua các đánh giá thực tế của du khách đã đến đây. Những trải nghiệm này không chỉ giúp bạn hiểu hơn về văn hóa phong phú của đồng bào Khmer mà còn là cơ hội để bạn khám phá bản sắc của vùng đất này.  Tìm Kiếm Cảnh Sắc Yên Bình và Phong Hóa Văn Hóa  Núi Nước là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn. Với sự kết hợp hài hòa giữa thiên nhiên và văn hóa, Núi Nước mang đến cho du khách những trải nghiệm đáng nhớ và một cảm giác thư giãn tuyệt vời.</t>
         </is>
       </c>
       <c r="O94" s="7" t="inlineStr"/>
       <c r="P94" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.41,105.01</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.492604,104.8905659</t>
         </is>
       </c>
     </row>
@@ -6453,12 +6453,12 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>tho-mo-muc-cave-hang-tho-mo-muc</t>
+          <t>c7d6fabf-rồng-vàng-resort-tri</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Tho Mo Muc Cave (Hang Tho Mo Muc)</t>
+          <t>Rồng Vàng Resort Tri Tôn</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -6469,20 +6469,20 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>attraction</t>
+          <t>Resort</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>10.374438, 104.9655284</t>
+          <t>10.41, 105.01</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>Tho Mo Muc Cave (Hang Tho Mo Muc), Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr"/>
@@ -6498,18 +6498,18 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>Hang Thọ Mộc: Lối vào thiên đường tĩnh lặng giữa đại ngàn Thất Sơn</t>
+          <t>Rồng Vàng Resort Tri Tôn - Nơi Hấp Dẫn Của Bảy Núi</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>Tìm Hiểu Hang Tho-Mo-Múc – Dấu Ấn Lịch Sử Trong Lòng Đồi Tức Dụp  Hang Tho-Mo-Múc (hay Tho Mo Múc) là một hang đá tự nhiên mang giá trị lịch sử đặc biệt, nằm trong hệ thống hang động chằng chịt của ngọn đồi Tức Dụp (ngọn đồi 2 triệu đô la huyền thoại).  1. • Vị Trí &amp; Nguồn Gốc Địa Danh • Vị trí: Tọa lạc tại xã Ô Lâm, huyện Tri Tôn, tỉnh An Giang (thuộc cụm di tích Đồi Tức Dụp, nằm ngay triền phía Tây ngọn núi Cô Tô). • Nguồn gốc tên gọi: Tên gọi "Tho-Mo-Múc" (hay Thmâ Mốk / Thmâ Múk) bắt nguồn từ tiếng Khmer bản địa dùng để chỉ các khối đá, hốc đá đặc thù trên triền đồi Tức Dụp.  2. Dấu Ấn Lịch Sử Trong Kháng ChiếnTrong suốt những năm kháng chiến chống Mỹ (đặc biệt là trận đánh 128 ngày đêm huyền thoại bảo vệ đồi Tức • Dụp cuối năm 1968 – đầu năm 1969): Nơi trú • ẩn &amp; Trạm dã chiến: Cùng với các hang C.16, hang Quân y, hang Tỉnh ủy, hang Phụ nữ... Hang Tho-Mo-Múc là một trong những hốc đá kiên cố được quân dân cách mạng, lực lượng thanh niên xung phong (tuyến đường 1C huyền thoại) và các nữ chiến sĩ sử dụng làm nơi trú ẩn, hội họp dã chiến và che giấu thương binh trước các đợt oanh kích ác liệt của pháo binh và máy bay địch. • Cấu trúc hiểm trở: Hang được tạo thành bởi hàng trăm tảng đá granite khổng lồ xếp chồng lên nhau tự nhiên, bên trong có nhiều ngóc ngách, khe gió mát lạnh và luồng thông hiểm trở, giúp bộ đội bám trụ kiên cường dưới lòng đất.  3. Trải Nghiệm Khám Phá Hiện NayKhông gian hoang sơ, huyền bí: Hang vẫn giữ nguyên nét kiến tạo gập ghềnh tự nhiên của đá núi Thất Sơn. Bước vào bên trong, không khí lập tức hạ nhiệt mát lạnh, bóng tối mờ ảo tạo cảm giác hồi hộp, kỳ bí cho những ai thích khám phá mạo hiểm. • Hành trình về nguồn: Nằm trong quần thể di tích lịch sử Đồi Tức Dụp, du khách có thể kết hợp tham quan khu di tích, bảo tàng trưng bày chứng tích chiến tranh và trải nghiệm luồn lách qua các hốc đá tự nhiên.  4. Gợi Ý Lịch Trình Kết Hợp Quanh Khu Vực Xã Ô LâmKhu di tích Đồi Tức Dụp (Hang Tho-Mo-Múc) \longrightarrow Hồ Ô Thum (Ăn gà đốt lá chúc) \longrightarrow Cây thốt nốt trái tim / Cầu khỉ An Tức.  5. Lưu • Ý Dành Cho Người Khám PháTrang bị: Cần chuẩn bị đèn pin cầm tay có độ sáng tốt và đi giày thể thao có độ bám cao để tránh trượt ngã trên các bề mặt đá ẩm ướt. • An toàn: Lối vào hang hẹp, có nhiều đoạn phải khom lưng hoặc trườn qua khe đá; không nên tự ý đi sâu một mình vào những ngách tối chưa có biển chỉ dẫn.</t>
+          <t>1. Tổng quan Rồng Vàng Resort Tri Tôn - Một điểm du lịch lý tưởng nằm ở trung tâm thị trấn Tri Tôn, tỉnh An Giang. Resort này tọa lạc ở 19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang. Đây là một điểm đến lý tưởng để thư giãn và khám phá vẻ đẹp của vùng đất Bảy Núi.  Rồng Vàng Resort Tri Tôn mở cửa 24/7, với mức giá khoảng 500k - 900k. Đây là một lựa chọn tuyệt vời cho những ai muốn khám phá vẻ đẹp của Bảy Núi mà không cần lo lắng về chi phí.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng một số du khách đã chia sẻ về những trải nghiệm của mình. "Rồng Vàng Resort Tri Tôn là một nơi tuyệt vời để nghỉ ngơi và thư giãn. Tôi đã có một thời gian tuyệt vời tại đây và tôi chắc chắn sẽ trở lại."  3. Lời khuyên • Hãy đặt phòng trước để đảm bảo có chỗ ở. • Hãy khám phá vẻ đẹp của Bảy Núi bằng nhiều cách khác nhau, chẳng hạn như đi bộ, đạp xe, hoặc tham gia tour du lịch. • Hãy thử các món ăn địa phương và thưởng thức không khí mát mẻ của vùng đất Bảy Núi.</t>
         </is>
       </c>
       <c r="O95" s="4" t="inlineStr"/>
       <c r="P95" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.374438,104.9655284</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.41,105.01</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>dong-nhin-len-chu-tri-ton</t>
+          <t>tho-mo-muc-cave-hang-tho-mo-muc</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN</t>
+          <t>Tho Mo Muc Cave (Hang Tho Mo Muc)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>artwork</t>
+          <t>attraction</t>
         </is>
       </c>
       <c r="G96" s="6" t="n">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>10.4016818, 105.0014948</t>
+          <t>10.374438, 104.9655284</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Tho Mo Muc Cave (Hang Tho Mo Muc), Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr"/>
@@ -6564,18 +6564,18 @@
       </c>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>Khám phá vẻ đẹp yên bình của vùng đất Tri Tôn với Điểm check-in chữ Tri Tôn.</t>
+          <t>Hang Thọ Mộc: Lối vào thiên đường tĩnh lặng giữa đại ngàn Thất Sơn</t>
         </is>
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Đồng Nhin Len Chữ Tri Tôn là một điểm du lịch độc đáo ở huyện Tri Tôn, tỉnh An Giang. Địa điểm này nằm trong hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo của vùng đất này. Vùng đất Tri Tôn nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  2. Đánh giá từ du khách • Đường đi đến điểm check-in dễ dàng, chỉ cần đi bộ khoảng 1200-1500 bước hoặc thuê xe ôm để xuống. • Điểm check-in chữ Tri Tôn là một địa điểm sống ảo nổi bật với view núi non và cánh đồng rộng lớn. • Khung cảnh thoáng đãng và bảng chữ lớn đặc trưng thu hút nhiều bạn trẻ đến chụp ảnh. • Phong cảnh hùng vĩ, không khí mát mẻ trong lành. • Là một điểm du lịch lý thú và đáng trải nghiệm.  3. Lời khuyên • Khi đến đây, bạn có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer. • Hãy đi bộ lên khoảng 1200-1500 bước để có thể ngắm nhìn vẻ đẹp yên bình của cánh đồng rộng lớn và núi non hùng vĩ. • Để có thể ghi lại được những bức ảnh sống ảo đẹp nhất, hãy thuê xe ôm để xuống và chụp ảnh ở những góc cạnh đặc trưng. • Hãy tận hưởng phong cảnh hùng vĩ, không khí mát mẻ trong lành và lòng hiếu khách của người dân địa phương.</t>
+          <t>Tìm Hiểu Hang Tho-Mo-Múc – Dấu Ấn Lịch Sử Trong Lòng Đồi Tức Dụp  Hang Tho-Mo-Múc (hay Tho Mo Múc) là một hang đá tự nhiên mang giá trị lịch sử đặc biệt, nằm trong hệ thống hang động chằng chịt của ngọn đồi Tức Dụp (ngọn đồi 2 triệu đô la huyền thoại).  1. • Vị Trí &amp; Nguồn Gốc Địa Danh • Vị trí: Tọa lạc tại xã Ô Lâm, huyện Tri Tôn, tỉnh An Giang (thuộc cụm di tích Đồi Tức Dụp, nằm ngay triền phía Tây ngọn núi Cô Tô). • Nguồn gốc tên gọi: Tên gọi "Tho-Mo-Múc" (hay Thmâ Mốk / Thmâ Múk) bắt nguồn từ tiếng Khmer bản địa dùng để chỉ các khối đá, hốc đá đặc thù trên triền đồi Tức Dụp.  2. Dấu Ấn Lịch Sử Trong Kháng ChiếnTrong suốt những năm kháng chiến chống Mỹ (đặc biệt là trận đánh 128 ngày đêm huyền thoại bảo vệ đồi Tức • Dụp cuối năm 1968 – đầu năm 1969): Nơi trú • ẩn &amp; Trạm dã chiến: Cùng với các hang C.16, hang Quân y, hang Tỉnh ủy, hang Phụ nữ... Hang Tho-Mo-Múc là một trong những hốc đá kiên cố được quân dân cách mạng, lực lượng thanh niên xung phong (tuyến đường 1C huyền thoại) và các nữ chiến sĩ sử dụng làm nơi trú ẩn, hội họp dã chiến và che giấu thương binh trước các đợt oanh kích ác liệt của pháo binh và máy bay địch. • Cấu trúc hiểm trở: Hang được tạo thành bởi hàng trăm tảng đá granite khổng lồ xếp chồng lên nhau tự nhiên, bên trong có nhiều ngóc ngách, khe gió mát lạnh và luồng thông hiểm trở, giúp bộ đội bám trụ kiên cường dưới lòng đất.  3. Trải Nghiệm Khám Phá Hiện NayKhông gian hoang sơ, huyền bí: Hang vẫn giữ nguyên nét kiến tạo gập ghềnh tự nhiên của đá núi Thất Sơn. Bước vào bên trong, không khí lập tức hạ nhiệt mát lạnh, bóng tối mờ ảo tạo cảm giác hồi hộp, kỳ bí cho những ai thích khám phá mạo hiểm. • Hành trình về nguồn: Nằm trong quần thể di tích lịch sử Đồi Tức Dụp, du khách có thể kết hợp tham quan khu di tích, bảo tàng trưng bày chứng tích chiến tranh và trải nghiệm luồn lách qua các hốc đá tự nhiên.  4. Gợi Ý Lịch Trình Kết Hợp Quanh Khu Vực Xã Ô LâmKhu di tích Đồi Tức Dụp (Hang Tho-Mo-Múc) \longrightarrow Hồ Ô Thum (Ăn gà đốt lá chúc) \longrightarrow Cây thốt nốt trái tim / Cầu khỉ An Tức.  5. Lưu • Ý Dành Cho Người Khám PháTrang bị: Cần chuẩn bị đèn pin cầm tay có độ sáng tốt và đi giày thể thao có độ bám cao để tránh trượt ngã trên các bề mặt đá ẩm ướt. • An toàn: Lối vào hang hẹp, có nhiều đoạn phải khom lưng hoặc trườn qua khe đá; không nên tự ý đi sâu một mình vào những ngách tối chưa có biển chỉ dẫn.</t>
         </is>
       </c>
       <c r="O96" s="7" t="inlineStr"/>
       <c r="P96" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4016818,105.0014948</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.374438,104.9655284</t>
         </is>
       </c>
     </row>
@@ -6585,36 +6585,36 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>3383c54e-con-đường-vòm-còng-c</t>
+          <t>dong-nhin-len-chu-tri-ton</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Vòm Còng Châu Lăng</t>
+          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Xã Châu Lăng</t>
+          <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Con đường nhiếp ảnh</t>
+          <t>artwork</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>10.4355, 105.0015</t>
+          <t>10.4016818, 105.0014948</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Tuyến đường Hàng Còng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr"/>
@@ -6630,18 +6630,18 @@
       </c>
       <c r="M97" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Vòm Còng Châu Lăng: Một dấu ấn văn hóa độc đáo tại Bảy Núi</t>
+          <t>Khám phá vẻ đẹp yên bình của vùng đất Tri Tôn với Điểm check-in chữ Tri Tôn.</t>
         </is>
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>Khám Phá Con Đường Vòm Còng Châu Lăng (Chùa Hàng Còng – Krăng Krốch)1. • Vị Trí &amp; Tên GọiĐịa chỉ: Ấp An Hòa, xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Tên gọi địa phương: Chùa có tên chữ là Prochum Meáp Chhưm Kiriram (nghĩa là "Ngôi chùa ở giữa núi").Người Khmer gọi là Krăng Krốch (Krăng là "gò cao", Krốch là "bưởi rừng").Do nét đặc trưng độc nhất vô nhị của hàng cây cổ thụ dẫn vào chùa, người dân bản địa lẫn du khách quen gọi bằng cái tên thân thuộc: Chùa Hàng Còng hay Con đường Hàng Còng Châu Lăng.  2. Điểm Độc Đáo Của "Con Đường Vòm Còng"Mái vòm tự nhiên hàng trăm năm tuổi: Con đường dài hàng trăm mét dẫn từ cổng vào sâu trong sân chùa được che phủ bởi khoảng 60 – 70 cây còng cổ thụ (còn gọi là cây me tây/muồng tím). Các nhánh cây vươn dài, đan cài vào nhau tạo thành một "mái vòm xanh mát" khổng lồ, tách biệt hoàn toàn khỏi cái nắng gắt của vùng đồng bằng. • Thân cây cổ thụ độc lạ: Những gốc còng to lớn đến 2 – 3 người ôm mới xuể, thân cây xù xì, nổi nhiều u sần và rễ cây cuồn cuộn trồi lên mặt đất tạo thành những hình khối điêu khắc tự nhiên rất ấn tượng. • Vẻ đẹp biến chuyển theo mùa: Mùa xuân – hè: Tán lá xanh um tùm, ánh nắng xuyên qua kẽ lá rọi xuống mặt đường tạo nên khung cảnh thanh bình, thơ mộng. • Mùa thay lá: Hàng còng trút lá để lại những cành nhánh khẳng khiu, trầm mặc, mang lại cảm giác ma mị, huyền bí rất đậm chất điện ảnh.  3. Hướng Dẫn Di Chuyển &amp; • Gợi Ý Lịch Trình Kết HợpHướng đi: Từ trung tâm thị trấn Tri Tôn hoặc từ TP. Châu Đốc đi theo hướng về ngã ba Ba Chúc/Châu Lăng. Lối vào chùa nằm ven tuyến đường giao thông ở ấp An Hòa (cổng chùa hơi khuất sau nhà dân, bạn có thể hỏi người dân quanh đó đường vào "Chùa Hàng Còng").Cung đường check-in liên hoàn tại • Châu Lăng: Chùa Hàng Còng (Krăng Krốch) \longrightarrow Cổng trời Tri Tôn (Chùa Koh Kas - cách chừng 2km) \longrightarrow Tuyến tránh Tri Tôn săn hoàng hôn.  4. Lưu Ý Dành • Cho Du KháchKhông gian tôn nghiêm: Đây là lối đi vào chốn tu tập Phật giáo Nam tông Khmer. Du khách đến chụp ảnh nên giữ trật tự, đi đứng nhẹ nhàng, không xả rác và không bẻ cành/khắc tên lên thân cây cổ thụ. • Thời điểm chụp ảnh đẹp nhất: Sáng sớm (khoảng 7h00 – 9h00) khi ánh nắng xiên rọi qua vòm lá tạo hiệu ứng luồng sáng (ray sáng), hoặc buổi chiều dịu mát lúc 15h30 – 17h00.</t>
+          <t>1. Tổng quan Đồng Nhin Len Chữ Tri Tôn là một điểm du lịch độc đáo ở huyện Tri Tôn, tỉnh An Giang. Địa điểm này nằm trong hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo của vùng đất này. Vùng đất Tri Tôn nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  2. Đánh giá từ du khách • Đường đi đến điểm check-in dễ dàng, chỉ cần đi bộ khoảng 1200-1500 bước hoặc thuê xe ôm để xuống. • Điểm check-in chữ Tri Tôn là một địa điểm sống ảo nổi bật với view núi non và cánh đồng rộng lớn. • Khung cảnh thoáng đãng và bảng chữ lớn đặc trưng thu hút nhiều bạn trẻ đến chụp ảnh. • Phong cảnh hùng vĩ, không khí mát mẻ trong lành. • Là một điểm du lịch lý thú và đáng trải nghiệm.  3. Lời khuyên • Khi đến đây, bạn có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer. • Hãy đi bộ lên khoảng 1200-1500 bước để có thể ngắm nhìn vẻ đẹp yên bình của cánh đồng rộng lớn và núi non hùng vĩ. • Để có thể ghi lại được những bức ảnh sống ảo đẹp nhất, hãy thuê xe ôm để xuống và chụp ảnh ở những góc cạnh đặc trưng. • Hãy tận hưởng phong cảnh hùng vĩ, không khí mát mẻ trong lành và lòng hiếu khách của người dân địa phương.</t>
         </is>
       </c>
       <c r="O97" s="4" t="inlineStr"/>
       <c r="P97" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4355,105.0015</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4016818,105.0014948</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>d3e73741-cánh-đồng-thốt-nốt-c</t>
+          <t>3383c54e-con-đường-vòm-còng-c</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Cánh Đồng Thốt Nốt Châu Lăng</t>
+          <t>Con Đường Vòm Còng Châu Lăng</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr"/>
@@ -6667,20 +6667,20 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng</t>
+          <t>Con đường nhiếp ảnh</t>
         </is>
       </c>
       <c r="G98" s="6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>10.437, 105.003</t>
+          <t>10.4355, 105.0015</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Tuyến đường Hàng Còng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J98" s="7" t="inlineStr"/>
@@ -6696,18 +6696,18 @@
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>Danh từ cánh Bộ phận trong thân thể chim và một số côn trùng, dùng để bay. Chim vỗ cánh. Thẳng cánh cò bay. Bộ phận hình như cánh …</t>
+          <t>Khám phá Con Đường Vòm Còng Châu Lăng: Một dấu ấn văn hóa độc đáo tại Bảy Núi</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Cánh Đồng Thốt Nốt Châu Lăng - Một Thiên Nhiên Huyền Bí Tại Tri Tôn  1. Tổng quan Cánh Đồng Thốt Nốt Châu Lăng tọa lạc tại Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang. Nơi đây là một thiên nhiên huyền bí, mang dấu ấn đặc trưng của vùng đất An Giang. Với mô hình cánh đồng thốt nốt độc đáo, Cánh Đồng Thốt Nốt Châu Lăng trở thành một điểm đến thú vị cho những ai yêu thích thiên nhiên và muốn khám phá vẻ đẹp nguyên sơ của Việt Nam.  2. Đánh giá từ du khách Chưa có đánh giá cụ thể từ du khách, nhưng với vẻ đẹp nguyên sơ và độc đáo, Cánh Đồng Thốt Nốt Châu Lăng chắc chắn sẽ mang lại những trải nghiệm thú vị và đáng nhớ cho du khách. Du khách sẽ được tận hưởng không gian mở, cảm nhận được sự yên tĩnh và hòa mình với thiên nhiên.  3. Lời khuyên Trước khi đến Cánh Đồng Thốt Nốt Châu Lăng, bạn nên tìm hiểu thêm về địa điểm này để có những chuẩn bị cần thiết. Ngoài ra, nên mang theo đủ nước, thức ăn và trang thiết bị cần thiết để có một chuyến đi thoải mái và an toàn.</t>
+          <t>Khám Phá Con Đường Vòm Còng Châu Lăng (Chùa Hàng Còng – Krăng Krốch)1. • Vị Trí &amp; Tên GọiĐịa chỉ: Ấp An Hòa, xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Tên gọi địa phương: Chùa có tên chữ là Prochum Meáp Chhưm Kiriram (nghĩa là "Ngôi chùa ở giữa núi").Người Khmer gọi là Krăng Krốch (Krăng là "gò cao", Krốch là "bưởi rừng").Do nét đặc trưng độc nhất vô nhị của hàng cây cổ thụ dẫn vào chùa, người dân bản địa lẫn du khách quen gọi bằng cái tên thân thuộc: Chùa Hàng Còng hay Con đường Hàng Còng Châu Lăng.  2. Điểm Độc Đáo Của "Con Đường Vòm Còng"Mái vòm tự nhiên hàng trăm năm tuổi: Con đường dài hàng trăm mét dẫn từ cổng vào sâu trong sân chùa được che phủ bởi khoảng 60 – 70 cây còng cổ thụ (còn gọi là cây me tây/muồng tím). Các nhánh cây vươn dài, đan cài vào nhau tạo thành một "mái vòm xanh mát" khổng lồ, tách biệt hoàn toàn khỏi cái nắng gắt của vùng đồng bằng. • Thân cây cổ thụ độc lạ: Những gốc còng to lớn đến 2 – 3 người ôm mới xuể, thân cây xù xì, nổi nhiều u sần và rễ cây cuồn cuộn trồi lên mặt đất tạo thành những hình khối điêu khắc tự nhiên rất ấn tượng. • Vẻ đẹp biến chuyển theo mùa: Mùa xuân – hè: Tán lá xanh um tùm, ánh nắng xuyên qua kẽ lá rọi xuống mặt đường tạo nên khung cảnh thanh bình, thơ mộng. • Mùa thay lá: Hàng còng trút lá để lại những cành nhánh khẳng khiu, trầm mặc, mang lại cảm giác ma mị, huyền bí rất đậm chất điện ảnh.  3. Hướng Dẫn Di Chuyển &amp; • Gợi Ý Lịch Trình Kết HợpHướng đi: Từ trung tâm thị trấn Tri Tôn hoặc từ TP. Châu Đốc đi theo hướng về ngã ba Ba Chúc/Châu Lăng. Lối vào chùa nằm ven tuyến đường giao thông ở ấp An Hòa (cổng chùa hơi khuất sau nhà dân, bạn có thể hỏi người dân quanh đó đường vào "Chùa Hàng Còng").Cung đường check-in liên hoàn tại • Châu Lăng: Chùa Hàng Còng (Krăng Krốch) \longrightarrow Cổng trời Tri Tôn (Chùa Koh Kas - cách chừng 2km) \longrightarrow Tuyến tránh Tri Tôn săn hoàng hôn.  4. Lưu Ý Dành • Cho Du KháchKhông gian tôn nghiêm: Đây là lối đi vào chốn tu tập Phật giáo Nam tông Khmer. Du khách đến chụp ảnh nên giữ trật tự, đi đứng nhẹ nhàng, không xả rác và không bẻ cành/khắc tên lên thân cây cổ thụ. • Thời điểm chụp ảnh đẹp nhất: Sáng sớm (khoảng 7h00 – 9h00) khi ánh nắng xiên rọi qua vòm lá tạo hiệu ứng luồng sáng (ray sáng), hoặc buổi chiều dịu mát lúc 15h30 – 17h00.</t>
         </is>
       </c>
       <c r="O98" s="7" t="inlineStr"/>
       <c r="P98" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.437,105.003</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4355,105.0015</t>
         </is>
       </c>
     </row>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>a810d441-cây-thốt-nốt-cô-độc-</t>
+          <t>d3e73741-cánh-đồng-thốt-nốt-c</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Cây Thốt Nốt Cô Độc Châu Lăng</t>
+          <t>Cánh Đồng Thốt Nốt Châu Lăng</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Điểm check-in độc đáo</t>
+          <t>Cánh đồng</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>10.439, 105.0035</t>
+          <t>10.437, 105.003</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>Cây thốt nốt cô độc, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr"/>
@@ -6762,18 +6762,18 @@
       </c>
       <c r="M99" s="4" t="inlineStr">
         <is>
-          <t>Thông Tin Thực Tế Về "Cây Thốt Nốt Cô Độc" (Châu Lăng)</t>
+          <t>Danh từ cánh Bộ phận trong thân thể chim và một số côn trùng, dùng để bay. Chim vỗ cánh. Thẳng cánh cò bay. Bộ phận hình như cánh …</t>
         </is>
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>Tương tự như nhiều góc check-in tự nhiên tại vùng Bảy Núi, "Cây thốt nốt cô độc" không có ban quản lý, không bán vé và không có biển chỉ dẫn chính thức.  Tên gọi từ cộng • đồng nhiếp ảnh và phượt thủ: Tên gọi này do các nhiếp ảnh gia và bạn trẻ đam mê du lịch đặt ra khi săn ảnh phong cảnh vùng Tri Tôn. Điểm đặc biệt là giữa cánh đồng lúa mênh mông, thay vì mọc thành hàng hoặc cụm dày đặc như thông thường, cây này đứng lẻ loi một mình giữa bờ ruộng, tạo nên bố cục "cô độc" cực kỳ đắt giá cho khung hình.  2. Vị trí thực tế &amp; • Cách tiếp cận  Khu vực: Nằm giữa các cánh đồng lúa thuộc địa phận xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Trục đường: Nằm dọc theo các con đường đan, đường nội đồng cắt ngang cánh đồng nối giữa khu vực Chùa Hàng Còng (ấp An Hòa) và hướng đi về Cổng trời Chùa Koh Kas. • Nhận diện thực tế: Giữa một khoảng ruộng trống trải, tầm nhìn thoáng đãng không bị vướng nhà dân hay cột điện lớn, một thân thốt nốt thẳng đứng vươn cao với tán lá tròn xòe rộng, phía hậu cảnh là bóng mờ của các dãy núi thuộc vùng Thất Sơn.  3. Vì sao góc chụp này nổi tiếng trong giới nhiếp ảnh? • Bố cục tối giản (Minimalism): Cảnh quan xung quanh chỉ có trời, thảm lúa phẳng lì và một bóng cây duy nhất. Bố cục này giúp chủ thể chụp ảnh nổi bật hoàn toàn mà không bị rối mắt. • Hiệu ứng bóng đổ và Silhouette:  Vào buổi chiều tà (khoảng 17h15 – 18h00), khi mặt trời lặn sau dãy núi phía Tây, chụp ngược sáng sẽ bắt trọn dáng hình cây thốt nốt in bóng đen cắt ngang bầu trời ráng chiều đỏ rực hoặc tím biếc.  Vào mùa nước nổi, mặt ruộng ngập nước in bóng cây xuống như một chiếc gương khổng lồ.  4. Lưu ý thực tế khi ghé thăm • Địa hình bờ ruộng: Lối đi vào sát gốc cây là bờ đất nhỏ của ruộng lúa, vào mùa mưa hoặc mùa nước có thể trơn trượt hoặc lầy lội; nên cẩn thận khi bước đi và ưu tiên giày dép có độ bám tốt. • Tôn trọng bà con làm nông: Cây nằm trong đất canh tác lúa của người dân địa phương. Tuyệt đối không giẫm đạp lên lúa, không bẻ lá hay khắc tên lên thân cây và mang toàn bộ rác cá nhân ra ngoài.</t>
+          <t>Cánh Đồng Thốt Nốt Châu Lăng - Một Thiên Nhiên Huyền Bí Tại Tri Tôn  1. Tổng quan Cánh Đồng Thốt Nốt Châu Lăng tọa lạc tại Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang. Nơi đây là một thiên nhiên huyền bí, mang dấu ấn đặc trưng của vùng đất An Giang. Với mô hình cánh đồng thốt nốt độc đáo, Cánh Đồng Thốt Nốt Châu Lăng trở thành một điểm đến thú vị cho những ai yêu thích thiên nhiên và muốn khám phá vẻ đẹp nguyên sơ của Việt Nam.  2. Đánh giá từ du khách Chưa có đánh giá cụ thể từ du khách, nhưng với vẻ đẹp nguyên sơ và độc đáo, Cánh Đồng Thốt Nốt Châu Lăng chắc chắn sẽ mang lại những trải nghiệm thú vị và đáng nhớ cho du khách. Du khách sẽ được tận hưởng không gian mở, cảm nhận được sự yên tĩnh và hòa mình với thiên nhiên.  3. Lời khuyên Trước khi đến Cánh Đồng Thốt Nốt Châu Lăng, bạn nên tìm hiểu thêm về địa điểm này để có những chuẩn bị cần thiết. Ngoài ra, nên mang theo đủ nước, thức ăn và trang thiết bị cần thiết để có một chuyến đi thoải mái và an toàn.</t>
         </is>
       </c>
       <c r="O99" s="4" t="inlineStr"/>
       <c r="P99" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.439,105.0035</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.437,105.003</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>lang-nghe-tho-cam-chau-lang</t>
+          <t>a810d441-cây-thốt-nốt-cô-độc-</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Làng Nghề Dệt Thổ Cẩm Khmer Truyền Thống Châu Lăng</t>
+          <t>Cây Thốt Nốt Cô Độc Châu Lăng</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr"/>
@@ -6797,18 +6797,22 @@
           <t>Xã Châu Lăng</t>
         </is>
       </c>
-      <c r="F100" s="7" t="n"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Điểm check-in độc đáo</t>
+        </is>
+      </c>
       <c r="G100" s="6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>10.4412, 104.975</t>
+          <t>10.439, 105.0035</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Cây thốt nốt cô độc, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J100" s="7" t="inlineStr"/>
@@ -6824,18 +6828,18 @@
       </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>Làng nghề dệt thổ cẩm truyền thống lâu đời của phụ nữ Khmer xã Châu Lăng, lưu giữ kỹ thuật dệt hoa văn Thất Sơn tinh xảo trên khung cửi gỗ cổ truyền.</t>
+          <t>Thông Tin Thực Tế Về "Cây Thốt Nốt Cô Độc" (Châu Lăng)</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Thổ cẩm Khmer Châu Lăng nổi tiếng với màu sắc tự nhiên chiết xuất từ vỏ cây, củ nghệ và trái mặc nưa. Các sản phẩm đặc trưng gồm khăn Krama (khăn rằn Khmer), xà-rông, túi thổ cẩm và trang phục dạ hội truyền thống với các hoa văn hoa sen, rắn thần Naga và thần chim Garuda.</t>
+          <t>Tương tự như nhiều góc check-in tự nhiên tại vùng Bảy Núi, "Cây thốt nốt cô độc" không có ban quản lý, không bán vé và không có biển chỉ dẫn chính thức.  Tên gọi từ cộng • đồng nhiếp ảnh và phượt thủ: Tên gọi này do các nhiếp ảnh gia và bạn trẻ đam mê du lịch đặt ra khi săn ảnh phong cảnh vùng Tri Tôn. Điểm đặc biệt là giữa cánh đồng lúa mênh mông, thay vì mọc thành hàng hoặc cụm dày đặc như thông thường, cây này đứng lẻ loi một mình giữa bờ ruộng, tạo nên bố cục "cô độc" cực kỳ đắt giá cho khung hình.  2. Vị trí thực tế &amp; • Cách tiếp cận  Khu vực: Nằm giữa các cánh đồng lúa thuộc địa phận xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Trục đường: Nằm dọc theo các con đường đan, đường nội đồng cắt ngang cánh đồng nối giữa khu vực Chùa Hàng Còng (ấp An Hòa) và hướng đi về Cổng trời Chùa Koh Kas. • Nhận diện thực tế: Giữa một khoảng ruộng trống trải, tầm nhìn thoáng đãng không bị vướng nhà dân hay cột điện lớn, một thân thốt nốt thẳng đứng vươn cao với tán lá tròn xòe rộng, phía hậu cảnh là bóng mờ của các dãy núi thuộc vùng Thất Sơn.  3. Vì sao góc chụp này nổi tiếng trong giới nhiếp ảnh? • Bố cục tối giản (Minimalism): Cảnh quan xung quanh chỉ có trời, thảm lúa phẳng lì và một bóng cây duy nhất. Bố cục này giúp chủ thể chụp ảnh nổi bật hoàn toàn mà không bị rối mắt. • Hiệu ứng bóng đổ và Silhouette:  Vào buổi chiều tà (khoảng 17h15 – 18h00), khi mặt trời lặn sau dãy núi phía Tây, chụp ngược sáng sẽ bắt trọn dáng hình cây thốt nốt in bóng đen cắt ngang bầu trời ráng chiều đỏ rực hoặc tím biếc.  Vào mùa nước nổi, mặt ruộng ngập nước in bóng cây xuống như một chiếc gương khổng lồ.  4. Lưu ý thực tế khi ghé thăm • Địa hình bờ ruộng: Lối đi vào sát gốc cây là bờ đất nhỏ của ruộng lúa, vào mùa mưa hoặc mùa nước có thể trơn trượt hoặc lầy lội; nên cẩn thận khi bước đi và ưu tiên giày dép có độ bám tốt. • Tôn trọng bà con làm nông: Cây nằm trong đất canh tác lúa của người dân địa phương. Tuyệt đối không giẫm đạp lên lúa, không bẻ lá hay khắc tên lên thân cây và mang toàn bộ rác cá nhân ra ngoài.</t>
         </is>
       </c>
       <c r="O100" s="7" t="inlineStr"/>
       <c r="P100" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4412,104.975</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.439,105.0035</t>
         </is>
       </c>
     </row>
@@ -6845,12 +6849,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>nui-nam-quy</t>
+          <t>lang-nghe-tho-cam-chau-lang</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Núi Nam Quy</t>
+          <t>Làng Nghề Dệt Thổ Cẩm Khmer Truyền Thống Châu Lăng</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -6859,22 +6863,18 @@
           <t>Xã Châu Lăng</t>
         </is>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="F101" s="4" t="n"/>
       <c r="G101" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>10.4525302, 105.0037006</t>
+          <t>10.4412, 104.975</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>Núi Nam Quy, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr"/>
@@ -6890,18 +6890,18 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Nam Quy, điểm đến thiên nhiên độc đáo tại Bảy Núi, An Giang.</t>
+          <t>Làng nghề dệt thổ cẩm truyền thống lâu đời của phụ nữ Khmer xã Châu Lăng, lưu giữ kỹ thuật dệt hoa văn Thất Sơn tinh xảo trên khung cửi gỗ cổ truyền.</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>Núi • Nam Quy: Điểm đến thiên nhiên độc đáo tại Bảy Núi  Vùng đất Tri Tôn, thuộc dãy Thất Sơn (Bảy Núi) hùng vĩ, mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Núi Nam Quy là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang.  Hoàng sơ và bình yên  Núi Nam Quy nằm trong khu vực đồng bằng phù sa, với những dải núi đá granite trùng điệp. Cảnh sắc yên bình và không khí trong lành tạo nên một bức tranh tuyệt đẹp. Du khách có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về kinh nghiệm của mình khi đến với Núi Nam Quy. Một người đã nhận xét rằng công viên có nơi vui chơi dành cho trẻ em và cảnh quan thiên nhiên đẹp của núi rừng về chiều lén công viên ngồi gió mát. Tuy nhiên, cũng có một số người nhận xét rằng công viên này chủ yếu để buôn bán quà vặt và tập thể dục, chứ nếu đến để chơi là phụ thôi.  Lưu ý  Du khách cần lưu ý rằng có nhiều rắn sinh sống trong khu vực này, vì vậy cần cẩn thận khi di chuyển. Ngoài ra, không có đường lên núi cao 213m, vì có nhiều rắn dữ.  Kết luận  Núi Nam Quy là một điểm đến tuyệt vời cho những ai muốn khám phá cảnh sắc thiên nhiên độc đáo và trải nghiệm văn hóa phong phú của người Khmer. Hãy đến và khám phá!</t>
+          <t>Thổ cẩm Khmer Châu Lăng nổi tiếng với màu sắc tự nhiên chiết xuất từ vỏ cây, củ nghệ và trái mặc nưa. Các sản phẩm đặc trưng gồm khăn Krama (khăn rằn Khmer), xà-rông, túi thổ cẩm và trang phục dạ hội truyền thống với các hoa văn hoa sen, rắn thần Naga và thần chim Garuda.</t>
         </is>
       </c>
       <c r="O101" s="4" t="inlineStr"/>
       <c r="P101" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4525302,105.0037006</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4412,104.975</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>ho-latina</t>
+          <t>nui-nam-quy</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>hồ latina</t>
+          <t>Núi Nam Quy</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>camp_site</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G102" s="6" t="n">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>10.4240344, 104.9999364</t>
+          <t>10.4525302, 105.0037006</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>hồ latina, Xã An Hảo (Ranh giới giáp TX. Tịnh Biên), Tri Tôn, An Giang</t>
+          <t>Núi Nam Quy, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr"/>
@@ -6956,18 +6956,18 @@
       </c>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>Hồ Đá Latina (Vách Đá Latina) — Tuyệt tác vách đá dựng đứng soi bóng mặt nước tĩnh lặng, nằm tại khu vực Xã An Hảo, ngay cung đường giáp ranh TX. Tịnh Biên và Tri Tôn. Điểm check-in chụp ảnh vách đá hùng vĩ nổi tiếng.</t>
+          <t>Khám phá Núi Nam Quy, điểm đến thiên nhiên độc đáo tại Bảy Núi, An Giang.</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Vị trí và Ranh giới Thực địa Hồ Đá Latina nằm dưới chân núi Cấm, thuộc địa phận Xã An Hảo (tiếp giáp ranh giới giữa TX. Tịnh Biên và Tri Tôn). Du khách cần chú ý định vị chính xác vì khu vực này nằm trên trục đường liên ranh giới.  Trải nghiệm &amp; Cảnh quan Điểm nhấn ấn tượng nhất là vách đá hoa cương dựng đứng sừng sững bên hồ nước trong xanh. Đây là góc săn ảnh check-in thiên nhiên độc đáo, mang vẻ đẹp hoang sơ kỳ vĩ.</t>
+          <t>Núi • Nam Quy: Điểm đến thiên nhiên độc đáo tại Bảy Núi  Vùng đất Tri Tôn, thuộc dãy Thất Sơn (Bảy Núi) hùng vĩ, mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Núi Nam Quy là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang.  Hoàng sơ và bình yên  Núi Nam Quy nằm trong khu vực đồng bằng phù sa, với những dải núi đá granite trùng điệp. Cảnh sắc yên bình và không khí trong lành tạo nên một bức tranh tuyệt đẹp. Du khách có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về kinh nghiệm của mình khi đến với Núi Nam Quy. Một người đã nhận xét rằng công viên có nơi vui chơi dành cho trẻ em và cảnh quan thiên nhiên đẹp của núi rừng về chiều lén công viên ngồi gió mát. Tuy nhiên, cũng có một số người nhận xét rằng công viên này chủ yếu để buôn bán quà vặt và tập thể dục, chứ nếu đến để chơi là phụ thôi.  Lưu ý  Du khách cần lưu ý rằng có nhiều rắn sinh sống trong khu vực này, vì vậy cần cẩn thận khi di chuyển. Ngoài ra, không có đường lên núi cao 213m, vì có nhiều rắn dữ.  Kết luận  Núi Nam Quy là một điểm đến tuyệt vời cho những ai muốn khám phá cảnh sắc thiên nhiên độc đáo và trải nghiệm văn hóa phong phú của người Khmer. Hãy đến và khám phá!</t>
         </is>
       </c>
       <c r="O102" s="7" t="inlineStr"/>
       <c r="P102" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4240344,104.9999364</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4525302,105.0037006</t>
         </is>
       </c>
     </row>
@@ -6977,36 +6977,36 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>2ac3fb9a-con-đường-thốt-nốt-ô</t>
+          <t>ho-latina</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Thốt Nốt Ô Lâm - Cô Tô</t>
+          <t>hồ latina</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Xã Cô Tô</t>
+          <t>Xã Châu Lăng</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Con đường nhiếp ảnh</t>
+          <t>camp_site</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>10.38, 104.995</t>
+          <t>10.4240344, 104.9999364</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>Tuyến đường liên xã Ô Lâm - Núi Tô, Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>hồ latina, Xã An Hảo (Ranh giới giáp TX. Tịnh Biên), Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr"/>
@@ -7022,18 +7022,18 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Thốt Nốt Ô Lâm - Cô Tô, một điểm đến văn hóa độc đáo tại vùng Bảy Núi</t>
+          <t>Hồ Đá Latina (Vách Đá Latina) — Tuyệt tác vách đá dựng đứng soi bóng mặt nước tĩnh lặng, nằm tại khu vực Xã An Hảo, ngay cung đường giáp ranh TX. Tịnh Biên và Tri Tôn. Điểm check-in chụp ảnh vách đá hùng vĩ nổi tiếng.</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Thốt Nốt Ô Lâm – Cô Tô: Hàng Cây Biểu Tượng Triệu View Của Miền Tây Nam Bộ  Trải dài men theo con đường làng liên xã nối liền giữa Xã Ô Lâm và Xã Cô Tô, Con Đường Thốt Nốt Ô Lâm – Cô Tô là một trong những biểu tượng phong cảnh đặc trưng và đẹp mắt bậc nhất của vùng đất Tri Tôn An Giang. Hàng trăm thân cây thốt nốt cổ thụ cao vút mọc thẳng tắp hai bên lối đi đất đỏ xẻ dọc qua cánh đồng lúa bạt ngàn, tạo nên bối cảnh sống ảo triệu view đã từng xuất hiện trong vô số bộ ảnh cưới, phóng sự du lịch và video âm nhạc nổi tiếng.  1. Vị Trí &amp; Nét Đặc Biệt Của Tuyến Đường Thốt Nốt • Vị trí hành chính: Tuyến đường liên xã kết nối Xã Ô Lâm và Xã Cô Tô, tỉnh An Giang. • Khoảng cách: Cách trung tâm Thị trấn Tri Tôn khoảng 8 km về phía Tây Nam. • Mật độ thốt nốt dày đặc nhất Bảy Núi: Khác với những cây thốt nốt mọc rải rác đơn lẻ trên đồng, tại cung đường Ô Lâm – Cô Tô, hàng trăm cây thốt nốt hàng chục năm tuổi mọc thẳng hàng tăm tắp hai bên đường, tán lá xòe tròn như những chiếc quạt khổng lồ vươn lên nền trời xanh biếc.  2. Bức Tranh Đồng Quê Đậm Đà Bản Sắc Khmer • Sự hòa quyện giữa cây thốt nốt &amp; ruộng lúa: Dưới gốc những hàng thốt nốt là những thửa ruộng lúa bậc thang thoai thoải của đồng bào người Khmer. Tùy theo mùa vụ, mặt ruộng khoác lên màu xanh non mơn mởn, màu vàng rực rỡ của lúa chín, hoặc màu nước bạc lấp lánh mùa nước nổi. • Khai thác mật hoa thốt nốt truyền thống: Đi dạo trên cung đường này vào buổi sáng sớm hoặc xế chiều, du khách sẽ bắt gặp hình ảnh những người đàn ông Khmer thoăn thoắt leo lên ngọn thốt nốt cao vút bằng những thân tre gai để thu hoạch những ống tre đựng nước mật hoa ngọt lịm. • Những gánh hàng thốt nốt tươi ven đường: Dọc theo tuyến đường có nhiều quầy hàng mộc mạc của bà con địa phương bán nước thốt nốt tươi ướp lạnh, cùi thốt nốt dẻo giòn và đường thốt nốt nguyên chất gói trong lá thốt nốt khô thơm nức.  3. Tọa Độ Sống Ảo Triệu View Cho Giới Trẻ • Khung cảnh điện ảnh: Góc máy chụp dọc theo con đường với hàng thốt nốt chạy dài tít tắp về phía chân núi Cô Tô tạo nên chiều sâu phối cảnh hoàn hảo cho mọi bức ảnh. • Bối cảnh lý tưởng cho trang phục truyền thống: Cung đường rất thích hợp để chụp ảnh cùng tà áo bà ba, nón lá, khăn rằn Nam Bộ, trang phục xăm-pốt truyền thống Khmer hoặc phong cách du mục tự do.  4. Hướng Dẫn Khung Giờ Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm tuyệt vời nhất khi mặt trời đỏ ối dần lặn xuống sau rặng cây thốt nốt, bóng những hàng cây đổ dài trên mặt đất tạo nên những bức ảnh ngược sáng (silhouette) đầy tính nghệ thuật. • Bình minh dịu dàng (06:00 – 07:30 sáng): Khi sương sớm còn vương trên những tán lá và ánh nắng ban mai chiếu rọi nghiêng nghiêng qua kẽ lá. • Mùa lúa chín vàng: Tháng 4, Tháng 8 và Tháng 11–12 hàng năm là lúc cánh đồng hai bên đường rực vàng đẹp nhất.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Giao thông an toàn: Đường liên xã có xe máy và xe máy cày của bà con lưu thông, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào mép cỏ để đảm bảo an toàn. • Thưởng thức đặc sản: Đừng quên dừng chân mua ủng hộ bà con một ly nước thốt nốt tươi mát lạnh (giá chỉ 10.000đ – 15.000đ/ly) để tiếp thêm năng lượng cho hành trình khám phá.</t>
+          <t>Vị trí và Ranh giới Thực địa Hồ Đá Latina nằm dưới chân núi Cấm, thuộc địa phận Xã An Hảo (tiếp giáp ranh giới giữa TX. Tịnh Biên và Tri Tôn). Du khách cần chú ý định vị chính xác vì khu vực này nằm trên trục đường liên ranh giới.  Trải nghiệm &amp; Cảnh quan Điểm nhấn ấn tượng nhất là vách đá hoa cương dựng đứng sừng sững bên hồ nước trong xanh. Đây là góc săn ảnh check-in thiên nhiên độc đáo, mang vẻ đẹp hoang sơ kỳ vĩ.</t>
         </is>
       </c>
       <c r="O103" s="4" t="inlineStr"/>
       <c r="P103" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.38,104.995</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4240344,104.9999364</t>
         </is>
       </c>
     </row>
@@ -7043,12 +7043,12 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>d8731ae3-cầu-khỉ-giữa-cánh-đồ</t>
+          <t>2ac3fb9a-con-đường-thốt-nốt-ô</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Cầu Khỉ Giữa Cánh Đồng Thốt Nốt</t>
+          <t>Con Đường Thốt Nốt Ô Lâm - Cô Tô</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Điểm check-in mộc mạc</t>
+          <t>Con đường nhiếp ảnh</t>
         </is>
       </c>
       <c r="G104" s="6" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>10.388, 104.986</t>
+          <t>10.38, 104.995</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang</t>
+          <t>Tuyến đường liên xã Ô Lâm - Núi Tô, Xã Ô Lâm, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr"/>
@@ -7088,18 +7088,18 @@
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>Ngày nay, các loại cầu bằng bêtông trở nên phổ biến cùng với cầu thép. Nhịp cầu ngày càng được kéo dài, từ vài trăm mét như loại cầu …</t>
+          <t>Khám phá Con Đường Thốt Nốt Ô Lâm - Cô Tô, một điểm đến văn hóa độc đáo tại vùng Bảy Núi</t>
         </is>
       </c>
       <c r="N104" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm du lịch độc đáo và thú vị, tọa lạc tại Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang. Đây là một địa điểm văn hóa đặc sắc, mang lại trải nghiệm độc đáo cho du khách.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng chúng tôi tin rằng Cầu Khỉ Giữa Cánh Đồng Thốt Nốt sẽ mang lại cho bạn một trải nghiệm đáng nhớ. Với sự độc đáo và thú vị, nơi đây hứa hẹn sẽ khiến bạn không thể rời mắt.  3. Lời khuyên Khi đến Cầu Khỉ Giữa Cánh Đồng Thốt Nốt, bạn nên mang theo camera để chụp những bức ảnh độc đáo và thú vị. Cũng như, đừng quên mang theo nước uống và thực phẩm nhẹ để phục vụ cho chuyến tham quan của mình. Với mức giá Miễn phí, nơi đây là một địa điểm du lịch lý tưởng và đáng trải nghiệm.  Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm độc đáo và thú vị, mang lại cho bạn một trải nghiệm đáng nhớ. Với sự mở cửa tự do, nơi đây là một lựa chọn lý tưởng cho những ai muốn khám phá văn hóa và vẻ đẹp của An Giang. Hãy đến và trải nghiệm Cầu Khỉ Giữa Cánh Đồng Thốt Nốt để khám phá những điều thú vị và độc đáo!</t>
+          <t>Con Đường Thốt Nốt Ô Lâm – Cô Tô: Hàng Cây Biểu Tượng Triệu View Của Miền Tây Nam Bộ  Trải dài men theo con đường làng liên xã nối liền giữa Xã Ô Lâm và Xã Cô Tô, Con Đường Thốt Nốt Ô Lâm – Cô Tô là một trong những biểu tượng phong cảnh đặc trưng và đẹp mắt bậc nhất của vùng đất Tri Tôn An Giang. Hàng trăm thân cây thốt nốt cổ thụ cao vút mọc thẳng tắp hai bên lối đi đất đỏ xẻ dọc qua cánh đồng lúa bạt ngàn, tạo nên bối cảnh sống ảo triệu view đã từng xuất hiện trong vô số bộ ảnh cưới, phóng sự du lịch và video âm nhạc nổi tiếng.  1. Vị Trí &amp; Nét Đặc Biệt Của Tuyến Đường Thốt Nốt • Vị trí hành chính: Tuyến đường liên xã kết nối Xã Ô Lâm và Xã Cô Tô, tỉnh An Giang. • Khoảng cách: Cách trung tâm Thị trấn Tri Tôn khoảng 8 km về phía Tây Nam. • Mật độ thốt nốt dày đặc nhất Bảy Núi: Khác với những cây thốt nốt mọc rải rác đơn lẻ trên đồng, tại cung đường Ô Lâm – Cô Tô, hàng trăm cây thốt nốt hàng chục năm tuổi mọc thẳng hàng tăm tắp hai bên đường, tán lá xòe tròn như những chiếc quạt khổng lồ vươn lên nền trời xanh biếc.  2. Bức Tranh Đồng Quê Đậm Đà Bản Sắc Khmer • Sự hòa quyện giữa cây thốt nốt &amp; ruộng lúa: Dưới gốc những hàng thốt nốt là những thửa ruộng lúa bậc thang thoai thoải của đồng bào người Khmer. Tùy theo mùa vụ, mặt ruộng khoác lên màu xanh non mơn mởn, màu vàng rực rỡ của lúa chín, hoặc màu nước bạc lấp lánh mùa nước nổi. • Khai thác mật hoa thốt nốt truyền thống: Đi dạo trên cung đường này vào buổi sáng sớm hoặc xế chiều, du khách sẽ bắt gặp hình ảnh những người đàn ông Khmer thoăn thoắt leo lên ngọn thốt nốt cao vút bằng những thân tre gai để thu hoạch những ống tre đựng nước mật hoa ngọt lịm. • Những gánh hàng thốt nốt tươi ven đường: Dọc theo tuyến đường có nhiều quầy hàng mộc mạc của bà con địa phương bán nước thốt nốt tươi ướp lạnh, cùi thốt nốt dẻo giòn và đường thốt nốt nguyên chất gói trong lá thốt nốt khô thơm nức.  3. Tọa Độ Sống Ảo Triệu View Cho Giới Trẻ • Khung cảnh điện ảnh: Góc máy chụp dọc theo con đường với hàng thốt nốt chạy dài tít tắp về phía chân núi Cô Tô tạo nên chiều sâu phối cảnh hoàn hảo cho mọi bức ảnh. • Bối cảnh lý tưởng cho trang phục truyền thống: Cung đường rất thích hợp để chụp ảnh cùng tà áo bà ba, nón lá, khăn rằn Nam Bộ, trang phục xăm-pốt truyền thống Khmer hoặc phong cách du mục tự do.  4. Hướng Dẫn Khung Giờ Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm tuyệt vời nhất khi mặt trời đỏ ối dần lặn xuống sau rặng cây thốt nốt, bóng những hàng cây đổ dài trên mặt đất tạo nên những bức ảnh ngược sáng (silhouette) đầy tính nghệ thuật. • Bình minh dịu dàng (06:00 – 07:30 sáng): Khi sương sớm còn vương trên những tán lá và ánh nắng ban mai chiếu rọi nghiêng nghiêng qua kẽ lá. • Mùa lúa chín vàng: Tháng 4, Tháng 8 và Tháng 11–12 hàng năm là lúc cánh đồng hai bên đường rực vàng đẹp nhất.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Giao thông an toàn: Đường liên xã có xe máy và xe máy cày của bà con lưu thông, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào mép cỏ để đảm bảo an toàn. • Thưởng thức đặc sản: Đừng quên dừng chân mua ủng hộ bà con một ly nước thốt nốt tươi mát lạnh (giá chỉ 10.000đ – 15.000đ/ly) để tiếp thêm năng lượng cho hành trình khám phá.</t>
         </is>
       </c>
       <c r="O104" s="7" t="inlineStr"/>
       <c r="P104" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.388,104.986</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.38,104.995</t>
         </is>
       </c>
     </row>
@@ -7109,12 +7109,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>833d6714-nấc-thang-thiên-đườn</t>
+          <t>d8731ae3-cầu-khỉ-giữa-cánh-đồ</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum</t>
+          <t>Cầu Khỉ Giữa Cánh Đồng Thốt Nốt</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
@@ -7125,20 +7125,20 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Tiểu cảnh check-in</t>
+          <t>Điểm check-in mộc mạc</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>10.3776, 104.9926</t>
+          <t>10.388, 104.986</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>Khuôn viên Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr"/>
@@ -7154,18 +7154,18 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>Tiểu cảnh check-in nấc thang vươn lên trời mây ngắm trọn cảnh mặt hồ Ô Thum thơ mộng tại khuôn viên Quán Kiều Tiên, Xã Ô Lâm.</t>
+          <t>Ngày nay, các loại cầu bằng bêtông trở nên phổ biến cùng với cầu thép. Nhịp cầu ngày càng được kéo dài, từ vài trăm mét như loại cầu …</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum – Tọa Độ 'Sống Ảo' Chạm Mây Bên Lòng Hồ Ô Thum  Nằm nổi bật bên triền hồ Ô Thum thuộc Xã Ô Lâm, Nấc Thang Thiên Đường Kiều Tiên là một trong những tiểu cảnh check-in mang tính biểu tượng thu hút đông đảo bạn trẻ và du khách yêu thích nhiếp ảnh khi ghé thăm Tri Tôn. Nấc thang màu trắng tinh khôi vươn thẳng lên nền trời xanh biếc, hòa cùng mặt nước hồ phẳng lặng và bóng núi Thất Sơn tạo nên khung cảnh lãng mạn như chốn bồng lai tiên cảnh.  1. Vị Trí &amp; Không Gian Khuôn Viên Kiều Tiên • Địa chỉ hành chính: Khuôn viên Quán Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, tỉnh An Giang. • Tầm nhìn khoáng đạt: Nấc thang được xây dựng kiên cố ven bờ hồ, hướng thẳng ra vùng lòng hồ bao la và rặng thốt nốt xanh ngát của Xã Ô Lâm. Đứng từ chân cầu thang nhìn lên, các bậc thang nối đuôi nhau như dẫn lối thẳng lên trời mây.  2. Trải Nghiệm Check-in &amp; Săn Ảnh Độc Bản • Góc chụp 'vô cực' chạm mây: Chụp từ dưới góc thấp lên mút bậc thang cao nhất, tạo cảm giác như người mẫu đang bước đi giữa không trung bồng bềnh mây trời. • Khung giờ vàng hoàng hôn (16:30 – 17:30): Bầu trời Ô Thum chuyển sang sắc cam hồng rực rỡ, ánh nắng hoàng hôn dát vàng lên từng bậc thang tạo nên những bức ảnh ngược sáng (silhouette) tuyệt mỹ. • Kết hợp check-in cầu gỗ Ô Thum: Du khách có thể dễ dàng dạo bước sang cây cầu gỗ mộc mạc bắc ngang bờ hồ ngay kế bên để chụp trọn bộ ảnh thiên nhiên Bảy Núi.  3. Kết Hợp Thưởng Thức Ẩm Thực Bản Địa • Gà đốt lá chúc Kiều Tiên: Ngay tại khuôn viên là quán gà đốt trứ danh lâu đời nhất Hồ Ô Thum. Du khách sau khi chụp ảnh có thể ngồi tại các chòi tre lợp lá mát rượi thưởng thức đĩa gà đốt nóng giòn chấm muối ớt lá chúc cay nồng.  4. Lưu Ý Dành Cho Du Khách • An toàn khi chụp ảnh: Từng người bước lên bậc thang chậm rãi, giữ thăng bằng và không chen lấn xô đẩy trên các bậc cao. • Trang phục gợi ý: Trang phục màu sáng (trắng, vàng, đỏ, váy maxi bay bổng) sẽ nổi bật nhất trên nền trời xanh và mặt hồ ngọc bích. • Giờ mở cửa: 08:00 – 19:00 hàng ngày (Miễn phí check-in chụp ảnh cho thực khách dùng bữa tại quán).</t>
+          <t>1. Tổng quan Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm du lịch độc đáo và thú vị, tọa lạc tại Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang. Đây là một địa điểm văn hóa đặc sắc, mang lại trải nghiệm độc đáo cho du khách.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng chúng tôi tin rằng Cầu Khỉ Giữa Cánh Đồng Thốt Nốt sẽ mang lại cho bạn một trải nghiệm đáng nhớ. Với sự độc đáo và thú vị, nơi đây hứa hẹn sẽ khiến bạn không thể rời mắt.  3. Lời khuyên Khi đến Cầu Khỉ Giữa Cánh Đồng Thốt Nốt, bạn nên mang theo camera để chụp những bức ảnh độc đáo và thú vị. Cũng như, đừng quên mang theo nước uống và thực phẩm nhẹ để phục vụ cho chuyến tham quan của mình. Với mức giá Miễn phí, nơi đây là một địa điểm du lịch lý tưởng và đáng trải nghiệm.  Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm độc đáo và thú vị, mang lại cho bạn một trải nghiệm đáng nhớ. Với sự mở cửa tự do, nơi đây là một lựa chọn lý tưởng cho những ai muốn khám phá văn hóa và vẻ đẹp của An Giang. Hãy đến và trải nghiệm Cầu Khỉ Giữa Cánh Đồng Thốt Nốt để khám phá những điều thú vị và độc đáo!</t>
         </is>
       </c>
       <c r="O105" s="4" t="inlineStr"/>
       <c r="P105" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3776,104.9926</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.388,104.986</t>
         </is>
       </c>
     </row>
@@ -7175,12 +7175,12 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>6669ffb7-suối-vàng-soài-so</t>
+          <t>833d6714-nấc-thang-thiên-đườn</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Suối Vàng Soài So</t>
+          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr"/>
@@ -7191,7 +7191,7 @@
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Suối sinh thái</t>
+          <t>Tiểu cảnh check-in</t>
         </is>
       </c>
       <c r="G106" s="6" t="n">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>10.4055, 105.0255</t>
+          <t>10.3776, 104.9926</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>Khu vực Suối Vàng Soài So, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Khuôn viên Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr"/>
@@ -7220,18 +7220,18 @@
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>Dòng suối tự nhiên trong vắt bắt nguồn từ đỉnh Núi Cô Tô len lỏi qua các khe đá rợp bóng cây rừng, chảy về lòng Hồ Soài So, xã Núi Tô. Điểm dã ngoại, tắm mát và cắm trại lý tưởng.</t>
+          <t>Tiểu cảnh check-in nấc thang vươn lên trời mây ngắm trọn cảnh mặt hồ Ô Thum thơ mộng tại khuôn viên Quán Kiều Tiên, Xã Ô Lâm.</t>
         </is>
       </c>
       <c r="N106" s="7" t="inlineStr">
         <is>
-          <t>Khám Phá Suối Vàng Soài So &amp; Dòng Suối Bạc – Dải Lụa Nước Khoáng Trong Vắt Dưới Chân Núi Cô Tô  Ẩn mình dưới chân ngọn núi Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ thuộc Xã Núi Tô, Khu du lịch Suối Vàng Soài So là một trong những điểm dã ngoại, tắm suối tự nhiên và cắm trại sinh thái mát lành bậc nhất của vùng Bảy Núi An Giang. Dòng suối đá tự nhiên tuôn trào từ các tầng địa chất granite trên đỉnh núi, len lỏi qua những cánh rừng tầm vông xanh ngắt và đổ dòng nước trong vắt về lòng Hồ Soài So thơ mộng.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Suối Vàng - Suối Bạc" • Vị trí hành chính: Nằm trong khuôn viên Khu du lịch Suối Vàng Soài So, chân Núi Cô Tô, Xã Núi Tô, tỉnh An Giang. • Cách di chuyển: Từ trung tâm Thị trấn Tri Tôn, du khách đi theo đường Trần Hưng Đạo khoảng 2 km về hướng Nam, rẽ vào cổng chào Khu du lịch Suối Vàng Soài So sẽ thấy con đường rợp bóng cây dẫn thẳng vào chân suối. • Sự tích tên gọi: Theo truyền tích của các bậc cao niên Bảy Núi, dòng suối này bắt nguồn từ các mạch nước ngầm tinh khiết trên đỉnh Cô Tô. Nước chảy qua các khe đá có chứa quặng khoáng tự nhiên lấp lánh dưới ánh mặt trời, tạo nên hai nhánh suối kỳ ảo được người xưa tôn kính đặt tên là Suối Vàng và Suối Bạc.  2. Cảnh Quan Thiên Nhiên &amp; Hệ Sinh Thái Núi Rừng • Tầng tầng lớp lớp đá granite: Dòng suối chảy qua những tảng đá hoa cương khổng lồ với đủ hình thù kỳ thú, tạo thành những hồ tắm thiên nhiên nhỏ với mực nước chỉ ngang đầu gối, nước trong vắt đến mức có thể nhìn thấy đàn cá nhỏ bơi lội dưới đáy. • Rừng cây rợp bóng mát rượi: Hai bên bờ suối là những tán rừng tầm vông, vườn xoài cổ thụ và cây dầu rái trăm năm tuổi tỏa bóng mát rượi, giữ cho nhiệt độ nơi đây luôn thấp hơn khu vực đồng bằng từ 3–5 độ C. • Hồ chứa nước Soài So: Dưới chân suối là lòng Hồ Soài So rộng lớn phẳng lặng như gương soi, phản chiếu bóng núi Cô Tô sừng sững giữa bầu trời xanh biếc.  3. Trải Nghiệm Thực Địa Hấp Dẫn Không Thể Bỏ Qua • Tắm suối đá khoáng mát lạnh: Đắm mình trong làn nước suối mát rượi, lắng nghe tiếng nước chảy róc rách và tiếng chim rừng hót líu lo là liệu pháp thư giãn tinh thần tuyệt vời sau chuỗi ngày làm việc căng thẳng. • Tổ chức picnic &amp; Cắm trại ven suối: Các phiến đá phẳng rộng lớn bên bờ suối là vị trí lý tưởng để trải bạt, nướng đồ ăn dã ngoại và quây quần bên gia đình, bạn bè. • Trekking ngược dòng suối lên sườn núi: Với những ai yêu thích khám phá, cung đường men theo vách đá suối dẫn lên các am điện tu tập và vườn cây ăn trái lưng chừng núi Cô Tô mang lại cảm giác chinh phục thiên nhiên hoang sơ.  4. Hướng Dẫn Góc Check-in &amp; Khung Giờ Vàng • Khung giờ chụp ảnh đẹp nhất: 08:00 – 10:30 sáng khi ánh nắng ban mai rọi qua tán lá tạo thành những vạt sáng lung linh trên mặt nước suối; hoặc 15:00 – 17:00 chiều để ngắm hoàng hôn buông xuống mặt Hồ Soài So. • Góc chụp sống ảo: Đứng trên các phiến đá giữa dòng suối lấy hậu cảnh là vách đá rêu phong và rừng tầm vông, hoặc chụp toàn cảnh bờ kè Hồ Soài So hướng về đỉnh Phụng Hoàng Sơn. • Mùa lý tưởng: Mùa mưa từ tháng 6 đến tháng 11 âm lịch là thời điểm suối nhiều nước và trong xanh đẹp nhất trong năm.  5. Lưu Ý An Toàn &amp; Bảo Vệ Cảnh Quan • Cảnh báo trơn trượt: Các phiến đá ven suối có rêu bám trơn trượt, du khách nên đi dép có độ bám tốt hoặc giày thể thao lội nước, cẩn thận khi bước nhảy qua các khe đá. • Vệ sinh môi trường: Tuyệt đối không xả rác, túi nilon hay chai nhựa xuống lòng suối; gom toàn bộ rác thải vào thùng rác sau khi ăn uống dã ngoại. • Giá vé: Vé vào cổng khu du lịch khoảng 10.000đ – 20.000đ/người (giữ xe máy 5.000đ).</t>
+          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum – Tọa Độ 'Sống Ảo' Chạm Mây Bên Lòng Hồ Ô Thum  Nằm nổi bật bên triền hồ Ô Thum thuộc Xã Ô Lâm, Nấc Thang Thiên Đường Kiều Tiên là một trong những tiểu cảnh check-in mang tính biểu tượng thu hút đông đảo bạn trẻ và du khách yêu thích nhiếp ảnh khi ghé thăm Tri Tôn. Nấc thang màu trắng tinh khôi vươn thẳng lên nền trời xanh biếc, hòa cùng mặt nước hồ phẳng lặng và bóng núi Thất Sơn tạo nên khung cảnh lãng mạn như chốn bồng lai tiên cảnh.  1. Vị Trí &amp; Không Gian Khuôn Viên Kiều Tiên • Địa chỉ hành chính: Khuôn viên Quán Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, tỉnh An Giang. • Tầm nhìn khoáng đạt: Nấc thang được xây dựng kiên cố ven bờ hồ, hướng thẳng ra vùng lòng hồ bao la và rặng thốt nốt xanh ngát của Xã Ô Lâm. Đứng từ chân cầu thang nhìn lên, các bậc thang nối đuôi nhau như dẫn lối thẳng lên trời mây.  2. Trải Nghiệm Check-in &amp; Săn Ảnh Độc Bản • Góc chụp 'vô cực' chạm mây: Chụp từ dưới góc thấp lên mút bậc thang cao nhất, tạo cảm giác như người mẫu đang bước đi giữa không trung bồng bềnh mây trời. • Khung giờ vàng hoàng hôn (16:30 – 17:30): Bầu trời Ô Thum chuyển sang sắc cam hồng rực rỡ, ánh nắng hoàng hôn dát vàng lên từng bậc thang tạo nên những bức ảnh ngược sáng (silhouette) tuyệt mỹ. • Kết hợp check-in cầu gỗ Ô Thum: Du khách có thể dễ dàng dạo bước sang cây cầu gỗ mộc mạc bắc ngang bờ hồ ngay kế bên để chụp trọn bộ ảnh thiên nhiên Bảy Núi.  3. Kết Hợp Thưởng Thức Ẩm Thực Bản Địa • Gà đốt lá chúc Kiều Tiên: Ngay tại khuôn viên là quán gà đốt trứ danh lâu đời nhất Hồ Ô Thum. Du khách sau khi chụp ảnh có thể ngồi tại các chòi tre lợp lá mát rượi thưởng thức đĩa gà đốt nóng giòn chấm muối ớt lá chúc cay nồng.  4. Lưu Ý Dành Cho Du Khách • An toàn khi chụp ảnh: Từng người bước lên bậc thang chậm rãi, giữ thăng bằng và không chen lấn xô đẩy trên các bậc cao. • Trang phục gợi ý: Trang phục màu sáng (trắng, vàng, đỏ, váy maxi bay bổng) sẽ nổi bật nhất trên nền trời xanh và mặt hồ ngọc bích. • Giờ mở cửa: 08:00 – 19:00 hàng ngày (Miễn phí check-in chụp ảnh cho thực khách dùng bữa tại quán).</t>
         </is>
       </c>
       <c r="O106" s="7" t="inlineStr"/>
       <c r="P106" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4055,105.0255</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3776,104.9926</t>
         </is>
       </c>
     </row>
@@ -7241,36 +7241,36 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>nui-sa-lon</t>
+          <t>6669ffb7-suối-vàng-soài-so</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn</t>
+          <t>Suối Vàng Soài So</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Xã Lương Phi</t>
+          <t>Xã Cô Tô</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>Suối sinh thái</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>10.4386816, 104.9624942</t>
+          <t>10.4055, 105.0255</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn, Xã Lương Phi, Tri Tôn, An Giang</t>
+          <t>Khu vực Suối Vàng Soài So, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr"/>
@@ -7286,18 +7286,18 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Sà Lôn - điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang</t>
+          <t>Dòng suối tự nhiên trong vắt bắt nguồn từ đỉnh Núi Cô Tô len lỏi qua các khe đá rợp bóng cây rừng, chảy về lòng Hồ Soài So, xã Núi Tô. Điểm dã ngoại, tắm mát và cắm trại lý tưởng.</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn - Điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang  Núi Sà Lôn là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang. Vùng đất Tri Tôn nằm trong dãy Thất Sơn (Bảy Núi) hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  Khi đến Núi Sà Lôn, du khách có cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Đặc sản nước thốt nốt tươi, bánh bò thốt nốt là những món ăn bạn không thể bỏ qua khi đến đây. Du khách cũng có thể tìm hiểu các phong tục tập quán truyền thống của người dân địa phương.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về trải nghiệm của mình tại Núi Sà Lôn. Họ đã thưởng thức nước thốt nốt tươi ngon và bánh bò thốt nốt giòn tan. Họ cũng đã học hỏi được những phong tục tập quán truyền thống của người dân địa phương.  Khám phá Núi Sà Lôn  Núi Sà Lôn là một điểm đến không thể bỏ qua khi bạn đến thăm Tri Tôn, An Giang. Với cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương, Núi Sà Lôn chắc chắn sẽ mang lại cho bạn những trải nghiệm đáng nhớ.</t>
+          <t>Khám Phá Suối Vàng Soài So &amp; Dòng Suối Bạc – Dải Lụa Nước Khoáng Trong Vắt Dưới Chân Núi Cô Tô  Ẩn mình dưới chân ngọn núi Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ thuộc Xã Núi Tô, Khu du lịch Suối Vàng Soài So là một trong những điểm dã ngoại, tắm suối tự nhiên và cắm trại sinh thái mát lành bậc nhất của vùng Bảy Núi An Giang. Dòng suối đá tự nhiên tuôn trào từ các tầng địa chất granite trên đỉnh núi, len lỏi qua những cánh rừng tầm vông xanh ngắt và đổ dòng nước trong vắt về lòng Hồ Soài So thơ mộng.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Suối Vàng - Suối Bạc" • Vị trí hành chính: Nằm trong khuôn viên Khu du lịch Suối Vàng Soài So, chân Núi Cô Tô, Xã Núi Tô, tỉnh An Giang. • Cách di chuyển: Từ trung tâm Thị trấn Tri Tôn, du khách đi theo đường Trần Hưng Đạo khoảng 2 km về hướng Nam, rẽ vào cổng chào Khu du lịch Suối Vàng Soài So sẽ thấy con đường rợp bóng cây dẫn thẳng vào chân suối. • Sự tích tên gọi: Theo truyền tích của các bậc cao niên Bảy Núi, dòng suối này bắt nguồn từ các mạch nước ngầm tinh khiết trên đỉnh Cô Tô. Nước chảy qua các khe đá có chứa quặng khoáng tự nhiên lấp lánh dưới ánh mặt trời, tạo nên hai nhánh suối kỳ ảo được người xưa tôn kính đặt tên là Suối Vàng và Suối Bạc.  2. Cảnh Quan Thiên Nhiên &amp; Hệ Sinh Thái Núi Rừng • Tầng tầng lớp lớp đá granite: Dòng suối chảy qua những tảng đá hoa cương khổng lồ với đủ hình thù kỳ thú, tạo thành những hồ tắm thiên nhiên nhỏ với mực nước chỉ ngang đầu gối, nước trong vắt đến mức có thể nhìn thấy đàn cá nhỏ bơi lội dưới đáy. • Rừng cây rợp bóng mát rượi: Hai bên bờ suối là những tán rừng tầm vông, vườn xoài cổ thụ và cây dầu rái trăm năm tuổi tỏa bóng mát rượi, giữ cho nhiệt độ nơi đây luôn thấp hơn khu vực đồng bằng từ 3–5 độ C. • Hồ chứa nước Soài So: Dưới chân suối là lòng Hồ Soài So rộng lớn phẳng lặng như gương soi, phản chiếu bóng núi Cô Tô sừng sững giữa bầu trời xanh biếc.  3. Trải Nghiệm Thực Địa Hấp Dẫn Không Thể Bỏ Qua • Tắm suối đá khoáng mát lạnh: Đắm mình trong làn nước suối mát rượi, lắng nghe tiếng nước chảy róc rách và tiếng chim rừng hót líu lo là liệu pháp thư giãn tinh thần tuyệt vời sau chuỗi ngày làm việc căng thẳng. • Tổ chức picnic &amp; Cắm trại ven suối: Các phiến đá phẳng rộng lớn bên bờ suối là vị trí lý tưởng để trải bạt, nướng đồ ăn dã ngoại và quây quần bên gia đình, bạn bè. • Trekking ngược dòng suối lên sườn núi: Với những ai yêu thích khám phá, cung đường men theo vách đá suối dẫn lên các am điện tu tập và vườn cây ăn trái lưng chừng núi Cô Tô mang lại cảm giác chinh phục thiên nhiên hoang sơ.  4. Hướng Dẫn Góc Check-in &amp; Khung Giờ Vàng • Khung giờ chụp ảnh đẹp nhất: 08:00 – 10:30 sáng khi ánh nắng ban mai rọi qua tán lá tạo thành những vạt sáng lung linh trên mặt nước suối; hoặc 15:00 – 17:00 chiều để ngắm hoàng hôn buông xuống mặt Hồ Soài So. • Góc chụp sống ảo: Đứng trên các phiến đá giữa dòng suối lấy hậu cảnh là vách đá rêu phong và rừng tầm vông, hoặc chụp toàn cảnh bờ kè Hồ Soài So hướng về đỉnh Phụng Hoàng Sơn. • Mùa lý tưởng: Mùa mưa từ tháng 6 đến tháng 11 âm lịch là thời điểm suối nhiều nước và trong xanh đẹp nhất trong năm.  5. Lưu Ý An Toàn &amp; Bảo Vệ Cảnh Quan • Cảnh báo trơn trượt: Các phiến đá ven suối có rêu bám trơn trượt, du khách nên đi dép có độ bám tốt hoặc giày thể thao lội nước, cẩn thận khi bước nhảy qua các khe đá. • Vệ sinh môi trường: Tuyệt đối không xả rác, túi nilon hay chai nhựa xuống lòng suối; gom toàn bộ rác thải vào thùng rác sau khi ăn uống dã ngoại. • Giá vé: Vé vào cổng khu du lịch khoảng 10.000đ – 20.000đ/người (giữ xe máy 5.000đ).</t>
         </is>
       </c>
       <c r="O107" s="4" t="inlineStr"/>
       <c r="P107" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4386816,104.9624942</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4055,105.0255</t>
         </is>
       </c>
     </row>
@@ -7307,23 +7307,23 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>9616e5e5-con-đường-tơ-lụa-tà-</t>
+          <t>nui-sa-lon</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Con Đường Tơ Lụa Tà Pạ</t>
+          <t>Núi Sà Lôn</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr"/>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Xã Núi Tô</t>
+          <t>Xã Lương Phi</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Con đường tơ lụa</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G108" s="6" t="n">
@@ -7331,12 +7331,12 @@
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>10.4185, 105.0095</t>
+          <t>10.4386816, 104.9624942</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>Tuyến đường lúa Tà Pạ, Ấp Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Núi Sà Lôn, Xã Lương Phi, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr"/>
@@ -7352,18 +7352,18 @@
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Tơ Lụa Tà Pạ - Di tích lịch sử văn hóa độc đáo ở An Giang</t>
+          <t>Khám phá Núi Sà Lôn - điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
         <is>
-          <t>Con Đường Tơ Lụa Tà Pạ – Dải Lụa Nghìn Màu Uốn Lượn Giữa Cánh Đồng Thất Sơn  Được mệnh danh là một trong những cung đường đồng quê đẹp và lãng mạn nhất miền Tây Nam Bộ, Con Đường Tơ Lụa Tà Pạ là dải đường bê tông nhỏ uốn lượn mềm mại tựa như một dải lụa mềm xẻ dọc qua cánh đồng lúa Tà Pạ và Hồ Soài Chek thuộc Xã Núi Tô. Cung đường này đã trở thành nguồn cảm hứng bất tận cho các nhiếp ảnh gia, giới trẻ mê xê dịch và những ai trót say đắm vẻ đẹp mộc mạc, thanh bình của vùng đất Bảy Núi.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Con Đường Tơ Lụa" • Vị trí hành chính: Nằm tại cánh đồng Tà Pạ, kết nối giữa khu vực Hồ Soài Chek và chân Đồi Tà Pạ, Xã Núi Tô, tỉnh An Giang. • Sự tích tên gọi: Từ trên đỉnh Núi Tô hoặc chùa Tà Pạ nhìn xuống, con đường bê tông trắng uốn lượn nhiều khúc quanh co mềm mại, uốn quanh các bờ ruộng ô vuông bàn cờ như một dải lụa tơ tằm mềm mại vắt ngang qua bức tranh đồng lúa bạt ngàn. Du khách và các nhiếp ảnh gia đã ưu ái gọi tên cung đường này là "Con Đường Tơ Lụa Tri Tôn". • Hạ tầng hoàn thiện: Trước đây là đường đất bờ ruộng nhỏ hẹp, nay đã được chính quyền và bà con địa phương bê tông hóa phẳng phiu, giúp xe máy và xe đạp có thể di chuyển êm ái xuyên suốt cung đường.  2. Bức Họa Thiên Nhiên Rực Rỡ Bốn Mùa • Vũ điệu sắc màu theo mùa lúa:  • Mùa nước đổ &amp; Mạ non (Tháng 3, Tháng 7): Cả cánh đồng ngập tràn sắc xanh mướt mát mắt, mặt nước ruộng lúa phản chiếu mây trời lồng lộng. • Mùa lúa chín vàng (Tháng 4, Tháng 8, Tháng 11–12): Cung đường như chìm đắm giữa biển vàng óng ả, hương thơm ngọt ngào của lúa mới phảng phất khắp không gian. • Hàng cây thốt nốt &amp; Cây trâm cổ thụ: Dọc theo hai bên đ.  ường là những rặng cây thốt nốt vươn cao kiêu hãnh và những gốc trâm cổ thụ trăm năm tuổi tỏa bóng mát râm ran, tạo nên khung cảnh làng quê Khmer bình yên đến nao lòng. • Hậu cảnh núi non kỳ vĩ: Phía xa xa là bóng dáng hùng vĩ của Núi Tô và Núi Cấm che chắn, điểm xuyết những mái chùa Khmer chóp nhọn vàng rực ẩn hiện sau rặng cây.  3. Nhịp Sống Đồng Quê &amp; Nét Đẹp Đời Thường • Hình ảnh người nông dân Khmer trên đồng: Du khách sẽ dễ dàng bắt gặp hình ảnh những người nông dân Khmer đội nón lá cần mẫn gặt lúa, những đàn bò thong dong gặm cỏ trên bờ ruộng và các em nhỏ vui đùa thả diều mỗi buổi chiều tà. • Không gian tĩnh lặng, trong lành: Tách biệt hoàn toàn khỏi khói bụi và tiếng ồn của đô thị, nơi đây chỉ có tiếng gió lướt qua ngọn lúa xào xạc và tiếng chim hót rộn rã đầu cành.  4. Hướng Dẫn Check-in &amp; Khung Giờ Sống Ảo Triệu View • Săn bình minh rạng rỡ (06:00 – 07:30): Khi ánh mặt trời vừa ló rạng sau rặng núi, sương sớm còn đọng long lanh trên từng nhánh lúa, tạo nên một không gian mờ ảo, lung linh như cõi tiên. • Đón hoàng hôn ấm áp (16:30 – 17:45): Ánh nắng chiều tà nhuộm vàng rực rỡ cả cung đường, bóng những hàng cây thốt nốt đổ dài trên mặt ruộng là khoảnh khắc vàng để chụp ảnh ngược sáng (silhouette). • Góc chụp lý tưởng: Chụp từ góc thấp hướng dọc theo đường cong uốn lượn của cung đường; chụp cùng tà áo dài hoặc trang phục truyền thống Khmer; chụp toàn cảnh từ flycam trên cao.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Tôn trọng nông dân: Tuyệt đối không dẫm đạp lên lúa của bà con, không bẻ nhánh hay hái quả thốt nốt non của các hộ dân ven đường. • An toàn giao thông: Đường nhỏ vừa cho 2 xe máy tránh nhau, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào sát lề đường để không cản trở lối đi của bà con nông dân. • Chi phí: Hoàn toàn miễn phí tham quan và chụp ảnh tự do.</t>
+          <t>Núi Sà Lôn - Điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang  Núi Sà Lôn là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang. Vùng đất Tri Tôn nằm trong dãy Thất Sơn (Bảy Núi) hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  Khi đến Núi Sà Lôn, du khách có cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Đặc sản nước thốt nốt tươi, bánh bò thốt nốt là những món ăn bạn không thể bỏ qua khi đến đây. Du khách cũng có thể tìm hiểu các phong tục tập quán truyền thống của người dân địa phương.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về trải nghiệm của mình tại Núi Sà Lôn. Họ đã thưởng thức nước thốt nốt tươi ngon và bánh bò thốt nốt giòn tan. Họ cũng đã học hỏi được những phong tục tập quán truyền thống của người dân địa phương.  Khám phá Núi Sà Lôn  Núi Sà Lôn là một điểm đến không thể bỏ qua khi bạn đến thăm Tri Tôn, An Giang. Với cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương, Núi Sà Lôn chắc chắn sẽ mang lại cho bạn những trải nghiệm đáng nhớ.</t>
         </is>
       </c>
       <c r="O108" s="7" t="inlineStr"/>
       <c r="P108" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4185,105.0095</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4386816,104.9624942</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>ho-soai-chek</t>
+          <t>9616e5e5-con-đường-tơ-lụa-tà-</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Hồ Soài Chek</t>
+          <t>Con Đường Tơ Lụa Tà Pạ</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>Con đường tơ lụa</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>10.4285, 104.9924</t>
+          <t>10.4185, 105.0095</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Xã Ba Chúc, huyện Tri Tôn, An Giang</t>
+          <t>Tuyến đường lúa Tà Pạ, Ấp Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr"/>
@@ -7418,18 +7418,18 @@
       </c>
       <c r="M109" s="4" t="inlineStr">
         <is>
-          <t>Hồ thủy lợi thơ mộng dưới chân đồi Tà Pạ, xã Núi Tô. Không gian tĩnh lặng, thoáng đãng, là điểm cắm trại ngắm hoàng hôn buông trên đồi cát và rặng thốt nốt.</t>
+          <t>Khám phá Con Đường Tơ Lụa Tà Pạ - Di tích lịch sử văn hóa độc đáo ở An Giang</t>
         </is>
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>Khám Phá Hồ Soài Chék – Điểm Hẹn Thơ Mộng Dưới Chân Dãy Phụng Hoàng Sơn  Nằm khép mình bên sườn phía Bắc ngọn Núi Cô Tô, Hồ Soài Chék (thuộc ấp Tô Hạ, xã Núi Tô, huyện Tri Tôn, An Giang) là một trong những hồ chứa nước ngọt nhân tạo lớn và ấn tượng của vùng Thất Sơn. Với sự hòa quyện giữa mặt nước trong xanh phẳng lặng, núi non trùng điệp và không gian văn hóa Khmer đặc sắc kề bên, nơi đây trở thành tọa độ dã ngoại và check-in ưa thích của du khách.  1. Vị Trí &amp; Cảnh Quan • Đặc SắcTọa độ tự nhiên tuyệt đẹp: Hồ nằm ngay dưới chân dãy Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ. Một bên hồ tựa vào vách núi, một bên mở ra tầm nhìn hướng về cánh đồng lúa bạt ngàn và những rặng thốt nốt vươn cao. • Cung đường ven hồ nên thơ: Con đường nhỏ chạy dọc theo bờ hồ có góc nhìn • đắt giá: một bên là mặt nước mênh mông in bóng mây trời, phía trước là đỉnh núi Cô Tô sừng sững, bên còn lại là thảm lúa xanh mát hoặc vàng ươm theo mùa. • Đồi cát &amp; Bãi cỏ ven hồ: Quanh hồ có các khoảng đồi thoai thoải và bãi cát tự nhiên phẳng phiu, tạo nên không gian mở lộng gió, thích hợp cho việc dựng lều cắm trại, dã ngoại hoặc chụp ảnh theo phong cách hoang sơ, tự nhiên.  2. Điểm Nhấn Văn Hóa &amp; Lễ Hội Kế CậnHồ Soài Chék không chỉ là thắng cảnh thiên nhiên mà còn nằm liền kề cụm công trình văn hóa – thể thao lớn của huyện • Tri Tôn: Sân • đua bò Bảy Núi: Tọa lạc ngay phía trước khu vực hồ với quy mô khoảng 5,5 ha. Đây chính là nơi diễn ra Lễ hội Đua bò Bảy Núi truyền thống vào dịp lễ Sen Dolta (khoảng cuối tháng 8 – đầu tháng 9 Âm lịch), thu hút hàng vạn du khách và đồng bào trong vùng về tham dự.Công viên văn hóa &amp; • Nhà truyền thống Soài Chék: Khuôn viên rộng hơn 6.000 m² được bài trí các tiểu cảnh mang đậm bản sắc Nam Bộ và văn hóa Khmer (tượng đôi bò đua, giếng cổ, cụm cây trâm, thốt nốt...), cùng nhà trưng bày nông cụ truyền thống và không gian diễn xướng nhạc ngũ âm, múa Dì kê.  3. Trải Nghiệm Thú Vị &amp; • Thời Điểm Lý TưởngSăn ảnh hoàng hôn: Vào buổi chiều tà (khoảng 16h30 – 17h45), mặt trời lặn sau rặng núi Cô Tô phản chiếu ánh ráng đỏ rực rỡ lên mặt gương hồ, tạo nên khung cảnh lãng mạn và yên ả. • Thưởng thức cà phê ngắm đồng: Gần hồ có các quán cà phê ngắm cảnh đồng ruộng thoáng mát, là nơi dừng chân nghỉ ngơi lý tưởng sau chuyến dạo quanh bờ hồ. • Thời gian trong năm: Mùa nước nổi &amp; mùa gặt (Tháng 9 – • Tháng 11): Mực nước hồ dâng cao trong xanh, hòa cùng sắc vàng rực của đồng lúa chín bao quanh. • Mùa khô (Tháng 12 – Tháng 4 năm sau): Thời tiết tạnh ráo, nắng ấm, rất thuận tiện cho các hoạt động cắm trại, dã ngoại ngoài trời.  4. Gợi Ý Lịch Trình Kết HợpTừ Hồ Soài Chék, bạn có thể dễ dàng kết nối tham quan theo cung • đường: Hồ Soài Chék \longrightarrow "Con đường tơ lụa" \&amp; Cánh đồng Tà Pạ \longrightarrow Hồ Tà Pạ / Chùa Tà Pạ \longrightarrow Vườn cây trâm cổ thụ5. • Lưu Ý Dành Cho Du Khách • An toàn: Nước hồ sâu và lạnh, không nên tự ý bơi lội hoặc leo trèo ra các mỏm đá chênh vênh ven hồ. • Bảo vệ môi trường: Khu vực hồ còn giữ nét hoang sơ, du khách khi tổ chức picnic hoặc cắm trại cần dọn dẹp sạch sẽ toàn bộ rác thải trước khi rời đi để bảo tồn cảnh quan tự nhiên.</t>
+          <t>Con Đường Tơ Lụa Tà Pạ – Dải Lụa Nghìn Màu Uốn Lượn Giữa Cánh Đồng Thất Sơn  Được mệnh danh là một trong những cung đường đồng quê đẹp và lãng mạn nhất miền Tây Nam Bộ, Con Đường Tơ Lụa Tà Pạ là dải đường bê tông nhỏ uốn lượn mềm mại tựa như một dải lụa mềm xẻ dọc qua cánh đồng lúa Tà Pạ và Hồ Soài Chek thuộc Xã Núi Tô. Cung đường này đã trở thành nguồn cảm hứng bất tận cho các nhiếp ảnh gia, giới trẻ mê xê dịch và những ai trót say đắm vẻ đẹp mộc mạc, thanh bình của vùng đất Bảy Núi.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Con Đường Tơ Lụa" • Vị trí hành chính: Nằm tại cánh đồng Tà Pạ, kết nối giữa khu vực Hồ Soài Chek và chân Đồi Tà Pạ, Xã Núi Tô, tỉnh An Giang. • Sự tích tên gọi: Từ trên đỉnh Núi Tô hoặc chùa Tà Pạ nhìn xuống, con đường bê tông trắng uốn lượn nhiều khúc quanh co mềm mại, uốn quanh các bờ ruộng ô vuông bàn cờ như một dải lụa tơ tằm mềm mại vắt ngang qua bức tranh đồng lúa bạt ngàn. Du khách và các nhiếp ảnh gia đã ưu ái gọi tên cung đường này là "Con Đường Tơ Lụa Tri Tôn". • Hạ tầng hoàn thiện: Trước đây là đường đất bờ ruộng nhỏ hẹp, nay đã được chính quyền và bà con địa phương bê tông hóa phẳng phiu, giúp xe máy và xe đạp có thể di chuyển êm ái xuyên suốt cung đường.  2. Bức Họa Thiên Nhiên Rực Rỡ Bốn Mùa • Vũ điệu sắc màu theo mùa lúa:  • Mùa nước đổ &amp; Mạ non (Tháng 3, Tháng 7): Cả cánh đồng ngập tràn sắc xanh mướt mát mắt, mặt nước ruộng lúa phản chiếu mây trời lồng lộng. • Mùa lúa chín vàng (Tháng 4, Tháng 8, Tháng 11–12): Cung đường như chìm đắm giữa biển vàng óng ả, hương thơm ngọt ngào của lúa mới phảng phất khắp không gian. • Hàng cây thốt nốt &amp; Cây trâm cổ thụ: Dọc theo hai bên đ.  ường là những rặng cây thốt nốt vươn cao kiêu hãnh và những gốc trâm cổ thụ trăm năm tuổi tỏa bóng mát râm ran, tạo nên khung cảnh làng quê Khmer bình yên đến nao lòng. • Hậu cảnh núi non kỳ vĩ: Phía xa xa là bóng dáng hùng vĩ của Núi Tô và Núi Cấm che chắn, điểm xuyết những mái chùa Khmer chóp nhọn vàng rực ẩn hiện sau rặng cây.  3. Nhịp Sống Đồng Quê &amp; Nét Đẹp Đời Thường • Hình ảnh người nông dân Khmer trên đồng: Du khách sẽ dễ dàng bắt gặp hình ảnh những người nông dân Khmer đội nón lá cần mẫn gặt lúa, những đàn bò thong dong gặm cỏ trên bờ ruộng và các em nhỏ vui đùa thả diều mỗi buổi chiều tà. • Không gian tĩnh lặng, trong lành: Tách biệt hoàn toàn khỏi khói bụi và tiếng ồn của đô thị, nơi đây chỉ có tiếng gió lướt qua ngọn lúa xào xạc và tiếng chim hót rộn rã đầu cành.  4. Hướng Dẫn Check-in &amp; Khung Giờ Sống Ảo Triệu View • Săn bình minh rạng rỡ (06:00 – 07:30): Khi ánh mặt trời vừa ló rạng sau rặng núi, sương sớm còn đọng long lanh trên từng nhánh lúa, tạo nên một không gian mờ ảo, lung linh như cõi tiên. • Đón hoàng hôn ấm áp (16:30 – 17:45): Ánh nắng chiều tà nhuộm vàng rực rỡ cả cung đường, bóng những hàng cây thốt nốt đổ dài trên mặt ruộng là khoảnh khắc vàng để chụp ảnh ngược sáng (silhouette). • Góc chụp lý tưởng: Chụp từ góc thấp hướng dọc theo đường cong uốn lượn của cung đường; chụp cùng tà áo dài hoặc trang phục truyền thống Khmer; chụp toàn cảnh từ flycam trên cao.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Tôn trọng nông dân: Tuyệt đối không dẫm đạp lên lúa của bà con, không bẻ nhánh hay hái quả thốt nốt non của các hộ dân ven đường. • An toàn giao thông: Đường nhỏ vừa cho 2 xe máy tránh nhau, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào sát lề đường để không cản trở lối đi của bà con nông dân. • Chi phí: Hoàn toàn miễn phí tham quan và chụp ảnh tự do.</t>
         </is>
       </c>
       <c r="O109" s="4" t="inlineStr"/>
       <c r="P109" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.9924</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4185,105.0095</t>
         </is>
       </c>
     </row>
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>ho-ta-pa</t>
+          <t>ho-soai-chek</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Hồ Tà Pạ (Tuyệt Tình Cốc Bảy Núi)</t>
+          <t>Hồ Soài Chek</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr"/>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>10.4165, 105.0042</t>
+          <t>10.4285, 104.9924</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Xã Ba Chúc, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr"/>
@@ -7484,18 +7484,18 @@
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>Hồ nước ngọt trong xanh như ngọc bích trên đỉnh đồi Tà Pạ, xã Núi Tô, được mệnh danh là Tuyệt tình cốc Bảy Núi.</t>
+          <t>Hồ thủy lợi thơ mộng dưới chân đồi Tà Pạ, xã Núi Tô. Không gian tĩnh lặng, thoáng đãng, là điểm cắm trại ngắm hoàng hôn buông trên đồi cát và rặng thốt nốt.</t>
         </is>
       </c>
       <c r="N110" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Hồ Đá Đồi Tà Pạ – "Tuyệt Tình Cốc" của An Giang  1. Vị trí và Nguồn gốc: • Địa chỉ: Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang (nằm cạnh cánh đồng lúa Tà Pạ). • Nguồn gốc: Hồ là tuyệt tác hình thành từ quá trình khai thác đá trước đây. Với độ sâu khoảng 17 mét, hồ chứa mạch nước ngầm tự nhiên trong vắt nhìn thấu tận đáy. • Cảnh quan: Lọt thỏm giữa những vách đá granite sừng sững, hồ đổi màu nước huyền ảo theo góc chiếu ánh nắng (từ xanh lam, ngọc bích đến vàng cam).  2. Hướng dẫn di chuyển &amp; Thời điểm đẹp nhất: • Cách đi: Từ chợ Tri Tôn theo đường Nguyễn Trãi lên chân đồi Tà Pạ ➔ Chạy theo đường bê tông dốc thoai thoải 1.2km lên đỉnh đồi. Xe máy và ô tô dưới 16 chỗ lên tận nơi. • Thời điểm check-in: 06:00 – 08:30 sáng đón nắng sớm hoặc 16:00 – 17:30 chiều ngắm hoàng hôn buông xuống thung lũng lúa.</t>
+          <t>Khám Phá Hồ Soài Chék – Điểm Hẹn Thơ Mộng Dưới Chân Dãy Phụng Hoàng Sơn  Nằm khép mình bên sườn phía Bắc ngọn Núi Cô Tô, Hồ Soài Chék (thuộc ấp Tô Hạ, xã Núi Tô, huyện Tri Tôn, An Giang) là một trong những hồ chứa nước ngọt nhân tạo lớn và ấn tượng của vùng Thất Sơn. Với sự hòa quyện giữa mặt nước trong xanh phẳng lặng, núi non trùng điệp và không gian văn hóa Khmer đặc sắc kề bên, nơi đây trở thành tọa độ dã ngoại và check-in ưa thích của du khách.  1. Vị Trí &amp; Cảnh Quan • Đặc SắcTọa độ tự nhiên tuyệt đẹp: Hồ nằm ngay dưới chân dãy Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ. Một bên hồ tựa vào vách núi, một bên mở ra tầm nhìn hướng về cánh đồng lúa bạt ngàn và những rặng thốt nốt vươn cao. • Cung đường ven hồ nên thơ: Con đường nhỏ chạy dọc theo bờ hồ có góc nhìn • đắt giá: một bên là mặt nước mênh mông in bóng mây trời, phía trước là đỉnh núi Cô Tô sừng sững, bên còn lại là thảm lúa xanh mát hoặc vàng ươm theo mùa. • Đồi cát &amp; Bãi cỏ ven hồ: Quanh hồ có các khoảng đồi thoai thoải và bãi cát tự nhiên phẳng phiu, tạo nên không gian mở lộng gió, thích hợp cho việc dựng lều cắm trại, dã ngoại hoặc chụp ảnh theo phong cách hoang sơ, tự nhiên.  2. Điểm Nhấn Văn Hóa &amp; Lễ Hội Kế CậnHồ Soài Chék không chỉ là thắng cảnh thiên nhiên mà còn nằm liền kề cụm công trình văn hóa – thể thao lớn của huyện • Tri Tôn: Sân • đua bò Bảy Núi: Tọa lạc ngay phía trước khu vực hồ với quy mô khoảng 5,5 ha. Đây chính là nơi diễn ra Lễ hội Đua bò Bảy Núi truyền thống vào dịp lễ Sen Dolta (khoảng cuối tháng 8 – đầu tháng 9 Âm lịch), thu hút hàng vạn du khách và đồng bào trong vùng về tham dự.Công viên văn hóa &amp; • Nhà truyền thống Soài Chék: Khuôn viên rộng hơn 6.000 m² được bài trí các tiểu cảnh mang đậm bản sắc Nam Bộ và văn hóa Khmer (tượng đôi bò đua, giếng cổ, cụm cây trâm, thốt nốt...), cùng nhà trưng bày nông cụ truyền thống và không gian diễn xướng nhạc ngũ âm, múa Dì kê.  3. Trải Nghiệm Thú Vị &amp; • Thời Điểm Lý TưởngSăn ảnh hoàng hôn: Vào buổi chiều tà (khoảng 16h30 – 17h45), mặt trời lặn sau rặng núi Cô Tô phản chiếu ánh ráng đỏ rực rỡ lên mặt gương hồ, tạo nên khung cảnh lãng mạn và yên ả. • Thưởng thức cà phê ngắm đồng: Gần hồ có các quán cà phê ngắm cảnh đồng ruộng thoáng mát, là nơi dừng chân nghỉ ngơi lý tưởng sau chuyến dạo quanh bờ hồ. • Thời gian trong năm: Mùa nước nổi &amp; mùa gặt (Tháng 9 – • Tháng 11): Mực nước hồ dâng cao trong xanh, hòa cùng sắc vàng rực của đồng lúa chín bao quanh. • Mùa khô (Tháng 12 – Tháng 4 năm sau): Thời tiết tạnh ráo, nắng ấm, rất thuận tiện cho các hoạt động cắm trại, dã ngoại ngoài trời.  4. Gợi Ý Lịch Trình Kết HợpTừ Hồ Soài Chék, bạn có thể dễ dàng kết nối tham quan theo cung • đường: Hồ Soài Chék \longrightarrow "Con đường tơ lụa" \&amp; Cánh đồng Tà Pạ \longrightarrow Hồ Tà Pạ / Chùa Tà Pạ \longrightarrow Vườn cây trâm cổ thụ5. • Lưu Ý Dành Cho Du Khách • An toàn: Nước hồ sâu và lạnh, không nên tự ý bơi lội hoặc leo trèo ra các mỏm đá chênh vênh ven hồ. • Bảo vệ môi trường: Khu vực hồ còn giữ nét hoang sơ, du khách khi tổ chức picnic hoặc cắm trại cần dọn dẹp sạch sẽ toàn bộ rác thải trước khi rời đi để bảo tồn cảnh quan tự nhiên.</t>
         </is>
       </c>
       <c r="O110" s="7" t="inlineStr"/>
       <c r="P110" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4165,105.0042</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.9924</t>
         </is>
       </c>
     </row>
@@ -7505,12 +7505,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>nui-ta-pa</t>
+          <t>ho-ta-pa</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Núi Tà Pạ</t>
+          <t>Hồ Tà Pạ (Tuyệt Tình Cốc Bảy Núi)</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr"/>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>10.4072869, 104.9747836</t>
+          <t>10.4165, 105.0042</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Núi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr"/>
@@ -7550,18 +7550,18 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>Khám phá vẻ đẹp yên bình của Núi Tà Pạ và trải nghiệm nét văn hóa độc đáo tại vùng đất Bảy Núi</t>
+          <t>Hồ nước ngọt trong xanh như ngọc bích trên đỉnh đồi Tà Pạ, xã Núi Tô, được mệnh danh là Tuyệt tình cốc Bảy Núi.</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>Núi • Tà Pạ: Trái tim của dãy Thất Sơn  Vùng đất Tri Tôn, nằm trong dãy Thất Sơn hùng vĩ, là nơi kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer. Núi Tà Pạ là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại đây.  Cảnh sắc yên bình và lòng hiếu khách  Khi đến đây, du khách có thể khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Du khách cũng có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Hồ • Tà Pạ: Tuyệt tình cốc của miền Tây  Theo đánh giá của du khách, hồ Tà Pạ tại Tri Tôn, An Giang được mệnh danh là "Tuyệt tình cốc" của miền Tây. Nước hồ rất trong, tạo nên một kiệt tác thiên nhiên đầy mê hoặc. Ngoài ra, cánh đồng Tà Pạ nằm dưới chân núi Tà Pạ và Cô Tô, cách thị trấn Tri Tôn khoảng 1km, cũng là một thắng cảnh tuyệt đẹp đáng tự hào của An Giang. Cánh đồng này là một bức tranh tuyệt đẹp khi có một cánh đồng xanh bát ngáy xen lẫn giữ những lùm cây, đường đi khá uốn lượn nên là đi tốc độ chậm chút.  Tuyệt vời khi có thể khám phá vẻ đẹp yên bình và văn hóa độc đáo của Núi Tà Pạ và vùng đất Bảy Núi!</t>
+          <t>Khám phá Hồ Đá Đồi Tà Pạ – "Tuyệt Tình Cốc" của An Giang  1. Vị trí và Nguồn gốc: • Địa chỉ: Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang (nằm cạnh cánh đồng lúa Tà Pạ). • Nguồn gốc: Hồ là tuyệt tác hình thành từ quá trình khai thác đá trước đây. Với độ sâu khoảng 17 mét, hồ chứa mạch nước ngầm tự nhiên trong vắt nhìn thấu tận đáy. • Cảnh quan: Lọt thỏm giữa những vách đá granite sừng sững, hồ đổi màu nước huyền ảo theo góc chiếu ánh nắng (từ xanh lam, ngọc bích đến vàng cam).  2. Hướng dẫn di chuyển &amp; Thời điểm đẹp nhất: • Cách đi: Từ chợ Tri Tôn theo đường Nguyễn Trãi lên chân đồi Tà Pạ ➔ Chạy theo đường bê tông dốc thoai thoải 1.2km lên đỉnh đồi. Xe máy và ô tô dưới 16 chỗ lên tận nơi. • Thời điểm check-in: 06:00 – 08:30 sáng đón nắng sớm hoặc 16:00 – 17:30 chiều ngắm hoàng hôn buông xuống thung lũng lúa.</t>
         </is>
       </c>
       <c r="O111" s="4" t="inlineStr"/>
       <c r="P111" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4072869,104.9747836</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4165,105.0042</t>
         </is>
       </c>
     </row>
@@ -7571,12 +7571,12 @@
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>san-dua-bo-ta-pa-soai-chek</t>
+          <t>nui-ta-pa</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Sân Đua Bò Thể Thao Tà Pạ - Soài Chek (Nơi Thi Đấu Chính Thức)</t>
+          <t>Núi Tà Pạ</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr"/>
@@ -7585,18 +7585,22 @@
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F112" s="7" t="n"/>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
       <c r="G112" s="6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H112" s="6" t="inlineStr">
         <is>
-          <t>10.4215, 105.0085</t>
+          <t>10.4072869, 104.9747836</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>Khu Thể Thao Tà Pạ - Soài Chek, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Núi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr"/>
@@ -7612,18 +7616,18 @@
       </c>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>Sân đua bò trung tâm quy mô lớn thuộc Khu Thể thao - Du lịch Tà Pạ - Soài Chek (Xã Núi Tô), nơi diễn ra Hội Đua Bò Bảy Núi tranh Cúp Truyền hình An Giang chính thức hàng năm với hàng vạn khán giả.</t>
+          <t>Khám phá vẻ đẹp yên bình của Núi Tà Pạ và trải nghiệm nét văn hóa độc đáo tại vùng đất Bảy Núi</t>
         </is>
       </c>
       <c r="N112" s="7" t="inlineStr">
         <is>
-          <t>Để đáp ứng quy mô lễ hội ngày càng lớn mạnh (Di sản văn hóa phi vật thể Quốc gia), huyện Tri Tôn và tỉnh An Giang đã đầu tư sân đua bò chuyên dụng tại chân đồi Tà Pạ - Hồ Soài Chek với khán đài, bờ bao an toàn và đường đua bùn lầy đạt chuẩn 120m (gồm 1 vòng hô và 1 vòng thả về đích kịch tính).</t>
+          <t>Núi • Tà Pạ: Trái tim của dãy Thất Sơn  Vùng đất Tri Tôn, nằm trong dãy Thất Sơn hùng vĩ, là nơi kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer. Núi Tà Pạ là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại đây.  Cảnh sắc yên bình và lòng hiếu khách  Khi đến đây, du khách có thể khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Du khách cũng có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Hồ • Tà Pạ: Tuyệt tình cốc của miền Tây  Theo đánh giá của du khách, hồ Tà Pạ tại Tri Tôn, An Giang được mệnh danh là "Tuyệt tình cốc" của miền Tây. Nước hồ rất trong, tạo nên một kiệt tác thiên nhiên đầy mê hoặc. Ngoài ra, cánh đồng Tà Pạ nằm dưới chân núi Tà Pạ và Cô Tô, cách thị trấn Tri Tôn khoảng 1km, cũng là một thắng cảnh tuyệt đẹp đáng tự hào của An Giang. Cánh đồng này là một bức tranh tuyệt đẹp khi có một cánh đồng xanh bát ngáy xen lẫn giữ những lùm cây, đường đi khá uốn lượn nên là đi tốc độ chậm chút.  Tuyệt vời khi có thể khám phá vẻ đẹp yên bình và văn hóa độc đáo của Núi Tà Pạ và vùng đất Bảy Núi!</t>
         </is>
       </c>
       <c r="O112" s="7" t="inlineStr"/>
       <c r="P112" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4215,105.0085</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4072869,104.9747836</t>
         </is>
       </c>
     </row>
@@ -7633,12 +7637,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>30ac578e-vườn-mãng-cầu-núi-tô</t>
+          <t>san-dua-bo-ta-pa-soai-chek</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Vườn Mãng Cầu Ta Núi Tô</t>
+          <t>Sân Đua Bò Thể Thao Tà Pạ - Soài Chek (Nơi Thi Đấu Chính Thức)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr"/>
@@ -7647,22 +7651,18 @@
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Nông trại</t>
-        </is>
-      </c>
+      <c r="F113" s="4" t="n"/>
       <c r="G113" s="3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>10.408, 105.021</t>
+          <t>10.4215, 105.0085</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>Vườn mãng cầu sườn Núi Tô, Ấp Tô Thuận, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Khu Thể Thao Tà Pạ - Soài Chek, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr"/>
@@ -7678,18 +7678,18 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>Nhà vườn sinh thái chuyên trồng giống mãng cầu ta (na Bảy Núi) thơm ngọt, trái to vỏ mỏng trên sườn đá bazan chân đồi Tà Pạ, xã Núi Tô.</t>
+          <t>Sân đua bò trung tâm quy mô lớn thuộc Khu Thể thao - Du lịch Tà Pạ - Soài Chek (Xã Núi Tô), nơi diễn ra Hội Đua Bò Bảy Núi tranh Cúp Truyền hình An Giang chính thức hàng năm với hàng vạn khán giả.</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>Vườn Mãng Cầu Triền Đá Núi Tô – Trải Nghiệm Miệt Vườn Cây Ăn Trái Độc Đáo Bám Rễ Đá Granit  Trải dài trên các triền dốc đá thoai thoải của Núi Tô (Phụng Hoàng Sơn) thuộc Xã Núi Tô, Vườn Mãng Cầu Triền Đá là một điểm đến trải nghiệm nông nghiệp sinh thái đặc sắc mang đậm dấu ấn thích nghi kỳ diệu của người dân Bảy Núi. Từng gốc mãng cầu bám rễ sâu vào các kẽ đá hoa cương, chắt chiu dòng khoáng chất tinh khiết của đất núi để cho ra đời những trái mãng cầu dai ngọt lịm, vỏ mỏng, thịt chắc thơm nồng nàn không nơi nào sánh bằng.  1. Vị Trí &amp; Nghề Trồng Cây Ăn Trái Trên Đá • Vị trí hành chính: Triền dốc Núi Tô, Xã Núi Tô, tỉnh An Giang. • Thổ nhưỡng đá granite đặc thù: Núi Tô có cấu tạo địa chất chủ yếu là đá hoa cương xám. Người dân địa phương qua nhiều thế hệ đã cần mẫn đục đá, be đất trên sườn dốc để trồng mãng cầu ta (mãng cầu dai) và các loại cây ăn trái như xoài bưởi, bơ núi. • Hương vị đặc hữu: Nhờ sinh trưởng trên nền đất đá thoát nước tốt và hấp thụ khoáng chất tự nhiên từ đá granit, quả mãng cầu Núi Tô có mắt nở to đều, vỏ mỏng, cùi dày ít hạt, vị ngọt đậm đà và có mùi thơm thoang thoảng của hương rừng Bảy Núi.  2. Trải Nghiệm Khám Phá Miệt Vườn Triền Dốc • Dạo bước dưới tán vườn xanh mát: Du khách sẽ được leo men theo các lối mòn lát đá uốn lượn qua từng tầng vườn mãng cầu xanh mướt, tận mắt chiêm ngưỡng những quả mãng cầu trĩu nặng lúc lỉu bám sát vào thân cây. • Tự tay thu hoạch trái chín tại vườn: Được chủ vườn hướng dẫn cách chọn những quả mãng cầu đã "mở mắt" chín tới, tự tay cắt cuống quả và thưởng thức vị ngọt thơm mát lành ngay dưới bóng cây. • Trò chuyện cùng nông dân bản địa: Nghe bà con người Kinh và Khmer chia sẻ về kỹ thuật thụ phấn hoa mãng cầu thủ công bằng tay từ tờ mờ sáng và cách giữ gìn nguồn nước tưới trên vách núi đá khô cằn.  3. Mùa Vụ Thu Hoạch &amp; Mua Làm Quà • Mùa thu hoạch rộ: Mãng cầu Núi Tô cho trái ngon nhất từ tháng 6 đến tháng 9 hàng năm (mùa mưa) và một vụ rải rác phục vụ dịp Tết Nguyên Đán. • Thức quà quý Bảy Núi: Mãng cầu ta Núi Tô được đóng thùng cẩn thận là món quà biếu ý nghĩa, mang đậm phong vị thiên nhiên trù phú của vùng đất An Giang cho người thân và bạn bè.  4. Hướng Dẫn Khung Giờ &amp; Check-in • Khung giờ lý tưởng: 07:30 – 10:00 sáng hoặc 15:00 – 17:00 chiều để tránh nắng gắt khi leo triền dốc. • Góc chụp sống ảo: Đứng giữa các tầng cây mãng cầu trĩu quả với hậu cảnh là những tảng đá granite khổng lồ và toàn cảnh cánh đồng Tà Pạ thấp thoáng bên dưới.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Trang phục: Đường vườn dốc đá thoai thoải, du khách nên đi giày thể thao có độ ma sát cao để tránh trơn trượt. • Mua trái cây tại vườn: Giá mãng cầu mua trực tiếp tại vườn dao động từ 35.000đ – 60.000đ/kg tùy loại và thời điểm mùa vụ.</t>
+          <t>Để đáp ứng quy mô lễ hội ngày càng lớn mạnh (Di sản văn hóa phi vật thể Quốc gia), huyện Tri Tôn và tỉnh An Giang đã đầu tư sân đua bò chuyên dụng tại chân đồi Tà Pạ - Hồ Soài Chek với khán đài, bờ bao an toàn và đường đua bùn lầy đạt chuẩn 120m (gồm 1 vòng hô và 1 vòng thả về đích kịch tính).</t>
         </is>
       </c>
       <c r="O113" s="4" t="inlineStr"/>
       <c r="P113" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.408,105.021</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4215,105.0085</t>
         </is>
       </c>
     </row>
@@ -7699,36 +7699,36 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>dinh-than-cau-dai</t>
+          <t>30ac578e-vườn-mãng-cầu-núi-tô</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Đình Thần Cầu Dài (Xã Vĩnh Gia)</t>
+          <t>Vườn Mãng Cầu Ta Núi Tô</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Xã Vĩnh Gia</t>
+          <t>Xã Núi Tô</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>worship</t>
+          <t>Nông trại</t>
         </is>
       </c>
       <c r="G114" s="6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>10.495, 104.92</t>
+          <t>10.408, 105.021</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>Tỉnh lộ ĐT955A (gần Cầu Dài), Xã Vĩnh Gia, Tri Tôn, An Giang</t>
+          <t>Vườn mãng cầu sườn Núi Tô, Ấp Tô Thuận, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J114" s="7" t="inlineStr"/>
@@ -7744,18 +7744,18 @@
       </c>
       <c r="M114" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Đình thần Cầu Dài - điểm hẹn văn hóa tâm linh giữa lòng Bảy Núi hùng vĩ.</t>
+          <t>Nhà vườn sinh thái chuyên trồng giống mãng cầu ta (na Bảy Núi) thơm ngọt, trái to vỏ mỏng trên sườn đá bazan chân đồi Tà Pạ, xã Núi Tô.</t>
         </is>
       </c>
       <c r="N114" s="7" t="inlineStr">
         <is>
-          <t>Đình Thần Cầu Dài – Nét đẹp văn hóa tâm linh vùng biên giới  1. Nét văn hóa truyền thống: • Đình thần Cầu Dài là nơi thờ cúng các bậc tiền hiền có công khai hoang lập ấp vùng đất biên thùy Tây Nam. • Hằng năm vào dịp lễ hội Kỳ Yên 15/2 âm lịch, bà con tổ chức cúng tế trang nghiêm thu hút đông đảo phật tử và du khách thập phương.</t>
+          <t>Vườn Mãng Cầu Triền Đá Núi Tô – Trải Nghiệm Miệt Vườn Cây Ăn Trái Độc Đáo Bám Rễ Đá Granit  Trải dài trên các triền dốc đá thoai thoải của Núi Tô (Phụng Hoàng Sơn) thuộc Xã Núi Tô, Vườn Mãng Cầu Triền Đá là một điểm đến trải nghiệm nông nghiệp sinh thái đặc sắc mang đậm dấu ấn thích nghi kỳ diệu của người dân Bảy Núi. Từng gốc mãng cầu bám rễ sâu vào các kẽ đá hoa cương, chắt chiu dòng khoáng chất tinh khiết của đất núi để cho ra đời những trái mãng cầu dai ngọt lịm, vỏ mỏng, thịt chắc thơm nồng nàn không nơi nào sánh bằng.  1. Vị Trí &amp; Nghề Trồng Cây Ăn Trái Trên Đá • Vị trí hành chính: Triền dốc Núi Tô, Xã Núi Tô, tỉnh An Giang. • Thổ nhưỡng đá granite đặc thù: Núi Tô có cấu tạo địa chất chủ yếu là đá hoa cương xám. Người dân địa phương qua nhiều thế hệ đã cần mẫn đục đá, be đất trên sườn dốc để trồng mãng cầu ta (mãng cầu dai) và các loại cây ăn trái như xoài bưởi, bơ núi. • Hương vị đặc hữu: Nhờ sinh trưởng trên nền đất đá thoát nước tốt và hấp thụ khoáng chất tự nhiên từ đá granit, quả mãng cầu Núi Tô có mắt nở to đều, vỏ mỏng, cùi dày ít hạt, vị ngọt đậm đà và có mùi thơm thoang thoảng của hương rừng Bảy Núi.  2. Trải Nghiệm Khám Phá Miệt Vườn Triền Dốc • Dạo bước dưới tán vườn xanh mát: Du khách sẽ được leo men theo các lối mòn lát đá uốn lượn qua từng tầng vườn mãng cầu xanh mướt, tận mắt chiêm ngưỡng những quả mãng cầu trĩu nặng lúc lỉu bám sát vào thân cây. • Tự tay thu hoạch trái chín tại vườn: Được chủ vườn hướng dẫn cách chọn những quả mãng cầu đã "mở mắt" chín tới, tự tay cắt cuống quả và thưởng thức vị ngọt thơm mát lành ngay dưới bóng cây. • Trò chuyện cùng nông dân bản địa: Nghe bà con người Kinh và Khmer chia sẻ về kỹ thuật thụ phấn hoa mãng cầu thủ công bằng tay từ tờ mờ sáng và cách giữ gìn nguồn nước tưới trên vách núi đá khô cằn.  3. Mùa Vụ Thu Hoạch &amp; Mua Làm Quà • Mùa thu hoạch rộ: Mãng cầu Núi Tô cho trái ngon nhất từ tháng 6 đến tháng 9 hàng năm (mùa mưa) và một vụ rải rác phục vụ dịp Tết Nguyên Đán. • Thức quà quý Bảy Núi: Mãng cầu ta Núi Tô được đóng thùng cẩn thận là món quà biếu ý nghĩa, mang đậm phong vị thiên nhiên trù phú của vùng đất An Giang cho người thân và bạn bè.  4. Hướng Dẫn Khung Giờ &amp; Check-in • Khung giờ lý tưởng: 07:30 – 10:00 sáng hoặc 15:00 – 17:00 chiều để tránh nắng gắt khi leo triền dốc. • Góc chụp sống ảo: Đứng giữa các tầng cây mãng cầu trĩu quả với hậu cảnh là những tảng đá granite khổng lồ và toàn cảnh cánh đồng Tà Pạ thấp thoáng bên dưới.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Trang phục: Đường vườn dốc đá thoai thoải, du khách nên đi giày thể thao có độ ma sát cao để tránh trơn trượt. • Mua trái cây tại vườn: Giá mãng cầu mua trực tiếp tại vườn dao động từ 35.000đ – 60.000đ/kg tùy loại và thời điểm mùa vụ.</t>
         </is>
       </c>
       <c r="O114" s="7" t="inlineStr"/>
       <c r="P114" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.495,104.92</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.408,105.021</t>
         </is>
       </c>
     </row>
@@ -7765,23 +7765,23 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>ho-o-thum</t>
+          <t>dinh-than-cau-dai</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Hồ Ô Thum</t>
+          <t>Đình Thần Cầu Dài (Xã Vĩnh Gia)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm</t>
+          <t>Xã Vĩnh Gia</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Hồ nước nhân tạo</t>
+          <t>worship</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>10.3765, 104.9875</t>
+          <t>10.495, 104.92</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm, huyện Tri Tôn, An Giang</t>
+          <t>Tỉnh lộ ĐT955A (gần Cầu Dài), Xã Vĩnh Gia, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr"/>
@@ -7810,18 +7810,18 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>Hồ Ô Thum là hồ nước ngọt nhân tạo dưới chân đồi Bảy Núi, thủ phủ ẩm thực Gà Đốt trứ danh tại Xã Ô Lâm, Tri Tôn.</t>
+          <t>Khám phá Đình thần Cầu Dài - điểm hẹn văn hóa tâm linh giữa lòng Bảy Núi hùng vĩ.</t>
         </is>
       </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>Quán Gà Đốt Ai Đó Ô Thum – Mỏm Đất Nhô Giữa Lòng Hồ Với View Nước 360 Độ Tuyệt Mỹ  Tọa lạc trên một mỏm đất tự nhiên nhô hẳn ra giữa lòng hồ Ô Thum tựa như một ốc đảo xanh thu nhỏ, Quán Gà Đốt Ốc Đảo mang lại trải nghiệm ẩm thực độc nhất vô nhị với tầm nhìn 360 độ ngắm trọn mặt nước xanh biếc và dãy đồi núi Ô Lâm trập trùng bao quanh.  1. Vị Trí "Ốc Đảo" Độc Nhất Vô Nhị • Vị trí hành chính: Bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Địa thế ốc đảo xanh: Quán được bao bọc ba mặt bởi làn nước hồ trong vắt, gió thổi lồng lộng quanh năm mang lại không khí mát lạnh tự nhiên không cần quạt máy.  2. Món Gà Đốt Nồi Đất Vàng Giòn • Kỹ thuật đốt gà đỉnh cao: Gà được đốt trong nồi gang đất dày trên than hồng, da gà xém vàng giòn rụm thơm nức mũi mùi lá chúc, thịt bên trong mềm ngọt mọng nước. • Phục vụ đa dạng: Ngoài gà đốt còn có các món cá lóc nướng trui, lẩu cá lăng nấu măng chua, xôi bắp thốt nốt.  3. Trải Nghiệm Ngắm Hoàng Hôn 360 Độ • Khung giờ vàng: 16:30 – 17:45 là khoảnh khắc đẹp nhất khi ánh hoàng hôn nhuộm đỏ cả mặt hồ bao quanh quán.  4. Thông Tin Đặt Chỗ • Giờ mở cửa: 08:00 – 19:00 hàng ngày. • Giá bán: 250.000đ – 320.000đ / con.</t>
+          <t>Đình Thần Cầu Dài – Nét đẹp văn hóa tâm linh vùng biên giới  1. Nét văn hóa truyền thống: • Đình thần Cầu Dài là nơi thờ cúng các bậc tiền hiền có công khai hoang lập ấp vùng đất biên thùy Tây Nam. • Hằng năm vào dịp lễ hội Kỳ Yên 15/2 âm lịch, bà con tổ chức cúng tế trang nghiêm thu hút đông đảo phật tử và du khách thập phương.</t>
         </is>
       </c>
       <c r="O115" s="4" t="inlineStr"/>
       <c r="P115" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3765,104.9875</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.495,104.92</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>lang-gom-dat-nung-o-lam</t>
+          <t>ho-o-thum</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Làng Nghề Gốm Đất Nung &amp; Bếp Cà Ràng Cổ Truyền Ô Lâm</t>
+          <t>Hồ Ô Thum</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr"/>
@@ -7845,18 +7845,22 @@
           <t>Xã Ô Lâm</t>
         </is>
       </c>
-      <c r="F116" s="7" t="n"/>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>Hồ nước nhân tạo</t>
+        </is>
+      </c>
       <c r="G116" s="6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
         <is>
-          <t>10.375, 104.992</t>
+          <t>10.3765, 104.9875</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>Xã Ô Lâm, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr"/>
@@ -7872,2070 +7876,2132 @@
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>Làng gốm thủ công mộc mạc của người Khmer chuyên chế tác bếp cà-ràng, nồi đất đun củi và niêu đất nướng gà đốt trứ danh bên sườn núi Cô Tô.</t>
+          <t>Hồ Ô Thum là hồ nước ngọt nhân tạo dưới chân đồi Bảy Núi, thủ phủ ẩm thực Gà Đốt trứ danh tại Xã Ô Lâm, Tri Tôn.</t>
         </is>
       </c>
       <c r="N116" s="7" t="inlineStr">
         <is>
-          <t>Sử dụng đất sét mịn đặc trưng lấy từ lòng đất Bảy Núi, các nghệ nhân Khmer nhào nặn hoàn toàn bằng tay không dùng bàn xoay, sau đó nung lộ thiên bằng rơm rạ. Chiếc bếp cà-ràng hình số 3 nổi tiếng là vật dụng gắn liền với đời sống sông nước và ẩm thực Bảy Núi hàng trăm năm qua.</t>
+          <t>Quán Gà Đốt Ai Đó Ô Thum – Mỏm Đất Nhô Giữa Lòng Hồ Với View Nước 360 Độ Tuyệt Mỹ  Tọa lạc trên một mỏm đất tự nhiên nhô hẳn ra giữa lòng hồ Ô Thum tựa như một ốc đảo xanh thu nhỏ, Quán Gà Đốt Ốc Đảo mang lại trải nghiệm ẩm thực độc nhất vô nhị với tầm nhìn 360 độ ngắm trọn mặt nước xanh biếc và dãy đồi núi Ô Lâm trập trùng bao quanh.  1. Vị Trí "Ốc Đảo" Độc Nhất Vô Nhị • Vị trí hành chính: Bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Địa thế ốc đảo xanh: Quán được bao bọc ba mặt bởi làn nước hồ trong vắt, gió thổi lồng lộng quanh năm mang lại không khí mát lạnh tự nhiên không cần quạt máy.  2. Món Gà Đốt Nồi Đất Vàng Giòn • Kỹ thuật đốt gà đỉnh cao: Gà được đốt trong nồi gang đất dày trên than hồng, da gà xém vàng giòn rụm thơm nức mũi mùi lá chúc, thịt bên trong mềm ngọt mọng nước. • Phục vụ đa dạng: Ngoài gà đốt còn có các món cá lóc nướng trui, lẩu cá lăng nấu măng chua, xôi bắp thốt nốt.  3. Trải Nghiệm Ngắm Hoàng Hôn 360 Độ • Khung giờ vàng: 16:30 – 17:45 là khoảnh khắc đẹp nhất khi ánh hoàng hôn nhuộm đỏ cả mặt hồ bao quanh quán.  4. Thông Tin Đặt Chỗ • Giờ mở cửa: 08:00 – 19:00 hàng ngày. • Giá bán: 250.000đ – 320.000đ / con.</t>
         </is>
       </c>
       <c r="O116" s="7" t="inlineStr"/>
       <c r="P116" s="8" t="inlineStr">
         <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3765,104.9875</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>lang-gom-dat-nung-o-lam</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Làng Nghề Gốm Đất Nung &amp; Bếp Cà Ràng Cổ Truyền Ô Lâm</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr"/>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Xã Ô Lâm</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>10.375, 104.992</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>Xã Ô Lâm, Tri Tôn, An Giang</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr"/>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>Làng gốm thủ công mộc mạc của người Khmer chuyên chế tác bếp cà-ràng, nồi đất đun củi và niêu đất nướng gà đốt trứ danh bên sườn núi Cô Tô.</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>Sử dụng đất sét mịn đặc trưng lấy từ lòng đất Bảy Núi, các nghệ nhân Khmer nhào nặn hoàn toàn bằng tay không dùng bàn xoay, sau đó nung lộ thiên bằng rơm rạ. Chiếc bếp cà-ràng hình số 3 nổi tiếng là vật dụng gắn liền với đời sống sông nước và ẩm thực Bảy Núi hàng trăm năm qua.</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr"/>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.375,104.992</t>
         </is>
       </c>
     </row>
-    <row r="117"/>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
+    <row r="118"/>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>📸 IV. ĐIỂM CHECK-IN &amp; CẢNH QUAN NỔI BẬT — TỔNG SỐ: 8 ĐỊA ĐIỂM</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Mã ID</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Tên Địa Điểm</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Tên Tiếng Anh (EN)</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Xã / Thị Trấn</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Phân Loại Phụ</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Đánh Giá (⭐)</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Tọa Độ GPS (Lat, Lng)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>Địa Chỉ Thực Địa</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>Điện Thoại / Hotline</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>Mức Giá</t>
         </is>
       </c>
-      <c r="L119" s="2" t="inlineStr">
+      <c r="L120" s="2" t="inlineStr">
         <is>
           <t>Giờ Mở Cửa / Giờ Vàng</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr">
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>Mô Tả Tổng Quan</t>
         </is>
       </c>
-      <c r="N119" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
         <is>
           <t>Sự Tích &amp; Di Sản Thực Địa</t>
         </is>
       </c>
-      <c r="O119" s="2" t="inlineStr">
+      <c r="O120" s="2" t="inlineStr">
         <is>
           <t>Mẹo Thực Địa</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr">
+      <c r="P120" s="2" t="inlineStr">
         <is>
           <t>Link Google Maps Dẫn Đường</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="3" t="n">
+    <row r="121" ht="24" customHeight="1">
+      <c r="A121" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>a8b28369-cánh-đồng-lúa-ba-chú</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>Cánh Đồng Lúa Ba Chúc</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr"/>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr"/>
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Ba Chúc</t>
         </is>
       </c>
-      <c r="F120" s="4" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>Cánh đồng</t>
         </is>
       </c>
-      <c r="G120" s="3" t="n">
+      <c r="G121" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>10.493, 104.905</t>
         </is>
       </c>
-      <c r="I120" s="4" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>Cánh đồng lúa Ba Chúc, Ấp An Bình, Thị trấn Ba Chúc, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J120" s="4" t="inlineStr"/>
-      <c r="K120" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
+      <c r="J121" s="4" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M121" s="4" t="inlineStr">
         <is>
           <t>Danh từ cánh Bộ phận trong thân thể chim và một số côn trùng, dùng để bay. Chim vỗ cánh. Thẳng cánh cò bay. Bộ phận hình như cánh …</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>1. Tổng quan Cánh Đồng Lúa Ba Chúc là một địa điểm du lịch tuyệt đẹp thuộc thị trấn Ba Chúc, huyện Tri Tôn, tỉnh An Giang. Nằm ở trung tâm của đồng bằng sông Cửu Long, cánh đồng lúa này mang vẻ đẹp yên bình và thơ mộng của vùng quê Nam Bộ. Với không gian mở và tự do, du khách có thể thoải mái tận hưởng không khí trong lành và cảnh quan tuyệt đẹp của cánh đồng lúa.  2. Đánh giá từ du khách Do chưa có đánh giá từ du khách, chúng tôi không thể cung cấp thông tin cụ thể về ưu nhược điểm của Cánh Đồng Lúa Ba Chúc. Tuy nhiên, với vẻ đẹp tự nhiên và không gian mở, đây có thể là một điểm đến lý tưởng cho những ai muốn thoát khỏi đô thị ồn ào và tìm kiếm sự yên tĩnh.  3. Lời khuyên Khi đến Cánh Đồng Lúa Ba Chúc, du khách nên chuẩn bị kem chống nắng, mũ và áo chống nắng để bảo vệ bản thân khỏi ánh nắng mặt trời. Ngoài ra, nên đi giày thoải mái và mang theo nước để giữ đủ nước trong suốt chuyến đi. Nếu muốn khám phá thêm về vùng quê Nam Bộ, du khách có thể kết hợp thăm các địa điểm lân cận như chùa Xiêm Cán, núi Cò và rừng tràm Trà Sư. Với mức giá miễn phí, Cánh Đồng Lúa Ba Chúc là một điểm đến hấp dẫn và tiết kiệm cho du khách.</t>
         </is>
       </c>
-      <c r="O120" s="4" t="inlineStr"/>
-      <c r="P120" s="5" t="inlineStr">
+      <c r="O121" s="4" t="inlineStr"/>
+      <c r="P121" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.493,104.905</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="6" t="n">
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>quang-truong-va-pho-di-bo-tri-ton</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>Quảng Trường &amp; Phố Đi Bộ Trung Tâm Tri Tôn</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr"/>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F121" s="7" t="n"/>
-      <c r="G121" s="6" t="n">
+      <c r="F122" s="7" t="n"/>
+      <c r="G122" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="H121" s="6" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>10.424, 105.009</t>
         </is>
       </c>
-      <c r="I121" s="7" t="inlineStr">
+      <c r="I122" s="7" t="inlineStr">
         <is>
           <t>Đường Trần Hưng Đạo &amp; Đường 3/2, Thị trấn Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J121" s="7" t="inlineStr"/>
-      <c r="K121" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M121" s="7" t="inlineStr">
+      <c r="J122" s="7" t="inlineStr"/>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M122" s="7" t="inlineStr">
         <is>
           <t>Khu vực quảng trường công viên trung tâm thị trấn Tri Tôn, nơi diễn ra các hoạt động dạo bộ, thả diều, vui chơi ngoài trời và thưởng thức trà chanh, ăn vặt vỉa hè sôi động mỗi tối.</t>
         </is>
       </c>
-      <c r="N121" s="7" t="inlineStr">
+      <c r="N122" s="7" t="inlineStr">
         <is>
           <t>Quảng Trường Tri Tôn – Nhịp sống đêm rộn ràng nơi phố núi  1. Hoạt động về đêm: • Điểm dạo mát, thư giãn của người dân và du khách từ 17:00 – 22:30 mỗi tối. • Tập trung nhiều hàng quán ăn vặt miền Tây: bánh tráng nướng, chè thốt nốt, trà đào dầm thốt nốt và sinh tố trái cây tươi.</t>
         </is>
       </c>
-      <c r="O121" s="7" t="inlineStr"/>
-      <c r="P121" s="8" t="inlineStr">
+      <c r="O122" s="7" t="inlineStr"/>
+      <c r="P122" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.424,105.009</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="3" t="n">
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>nui-co-to</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>Núi Cô Tô (Phụng Hoàng Sơn) &amp; Đỉnh Vồ Hội</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr"/>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr"/>
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Xã Cô Tô</t>
         </is>
       </c>
-      <c r="F122" s="4" t="inlineStr">
+      <c r="F123" s="4" t="inlineStr">
         <is>
           <t>mountain</t>
         </is>
       </c>
-      <c r="G122" s="3" t="n">
+      <c r="G123" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>10.3758, 104.9958</t>
         </is>
       </c>
-      <c r="I122" s="4" t="inlineStr">
+      <c r="I123" s="4" t="inlineStr">
         <is>
           <t>Xã Cô Tô &amp; Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J122" s="4" t="inlineStr"/>
-      <c r="K122" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M122" s="4" t="inlineStr">
+      <c r="J123" s="4" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M123" s="4" t="inlineStr">
         <is>
           <t>Tuyệt tác thiên nhiên giữa lòng Thất Sơn</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="N123" s="4" t="inlineStr">
         <is>
           <t>Khám Phá Núi Cô Tô (Phụng Hoàng Sơn) – Nóc Nhà Săn Mây Bảy Núi  1. Vị trí &amp; Tên gọi: • Tên tiếng Khmer là Phnom-Ktô. Nhìn từ xa, dáng núi uốn lượn như cánh chim phượng hoàng khổng lồ che chở vùng đồng bằng nên có mỹ danh Phụng Hoàng Sơn (cao 614m).  2. Các tọa độ check-in huyền thoại trên đỉnh núi: • Đỉnh Vồ Hội Lớn: Khối đá granite sừng sững nhô ra vực sâu, phóng tầm mắt ngắm trọn thung lũng lúa Tà Pạ và bình minh ngũ sắc. • Vồ Hội Nhỏ: Bãi đất phẳng lộng gió, điểm cắm trại qua đêm săn biển mây sáng sớm cực hot của giới trẻ. • Sân Tiên &amp; Dấu Chân Cổ: Phiến đá tự nhiên in hằn dấu chân khổng lồ gắn liền với truyền thuyết tiên nữ hạ phàm dạo chơi. • Biểu tượng chữ "TRI TÔN": 6 chữ cái bê tông cốt thép trắng sứ cao 7m tại sườn núi khu vực Sân Tiên, thắp đèn LED rực rỡ ban đêm.  3. Hướng dẫn di chuyển an toàn: • Bắt đầu từ cổng Hồ Soài So ➔ Thuê Đội xe ôm bản địa Núi Cô Tô (xe số độ 2 phanh phụ chuyên dụng, 100k - 150k/khứ hồi) hoặc trekking bộ 2 - 3 tiếng.</t>
         </is>
       </c>
-      <c r="O122" s="4" t="inlineStr"/>
-      <c r="P122" s="5" t="inlineStr">
+      <c r="O123" s="4" t="inlineStr"/>
+      <c r="P123" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.3758,104.9958</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="6" t="n">
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>3adb5c32-đá-vồ-hội-mẹ-cô-tô</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>Đá Vồ Hội Mẹ Cô Tô</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr"/>
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>Xã Cô Tô</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>Săn mây</t>
         </is>
       </c>
-      <c r="G123" s="6" t="n">
+      <c r="G124" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="H123" s="6" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>10.401, 105.016</t>
         </is>
       </c>
-      <c r="I123" s="7" t="inlineStr">
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>Đỉnh Núi Cô Tô, Ấp Tô Thuận, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J123" s="7" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L123" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M123" s="7" t="inlineStr">
+      <c r="J124" s="7" t="inlineStr"/>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M124" s="7" t="inlineStr">
         <is>
           <t>Tọa độ săn mây và ngắm bình minh tuyệt mỹ trên đỉnh Núi Cô Tô (độ cao 614m), thuộc xã Cô Tô. Từ đây, du khách có thể phóng tầm mắt ôm trọn biển mây trắng bồng bềnh và toàn cảnh cánh đồng lúa Tà Pạ bát ngát.</t>
         </is>
       </c>
-      <c r="N123" s="7" t="inlineStr">
+      <c r="N124" s="7" t="inlineStr">
         <is>
           <t>Đá Vồ Hội Mẹ Núi Cô Tô – Mỏm Đá Thiêng Ngắm Toàn Cảnh Tuyệt Sắc Đồng Bằng Bảy Núi  Tọa lạc ở độ cao hơn 500 mét gần đỉnh Phụng Hoàng Sơn (Núi Cô Tô) thuộc Xã Cô Tô, Đá Vồ Hội Mẹ là một trong những tọa độ săn mây, ngắm bình minh và hoàng hôn kỳ vĩ bậc nhất miền Tây Nam Bộ. Đứng trên mỏm đá granite nguyên khối khổng lồ nhô hẳn ra không trung, du khách sẽ được phóng tầm mắt ôm trọn bức tranh đồng ruộng Tà Pạ ô vuông bàn cờ trải dài tít tắp đến tận biên giới Tây Nam.  1. Vị Trí &amp; Ý Nghĩa Địa Danh "Vồ Hội" • Vị trí hành chính: Gần đỉnh Núi Cô Tô (Phụng Hoàng Sơn), Xã Cô Tô, tỉnh An Giang. • Độ cao: Nằm ở cao độ khoảng 520 mét so với mực nước biển. • Sự tích tên gọi Vồ Hội: Theo truyền tích dân gian Bảy Núi, ngày xưa đây là nơi các bậc tiền nhân, tu sĩ đắc đạo thường tề tựu đàm đạo việc đời việc đạo (nên gọi là "Vồ Hội"). Khu vực này chia làm hai mỏm đá lớn: Vồ Hội Lớn (Vồ Hội Mẹ) và Vồ Hội Nhỏ (Đá Vồ Hội Đổ sống ảo).  2. Tuyệt Tác Thiên Nhiên &amp; Góc Nhìn Toàn Cảnh Bảy Núi • Mỏm đá granite nguyên khối sừng sững: Khối đá hoa cương khổng lồ phẳng phiu nhô ra giữa khoảng trời mênh mông, đón nhận những cơn gió núi lồng lộng mát rượi. • Tầm nhìn panorama 360 độ: Từ Vồ Hội Mẹ, bạn có thể nhìn thấy toàn cảnh thị trấn Tri Tôn thu nhỏ, những cánh đồng lúa Tà Pạ rực rỡ sắc màu, dòng suối Bạc lấp lánh và các ngọn núi Cấm, núi Dài, núi Két nhấp nhô xa xăm trong mây ngàn. • Biển mây sáng sớm &amp; Hoàng hôn rực lửa: Vào mùa mưa hoặc những ngày ẩm ướt, sáng sớm Vồ Hội Mẹ chìm trong biển mây bồng bềnh; chiều tà là nơi ngắm mặt trời đỏ ối từ từ lặn xuống cánh đồng biên giới Campuchia.  3. Điểm Đến Tâm Linh &amp; Không Gian Thiền Tịnh • Các am cốc tu tập thanh tịnh: Quanh khu vực Vồ Hội Mẹ có nhiều am điện thờ cúng linh thiêng và các cốc đá của các đạo sĩ tu thiền, mang lại cảm giác bình an, thanh thoát cho tâm hồn. • Bàn chân tiên &amp; Điện thờ: Gần Vồ Hội còn có khu vực Sân Tiên với dấu tích bàn chân khổng lồ in trên mặt đá hoa cương theo truyền thuyết thần thoại dân gian Bảy Núi.  4. Hướng Dẫn Đường Đi &amp; Cách Di Chuyển • Cách 1 - Đi xe ôm bản địa: Từ chân Núi Cô Tô (khu vực Hồ Soài So), thuê các bác tài "xe ôm bay" bản địa chở lên với giá khoảng 70.000đ – 100.000đ/lượt. Đây là trải nghiệm cảm giác mạnh đầy thú vị trên những cung đường dốc cua ngoạn mục. • Cách 2 - Trekking leo bậc thang: Dành cho những ai yêu thích thử thách thể lực. Lộ trình leo khoảng 2,5 – 3,5 tiếng theo các bậc thang đá men qua các vườn xoài, mãng cầu và am điện thanh tịnh.  5. Lưu Ý An Toàn Dành Cho Du Khách • An toàn bên mép vực: Mỏm đá Vồ Hội nằm sát vực sâu thẳm, gió núi thổi rất mạnh. Tuyệt đối không chen lấn, không bước ra sát mép đá trơn trượt hoặc đùa giỡn chụp ảnh nguy hiểm. • Giữ gìn vệ sinh môi trường: Mang theo nước uống và gom toàn bộ rác thải mang xuống chân núi, bảo vệ cảnh quan thiên nhiên linh thiêng của ngọn núi. • Thời điểm lý tưởng: 05:30 – 07:30 (săn mây bình minh) hoặc 16:00 – 17:45 (ngắm hoàng hôn rực rỡ).</t>
         </is>
       </c>
-      <c r="O123" s="7" t="inlineStr"/>
-      <c r="P123" s="8" t="inlineStr">
+      <c r="O124" s="7" t="inlineStr"/>
+      <c r="P124" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.401,105.016</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="3" t="n">
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>5169fbf9-đá-vồ-hội-đổ-(mỏm-đá</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>Đá Vồ Hội Đổ (Mỏm Đá Sống Ảo)</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr"/>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Xã Cô Tô</t>
         </is>
       </c>
-      <c r="F124" s="4" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>Tọa độ săn ảnh đỉnh núi</t>
         </is>
       </c>
-      <c r="G124" s="3" t="n">
+      <c r="G125" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>10.4015, 105.0165</t>
         </is>
       </c>
-      <c r="I124" s="4" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>Đá Vồ Hội Đổ, Đỉnh Núi Cô Tô, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J124" s="4" t="inlineStr"/>
-      <c r="K124" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
+      <c r="J125" s="4" t="inlineStr"/>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M125" s="4" t="inlineStr">
         <is>
           <t>Thông Tin Thực Tế Về Vồ Hội (Đỉnh Núi Cô Tô)</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>Người dân Tri Tôn và vùng Bảy Núi quen gọi là Vồ Hội (phương ngữ miền Tây thường đọc là Dồ Hội). "Vồ" là từ chỉ mỏm đá hoặc chỏm núi đá nhô cao vươn ra ngoài không gian.  Tên gọi "Vồ Hội Đổ" trong giới phượt/trekking xuất phát từ hình thế tảng đá hoa cương phẳng lỳ nhô hẳn ra ngoài vách núi, dốc thoai thoải nghiêng về phía vực thung lũng sâu bên dưới. • Vị trí hành chính: Nằm ở độ cao khoảng 500 – 600m trên sườn/đỉnh Núi Cô Tô (Phụng Hoàng Sơn), thuộc địa phận xã Núi Tô / thị trấn Cô Tô, huyện Tri Tôn, tỉnh An Giang.  2. Cấu trúc thực tế tại Vồ Hội  Tại khu vực này được chia làm 2 vị trí đá riêng biệt nằm cách nhau khoảng 50 mét: • Vồ Hội Nhỏ:  Là tảng đá nhỏ hơn, hướng mặt về phía Đông.  Đây là tọa độ đón bình minh đẹp nhất trên đỉnh Cô Tô.  Khu vực này thoáng, ít người tụ tập hơn nên rất thuận tiện để ngồi ngắm cảnh và chụp ảnh. • Vồ Hội Lớn:  Là phiến đá granite khổng lồ, bằng phẳng, có tầm nhìn bao quát toàn bộ cánh đồng Tà Pạ, hồ Tà Pạ, thị trấn Tri Tôn và phóng tầm mắt sang dãy Núi Cấm (Thiên Cấm Sơn).  Hướng mặt về phía Tây, là điểm ngắm hoàng hôn và săn mây/săn ráng chiều nổi tiếng nhất vùng. • Yếu tố tâm linh thực tế: Trên sân đá Vồ Hội Lớn có lập bàn thờ Phật, bàn thờ tiền nhân và một bệ đá hình tháp/kim tự tháp có khắc chữ thư pháp, câu kinh tưởng nhớ người đã khuất.  3. Thực tế cung đường &amp; Cách di chuyển lên • Vồ Hội  Điểm xuất phát: Từ chân núi (khu vực cổng Khu du lịch Suối Vàng Soài So hoặc các ngõ bậc thang dưới chân núi Tô). • Phương tiện di chuyển:  Xe ôm chân núi (Dịch vụ xe thồ núi • Cô Tô): Đây là phương tiện phổ biến nhất. Đội ngũ tài xế bản địa sử dụng xe máy số đã độ/thay nhông sên dĩa để chở khách leo đường bê tông dốc đứng, quanh co lên đến Điện Năm Căn / Sân Tiên. Giá vé được niêm yết theo từng chặng (khoảng vài chục đến hơn 100.000 VNĐ/chuyến tùy độ cao). • Chặng đi bộ cuối: Từ Điện Năm Căn, xe máy không thể chạy tiếp. Du khách phải leo bộ thêm khoảng 100 – 150 bậc đá men theo sườn núi để đến được miếu Bà Cố và cụm Vồ Hội Lớn – Vồ Hội Nhỏ. • Trekking hoàn toàn bằng đường bộ: Đi men theo bậc thang từ chân núi, xuyên qua các rẫy xoài, vườn điều và các hang điện thờ. Thời gian leo mất từ 2,5 – 3,5 tiếng tùy thể lực.  4. Dịch vụ lưu trú &amp; Ăn uống thực tế trên núi • Nghỉ ngơi / Lưu trú:  Gần khu vực Vồ Hội và các điện thờ lân cận có các am, cốc và quán nước nhỏ của người dân bản địa. Khách hành hương hoặc dân phượt có thể xin tá túc (ngủ võng, trải chiếu trong mái hiên/am) hoặc mang theo lều tự cắm ở các bãi đất bằng phẳng gần đó.  Nước ngọt và điện trên núi khá hạn chế, dùng nguồn điện năng lượng mặt trời hoặc máy phát nhỏ. • Ăn uống: Các quán nước phục vụ mì gói, nước thốt nốt tươi, nước giải khát, cà phê và một số món ăn chay/mặn đơn giản.  5. Cảnh báo an toàn thực tế • Vực sâu không có lan can: Các phiến đá Vồ Hội nằm chênh vênh mép vực đá dựng đứng. Không leo trèo, nhảy nhót, đùa giỡn hoặc ngồi sát mép đá dốc khi trời mưa trơn trượt hoặc khi gió to. • Gió lốc: Đỉnh núi rất lộng gió, cần cất giữ cẩn thận điện thoại, flycam, nón/mũ cá nhân.</t>
         </is>
       </c>
-      <c r="O124" s="4" t="inlineStr"/>
-      <c r="P124" s="5" t="inlineStr">
+      <c r="O125" s="4" t="inlineStr"/>
+      <c r="P125" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4015,105.0165</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="6" t="n">
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>canh-dong-lua-ta-pa</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>Cánh đồng lúa Tà Pạ</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr"/>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G125" s="6" t="n">
+      <c r="G126" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="H125" s="6" t="inlineStr">
+      <c r="H126" s="6" t="inlineStr">
         <is>
           <t>10.412, 104.998</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr">
+      <c r="I126" s="7" t="inlineStr">
         <is>
           <t>Dưới chân đồi Tà Pạ, Xã Núi Tô, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J125" s="7" t="inlineStr"/>
-      <c r="K125" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L125" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M125" s="7" t="inlineStr">
+      <c r="J126" s="7" t="inlineStr"/>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M126" s="7" t="inlineStr">
         <is>
           <t>Cánh đồng lúa Tà Pạ: Một viên ngọc quý giá của vùng đất Bảy Núi.</t>
         </is>
       </c>
-      <c r="N125" s="7" t="inlineStr">
+      <c r="N126" s="7" t="inlineStr">
         <is>
           <t>Khám Phá Cánh Đồng Lúa Tà Pạ &amp; "Con Đường Tơ Lụa" – Bức Tranh Thu Nhỏ Của Miền Thất Sơn  Nằm dưới chân đồi Tà Pạ và rặng núi Cô Tô hùng vĩ, cánh đồng lúa Tà Pạ cùng "Con đường tơ lụa" uốn lượn xuyên qua những hàng thốt nốt và vườn cây trâm cổ thụ là một trong những cảnh sắc đồng quê đẹp và thơ mộng nhất miền Tây Nam Bộ.  1. Nét Độc Đáo Của Cánh Đồng Lúa Tà Pạ  Địa hình "ruộng bậc thang" hiếm hoi • ở ĐBSCL: Khác với những cánh đồng thẳng cánh cò bay bằng phẳng thông thường, cánh đồng Tà Pạ nằm thoai thoải bên sườn núi. Những thửa ruộng đan xen, giật cấp nhẹ nhàng như những bậc thang mềm mại. • Bức tranh ghép đa sắc màu: Người dân Khmer tại đây thường canh tác theo phương thức chia ô nhỏ, thời gian gieo cấy không đồng loạt. Do đó, khi nhìn từ trên cao (như đỉnh đồi Tà Pạ hoặc Vồ Hội - Núi Cô Tô), cánh đồng hiện ra như một tấm thảm ghép khổng lồ với nhiều mảng màu: chỗ xanh non mơn mởn, nơi vàng ươm trĩu hạt, có chỗ lại ánh lên màu nước phù sa. • Điểm xuyết bóng thốt nốt: Những hàng cây thốt nốt cao vút vươn thẳng lên nền trời xanh, tạo nên biểu tượng phong cảnh đặc trưng không thể nhầm lẫn của vùng đất An Giang.  2. "Con Đường Tơ Lụa" Tri Tôn – Dải Lụa Uốn • Lượn Giữa Đồng Vị trí tuyến đường: Đây là cách gọi thân thương của du khách và giới nhiếp ảnh dành cho cung đường uốn lượn chạy cắt ngang qua cánh đồng Tà Pạ, kết nối men theo khu vực hồ Soài Chek và vườn cây trâm cổ thụ. • Vẻ đẹp nên thơ: Đường đã được đổ bê tông sạch sẽ, bằng phẳng, uốn lượn mềm mại như một dải lụa vắt ngang thảm lúa.Chạy xe máy chầm chậm trên con đường này, bạn sẽ được đón từng cơn gió đồng lồng lộng, hít hà mùi thơm ngọt của lúa non hay hương lúa chín ngập tràn.Dọc hai bên đ.  ường là hàng cây thốt nốt, những khóm hoa dại ven ruộng và những bóng cây trâm già soi bóng, tạo thành những góc chụp ảnh "sống ảo" mộc mạc mà vô cùng cuốn hút.  3. Thời Điểm Lý Tưởng • Để Trải Nghiệm &amp; Chụp ẢnhMùa lúa:- Mùa lúa non (Tháng 4 – Tháng 7): Cả cánh đồng khoác lên màu xanh mướt mát mắt, tràn trề sức sống. • Mùa lúa chín (Tháng 8 – Tháng 11): Đây là thời điểm rực rỡ nhất. Cánh đồng ngả sang màu vàng óng ả, rộn ràng không khí thu hoạch của bà con Khmer. • Khung giờ vàng trong ngày: Bình minh (5h30 – 6h30): Khi sương sớm còn vương trên ngọn cỏ, ánh nắng đầu ngày le lói qua tán thốt nốt mang lại vẻ đẹp thanh khiết, tĩnh lặng. • Hoàng hôn (17h00 – 18h00): Mặt trời đỏ rực từ từ lặn sau lưng núi Cô Tô, bóng thốt nốt đổ dài trên ruộng lúa tạo nên khung cảnh lãng mạn mê hồn.  4. Gợi Ý Lịch Trình Khám Phá Quanh Khu VựcBạn có thể kết hợp trọn vẹn cụm • điểm đến gần kề trong vòng 1 ngày: Sáng: Viếng Chùa Tà Pạ (Chùa Núi) $\rightarrow$ Ngắm toàn cảnh cánh đồng từ trên cao $\rightarrow$ Xuống dạo chơi Hồ Tà Pạ. • Trưa: Thưởng thức đặc sản Gà đốt lá chúc bên Hồ Ô Thum hoặc nếm thử bún cá, đu đủ đâm Tri Tôn. • Chiều: Chạy xe máy vi vu trên "Con đường tơ lụa" xuyên cánh đồng Tà Pạ $\rightarrow$ Ghé Hồ Soài Chek, hàng cây trâm $\rightarrow$ Đón hoàng hôn rực rỡ trên đồng lúa.  5. Lưu Ý Dành Cho • Du KháchTôn trọng bà con nông dân: Khi chụp ảnh, chỉ đi trên các con đường bê tông hoặc bờ ruộng vững chắc; tuyệt đối không giẫm đạp làm gãy đổ lúa của người dân. • Bảo vệ cảnh quan: Luôn thu gom rác thải cá nhân, giữ cho cánh đồng luôn xanh sạch và giữ trọn nét bình yên vốn có.</t>
         </is>
       </c>
-      <c r="O125" s="7" t="inlineStr"/>
-      <c r="P125" s="8" t="inlineStr">
+      <c r="O126" s="7" t="inlineStr"/>
+      <c r="P126" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.412,104.998</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="3" t="n">
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>6ffa8a7b-cầu-gỗ-mộc-mạc-hồ-ô-</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>Cầu Gỗ Mộc Mạc Hồ Ô Thum</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr"/>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr"/>
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>Xã Ô Lâm</t>
         </is>
       </c>
-      <c r="F126" s="4" t="inlineStr">
+      <c r="F127" s="4" t="inlineStr">
         <is>
           <t>Điểm check-in sống ảo</t>
         </is>
       </c>
-      <c r="G126" s="3" t="n">
+      <c r="G127" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>10.377, 104.987</t>
         </is>
       </c>
-      <c r="I126" s="4" t="inlineStr">
+      <c r="I127" s="4" t="inlineStr">
         <is>
           <t>Lòng hồ Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J126" s="4" t="inlineStr"/>
-      <c r="K126" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M126" s="4" t="inlineStr">
+      <c r="J127" s="4" t="inlineStr"/>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M127" s="4" t="inlineStr">
         <is>
           <t>Cây cầu gỗ mộc mạc bắc ngang mỏm đồi ven hồ Ô Thum, địa điểm check-in ngắm hoàng hôn buông xuống mặt hồ tuyệt đẹp tại Xã Ô Lâm.</t>
         </is>
       </c>
-      <c r="N126" s="4" t="inlineStr">
+      <c r="N127" s="4" t="inlineStr">
         <is>
           <t>Cầu Gỗ Mộc Mạc Hồ Ô Thum – Tọa Độ Sống Ảo Nàng Thơ Bên Mặt Nước Xanh Ngọc Bích  Nằm duyên dáng ven bờ hồ nước ngọt nhân tạo Hồ Ô Thum thuộc Xã Ô Lâm, Cây Cầu Gỗ Mộc Mạc là một trong những điểm nhấn cảnh quan check-in thơ mộng và lãng mạn bậc nhất của Tri Tôn. Cây cầu gỗ mộc mạc nhô dài ra giữa làn nước xanh ngọc bích phẳng lặng, tạo nên một góc nhìn ngoạn mục hướng thẳng ra triền đồi núi Ô Lâm và những rặng thốt nốt xanh rì của vùng đất Bảy Núi.  1. Vị Trí &amp; Không Gian Hồ Nước Ô Thum • Vị trí hành chính: Ven bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Khoảng cách &amp; Hướng đi: Cách trung tâm Thị trấn Tri Tôn khoảng 11 km về phía Tây Nam. Du khách đi theo tuyến đường ĐT948 hướng về Ô Lâm, rẽ vào đường liên xã dẫn vào lòng hồ Ô Thum. • Khung cảnh thơ mộng: Hồ Ô Thum vốn là hồ thủy lợi tự nhiên được bao bọc bởi triền đồi dốc thoai thoải. Mặt hồ quanh năm trong xanh phẳng lặng như gương soi, phản chiếu bóng mây trời và đồi núi chập chùng.  2. Nét Đẹp Độc Bản Của Cây Cầu Gỗ Mộc Mạc • Thiết kế mộc mạc hòa hợp thiên nhiên: Cầu được dựng bằng những thân gỗ rừng tự nhiên mộc mạc, tay vịn thanh mảnh bắc men theo mép nước nhô hẳn ra giữa lòng hồ. • Góc nhìn panorama 180 độ: Đứng trên cầu gỗ, bạn sẽ có cảm giác như đang hòa mình trọn vẹn vào giữa không gian non nước mênh mông, đón nhận những cơn gió núi lồng lộng mát rượi thổi qua mặt hồ. • Hậu cảnh đồi núi trập trùng: Phía sau cây cầu là những triền đồi xanh mướt của Xã Ô Lâm, những rặng cây thốt nốt cao vút và những chiếc thuyền gỗ nhỏ neo đậu ven bờ tạo nên khung cảnh bình yên tựa chốn thôn dã Bắc Âu.  3. Trải Nghiệm Kết Hợp Check-in &amp; Thưởng Thức Ẩm Thực • Chụp ảnh sống ảo phong cách nàng thơ: Cầu gỗ Ô Thum là tọa độ lý tưởng cho các bộ ảnh dã ngoại mang phong cách vintage, váy maxi bay bổng hoặc trang phục truyền thống miền Tây. • Thưởng thức gà đốt lá chúc trứ danh: Ngay quanh khu vực hồ và cầu gỗ là "thủ phủ" của món Gà Đốt Ô Thum nổi tiếng khắp miền Tây (các quán Siêu Bó, Thảo Nguyên, Kim Suổl...). Du khách vừa có thể chụp ảnh ngắm cảnh hồ, vừa thưởng thức gà đốt nóng hổi chấm muối ớt lá chúc cay nồng.  4. Hướng Dẫn Khung Giờ &amp; Góc Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm vàng khi ánh mặt trời đỏ ối dần lặn sau rặng núi xa, nhuộm hồng cả mặt nước hồ Ô Thum và tạo nên những bức ảnh ngược sáng lung linh tuyệt mỹ. • Sáng sớm thanh bình (07:00 – 08:30): Mặt hồ phẳng lặng không một gợn sóng, sương sớm bảng lảng trôi trên mặt nước mang lại cảm giác tĩnh tại, an yên. • Góc chụp gợi ý: Chụp từ bờ hồ lấy trọn chiều dài của cây cầu gỗ với người mẫu đứng ở mút cầu ngắm nhìn ra xa; hoặc chụp cận cảnh với hậu cảnh mặt nước hồ xanh ngọc bích.  5. Lưu Ý Thực Địa Cho Du Khách • An toàn bên mép nước: Cầu gỗ nằm trên mặt hồ nước sâu, du khách khi di chuyển chụp ảnh cần cẩn thận giữ thăng bằng, không chen lấn xô đẩy và đặc biệt chú ý nếu có trẻ nhỏ đi cùng. • Giữ gìn cảnh quan: Tuyệt đối không vứt rác, vỏ chai hay thức ăn thừa xuống lòng hồ Ô Thum. • Chi phí: Thường miễn phí tham quan chụp ảnh nếu bạn sử dụng dịch vụ ăn uống tại các quán ăn ven hồ, hoặc phí tham quan nhẹ khoảng 10.000đ/lượt.</t>
         </is>
       </c>
-      <c r="O126" s="4" t="inlineStr"/>
-      <c r="P126" s="5" t="inlineStr">
+      <c r="O127" s="4" t="inlineStr"/>
+      <c r="P127" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.377,104.987</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="6" t="n">
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>cay-thot-not-trai-tim</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>Hàng Thốt Nốt Trái Tim Ô Lâm</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr"/>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr"/>
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>Xã Ô Lâm</t>
         </is>
       </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>photospot</t>
         </is>
       </c>
-      <c r="G127" s="6" t="n">
+      <c r="G128" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="H127" s="6" t="inlineStr">
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>10.3685, 104.9785</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
         <is>
           <t>Xã An Tức, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr"/>
-      <c r="K127" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M127" s="7" t="inlineStr">
+      <c r="J128" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M128" s="7" t="inlineStr">
         <is>
           <t>Cụm cây thốt nốt tự nhiên uốn lượn đan vòm thành hình trái tim độc đáo giữa cánh đồng lúa xã Ô Lâm. Điểm check-in sống ảo biểu tượng của du lịch Bảy Núi An Giang.</t>
         </is>
       </c>
-      <c r="N127" s="7" t="inlineStr">
+      <c r="N128" s="7" t="inlineStr">
         <is>
           <t>Check-in Cây Thốt Nốt Trái Tim – Tọa độ lãng mạn giữa đồng quê Tri Tôn  Giữa mênh mông đồng lúa vùng Bảy Núi, cụm Cây thốt nốt trái tim là một trong những điểm dừng chân check-in nổi bật và thu hút đông đảo bạn trẻ khi du lịch An Giang. 1. • Vị trí và Điểm độc đáo Địa chỉ: Xã An Tức, huyện Tri Tôn, tỉnh An Giang (nằm trên tuyến đường liên xã kết nối giữa Hồ Tà Pạ và Hồ Ô Thum). • Vẻ đẹp tự nhiên: Thực chất đây là cụm nhiều cây thốt nốt mọc sát nhau, phần thân và tán lá tự nhiên đan xen khéo léo tạo thành hình một trái tim khổng lồ rỗng ở giữa. • Cảnh quan xung quanh: Nằm lẻ loi giữa cánh đồng lúa bao la, phía xa xa là dãy núi chập chùng, tạo nên phông nền chụp ảnh vô cùng thơ mộng và bình yên.  2. Hướng dẫn di chuyển Từ TP  . • Châu  Đốc: Đi theo hướng QL91 về trung tâm thị trấn Tri Tôn, sau đó rẽ vào đường Tỉnh lộ hướng về xã An Tức (tuyến đường đi Hồ Ô Thum). Từ TP. • Long Xuyên: Đi dọc theo QL91 (hoặc TL943 qua Thoại Sơn) đến Tri Tôn, tiếp tục chạy theo đường đi xã An Tức. • Dấu mốc nhận biết: Khi đến gần khu vực UBND xã An Tức, đối diện có cột/trạm phát sóng viễn thông, bạn rẽ vào con hẻm nhỏ dẫn thẳng ra cánh đồng lúa sẽ bắt gặp cụm cây thốt nốt trái tim. Phương tiện lý tưởng nhất là xe máy để vừa tiện luồn lách vào đường bờ ruộng, vừa thảnh thơi ngắm cảnh núi non Tri Tôn.  3. Thời • điểm chụp ảnh đẹp nhất Trong ngày: Sáng sớm khi nắng vừa lên nhẹ hoặc buổi chiều tà lúc hoàng hôn buông xuống (tránh đi ban trưa vì nắng gắt và khó căn góc chụp ngược sáng). • Mùa lúa: Đẹp nhất là vào mùa lúa chín vàng ươm hoặc mùa lúa xanh mướt trải dài ngút ngàn, làm nổi bật trọn vẹn hình dáng trái tim của cụm cây.  4. Lưu ý khi tham quan &amp; • Trải nghiệm ẩm thựcÝ thức giữ gìn: Cụm thốt nốt nằm trực tiếp trên đất ruộng canh tác của người dân. Khi đến chụp ảnh, tuyệt đối không giẫm đạp lên lúa, không bẻ nhánh cây và thu gom sạch sẽ rác thải cá nhân để bảo vệ cảnh quan chung. • Đặc sản không thể bỏ lỡ: Uống nước thốt nốt tươi ngọt thanh mát lạnh dọc hai bên đường.Ghé thưởng thức món gà đốt lá chúc trứ danh tại Hồ Ô Thum ngay gần đó.</t>
         </is>
       </c>
-      <c r="O127" s="7" t="inlineStr"/>
-      <c r="P127" s="8" t="inlineStr">
+      <c r="O128" s="7" t="inlineStr"/>
+      <c r="P128" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.3685,104.9785</t>
         </is>
       </c>
     </row>
-    <row r="128"/>
-    <row r="129" ht="32" customHeight="1">
-      <c r="A129" s="12" t="inlineStr">
+    <row r="129"/>
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
         <is>
           <t>☕ V. CÀ PHÊ VIEW ĐẸP &amp; ĐIỂM ĐẾN VỀ ĐÊM — TỔNG SỐ: 13 ĐỊA ĐIỂM</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Mã ID</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>Tên Địa Điểm</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Tên Tiếng Anh (EN)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Xã / Thị Trấn</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Phân Loại Phụ</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>Đánh Giá (⭐)</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Tọa Độ GPS (Lat, Lng)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>Địa Chỉ Thực Địa</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>Điện Thoại / Hotline</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="K131" s="2" t="inlineStr">
         <is>
           <t>Mức Giá</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="L131" s="2" t="inlineStr">
         <is>
           <t>Giờ Mở Cửa / Giờ Vàng</t>
         </is>
       </c>
-      <c r="M130" s="2" t="inlineStr">
+      <c r="M131" s="2" t="inlineStr">
         <is>
           <t>Mô Tả Tổng Quan</t>
         </is>
       </c>
-      <c r="N130" s="2" t="inlineStr">
+      <c r="N131" s="2" t="inlineStr">
         <is>
           <t>Sự Tích &amp; Di Sản Thực Địa</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr">
+      <c r="O131" s="2" t="inlineStr">
         <is>
           <t>Mẹo Thực Địa</t>
         </is>
       </c>
-      <c r="P130" s="2" t="inlineStr">
+      <c r="P131" s="2" t="inlineStr">
         <is>
           <t>Link Google Maps Dẫn Đường</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="3" t="n">
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>b6a52dfa-chạm-coffee-&amp;-tea-tr</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>CHẠM Coffee &amp; Tea Tri Tôn</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr"/>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr"/>
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F131" s="4" t="n"/>
-      <c r="G131" s="3" t="n">
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>10.4128, 105.0068</t>
         </is>
       </c>
-      <c r="I131" s="4" t="inlineStr">
+      <c r="I132" s="4" t="inlineStr">
         <is>
           <t>120 Đường Hùng Vương, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J131" s="4" t="inlineStr"/>
-      <c r="K131" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M131" s="4" t="inlineStr">
+      <c r="J132" s="4" t="inlineStr"/>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
         <is>
           <t>Quán cà phê ngắm cảnh gió núi lộng lẫy về đêm tại trung tâm Thị trấn Tri Tôn. Không gian sân vườn mở ngoài trời đón gió Bảy Núi, có đèn trang trí lung linh và đêm nhạc acoustic nhẹ nhàng.</t>
         </is>
       </c>
-      <c r="N131" s="4" t="inlineStr">
+      <c r="N132" s="4" t="inlineStr">
         <is>
           <t>CHẠM Coffee &amp; Tea Tri Tôn – Không Gian Minimalist Trẻ Trung &amp; Đêm Nhạc Acoustic Sôi Động  Tọa lạc trên đường Hùng Vương sầm uất tại Thị trấn Tri Tôn, CHẠM Coffee &amp; Tea là điểm hẹn quen thuộc của giới trẻ và du khách yêu thích phong cách thiết kế Minimalist tối giản hiện đại cùng những đêm nhạc Acoustic sôi động vào dịp cuối tuần.  1. Vị Trí &amp; Không Gian Tối Giản Tinh Tế • Vị trí: 120 Đường Hùng Vương, Khóm 4, Thị trấn Tri Tôn, tỉnh An Giang. • Tone màu xám xi măng &amp; Cây xanh: Thiết kế hiện đại theo phong cách công nghiệp (Industrial Minimalist), kết hợp mảng tường bê tông mài, kính cường lực lớn và những chậu cây xương rồng, monstera xanh mát mắt.  2. Điểm Hẹn Đêm Nhạc Acoustic Cuối Tuần • Sân khấu giao lưu âm nhạc: Vào các tối thứ Bảy và Chủ Nhật, quán thường xuyên tổ chức các đêm nhạc Acoustic với các ban nhạc trẻ địa phương, mang lại bầu không khí ấm áp, vui tươi cho đêm phố núi Tri Tôn.  3. Thực Đơn Đồ Uống Bắt Trend • Cà phê muối béo ngậy, Cà phê trứng nướng: Đồ uống đậm đà chuẩn vị. • Trà ô long sữa nướng trân châu hoàng kim, Trà mãng cầu xiêm chua ngọt.  4. Thông Tin Quán • Giờ mở cửa: 06:30 – 22:30 mỗi ngày. • Mức giá: 22.000đ – 45.000đ / ly.</t>
         </is>
       </c>
-      <c r="O131" s="4" t="inlineStr"/>
-      <c r="P131" s="5" t="inlineStr">
+      <c r="O132" s="4" t="inlineStr"/>
+      <c r="P132" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4128,105.0068</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="6" t="n">
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B132" s="7" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>ca-phe-thuy-moc-tri-ton</t>
         </is>
       </c>
-      <c r="C132" s="7" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>Cà Phê Thủy Mộc Tri Tôn</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr"/>
-      <c r="E132" s="7" t="inlineStr">
+      <c r="D133" s="7" t="inlineStr"/>
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F132" s="7" t="inlineStr">
+      <c r="F133" s="7" t="inlineStr">
         <is>
           <t>cafe</t>
         </is>
       </c>
-      <c r="G132" s="6" t="n">
+      <c r="G133" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="H132" s="6" t="inlineStr">
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>10.4208, 105.0015</t>
         </is>
       </c>
-      <c r="I132" s="7" t="inlineStr">
+      <c r="I133" s="7" t="inlineStr">
         <is>
           <t>111 Nguyễn Thị Minh Khai, Thị trấn Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J132" s="7" t="inlineStr"/>
-      <c r="K132" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M132" s="7" t="inlineStr">
+      <c r="J133" s="7" t="inlineStr"/>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M133" s="7" t="inlineStr">
         <is>
           <t>Quán cà phê sân vườn yên tĩnh, mát mẻ thích hợp thư giãn và trò chuyện.</t>
         </is>
       </c>
-      <c r="N132" s="7" t="inlineStr">
+      <c r="N133" s="7" t="inlineStr">
         <is>
           <t>Cà Phê Thủy Mộc – Khoảng lặng bình yên giữa lòng Tri Tôn  1. Vị trí &amp; Cảnh quan: • Địa chỉ: 111 Nguyễn Thị Minh Khai, Thị trấn Tri Tôn, An Giang. • Cảnh quan: Không gian sân vườn thoáng đãng với hồ cá Koi bơi lội tung tăng, tiểu cảnh thác nước và rặng cây xanh mát rượi.  2. Menu &amp; Trải nghiệm: • Cà phê phin truyền thống, sinh tố trái cây tươi Bảy Núi, nước ép thanh mát. • Thích hợp cho gia đình, nhóm bạn chuyện trò thư thả sau chuyến leo núi hay dạo đồng lúa.  3. Giờ phục vụ: • Mở cửa: 06:30 – 21:30 mỗi ngày.</t>
         </is>
       </c>
-      <c r="O132" s="7" t="inlineStr"/>
-      <c r="P132" s="8" t="inlineStr">
+      <c r="O133" s="7" t="inlineStr"/>
+      <c r="P133" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4208,105.0015</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="24" customHeight="1">
-      <c r="A133" s="3" t="n">
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>4fc712e3-cầu-gỗ-giữa-đồng-lúa</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>Cầu Gỗ Giữa Đồng Lúa Ruộng Coffee</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr"/>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr"/>
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F133" s="4" t="inlineStr">
+      <c r="F134" s="4" t="inlineStr">
         <is>
           <t>Điểm check-in sống ảo</t>
         </is>
       </c>
-      <c r="G133" s="3" t="n">
+      <c r="G134" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>10.4152, 105.0182</t>
         </is>
       </c>
-      <c r="I133" s="4" t="inlineStr">
+      <c r="I134" s="4" t="inlineStr">
         <is>
           <t>Sân vườn Ruộng Coffee, Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J133" s="4" t="inlineStr"/>
-      <c r="K133" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
+      <c r="J134" s="4" t="inlineStr"/>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M134" s="4" t="inlineStr">
         <is>
           <t>Ngày nay, các loại cầu bằng bêtông trở nên phổ biến cùng với cầu thép. Nhịp cầu ngày càng được kéo dài, từ vài trăm mét như loại cầu …</t>
         </is>
       </c>
-      <c r="N133" s="4" t="inlineStr">
+      <c r="N134" s="4" t="inlineStr">
         <is>
           <t>Cầu Gỗ Mộc Mạc Hồ Ô Thum – Tọa Độ Sống Ảo Nàng Thơ Bên Mặt Nước Xanh Ngọc Bích  Nằm duyên dáng ven bờ hồ nước ngọt nhân tạo Hồ Ô Thum thuộc Xã Ô Lâm, Cây Cầu Gỗ Mộc Mạc là một trong những điểm nhấn cảnh quan check-in thơ mộng và lãng mạn bậc nhất của Tri Tôn. Cây cầu gỗ mộc mạc nhô dài ra giữa làn nước xanh ngọc bích phẳng lặng, tạo nên một góc nhìn ngoạn mục hướng thẳng ra triền đồi núi Ô Lâm và những rặng thốt nốt xanh rì của vùng đất Bảy Núi.  1. Vị Trí &amp; Không Gian Hồ Nước Ô Thum • Vị trí hành chính: Ven bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Khoảng cách &amp; Hướng đi: Cách trung tâm Thị trấn Tri Tôn khoảng 11 km về phía Tây Nam. Du khách đi theo tuyến đường ĐT948 hướng về Ô Lâm, rẽ vào đường liên xã dẫn vào lòng hồ Ô Thum. • Khung cảnh thơ mộng: Hồ Ô Thum vốn là hồ thủy lợi tự nhiên được bao bọc bởi triền đồi dốc thoai thoải. Mặt hồ quanh năm trong xanh phẳng lặng như gương soi, phản chiếu bóng mây trời và đồi núi chập chùng.  2. Nét Đẹp Độc Bản Của Cây Cầu Gỗ Mộc Mạc • Thiết kế mộc mạc hòa hợp thiên nhiên: Cầu được dựng bằng những thân gỗ rừng tự nhiên mộc mạc, tay vịn thanh mảnh bắc men theo mép nước nhô hẳn ra giữa lòng hồ. • Góc nhìn panorama 180 độ: Đứng trên cầu gỗ, bạn sẽ có cảm giác như đang hòa mình trọn vẹn vào giữa không gian non nước mênh mông, đón nhận những cơn gió núi lồng lộng mát rượi thổi qua mặt hồ. • Hậu cảnh đồi núi trập trùng: Phía sau cây cầu là những triền đồi xanh mướt của Xã Ô Lâm, những rặng cây thốt nốt cao vút và những chiếc thuyền gỗ nhỏ neo đậu ven bờ tạo nên khung cảnh bình yên tựa chốn thôn dã Bắc Âu.  3. Trải Nghiệm Kết Hợp Check-in &amp; Thưởng Thức Ẩm Thực • Chụp ảnh sống ảo phong cách nàng thơ: Cầu gỗ Ô Thum là tọa độ lý tưởng cho các bộ ảnh dã ngoại mang phong cách vintage, váy maxi bay bổng hoặc trang phục truyền thống miền Tây. • Thưởng thức gà đốt lá chúc trứ danh: Ngay quanh khu vực hồ và cầu gỗ là "thủ phủ" của món Gà Đốt Ô Thum nổi tiếng khắp miền Tây (các quán Siêu Bó, Thảo Nguyên, Kim Suổl...). Du khách vừa có thể chụp ảnh ngắm cảnh hồ, vừa thưởng thức gà đốt nóng hổi chấm muối ớt lá chúc cay nồng.  4. Hướng Dẫn Khung Giờ &amp; Góc Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm vàng khi ánh mặt trời đỏ ối dần lặn sau rặng núi xa, nhuộm hồng cả mặt nước hồ Ô Thum và tạo nên những bức ảnh ngược sáng lung linh tuyệt mỹ. • Sáng sớm thanh bình (07:00 – 08:30): Mặt hồ phẳng lặng không một gợn sóng, sương sớm bảng lảng trôi trên mặt nước mang lại cảm giác tĩnh tại, an yên. • Góc chụp gợi ý: Chụp từ bờ hồ lấy trọn chiều dài của cây cầu gỗ với người mẫu đứng ở mút cầu ngắm nhìn ra xa; hoặc chụp cận cảnh với hậu cảnh mặt nước hồ xanh ngọc bích.  5. Lưu Ý Thực Địa Cho Du Khách • An toàn bên mép nước: Cầu gỗ nằm trên mặt hồ nước sâu, du khách khi di chuyển chụp ảnh cần cẩn thận giữ thăng bằng, không chen lấn xô đẩy và đặc biệt chú ý nếu có trẻ nhỏ đi cùng. • Giữ gìn cảnh quan: Tuyệt đối không vứt rác, vỏ chai hay thức ăn thừa xuống lòng hồ Ô Thum. • Chi phí: Thường miễn phí tham quan chụp ảnh nếu bạn sử dụng dịch vụ ăn uống tại các quán ăn ven hồ, hoặc phí tham quan nhẹ khoảng 10.000đ/lượt.</t>
         </is>
       </c>
-      <c r="O133" s="4" t="inlineStr"/>
-      <c r="P133" s="5" t="inlineStr">
+      <c r="O134" s="4" t="inlineStr"/>
+      <c r="P134" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4152,105.0182</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="24" customHeight="1">
-      <c r="A134" s="6" t="n">
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>b1d52ac4-khu-ẩm-thực-chợ-đêm-</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>Khu Ẩm Thực Chợ Đêm Tri Tôn</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr"/>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="D135" s="7" t="inlineStr"/>
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
+      <c r="F135" s="7" t="inlineStr">
         <is>
           <t>Chợ</t>
         </is>
       </c>
-      <c r="G134" s="6" t="n">
+      <c r="G135" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H134" s="6" t="inlineStr">
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>10.4138, 105.0075</t>
         </is>
       </c>
-      <c r="I134" s="7" t="inlineStr">
+      <c r="I135" s="7" t="inlineStr">
         <is>
           <t>Quảng trường Quảng Tế, Khóm 3, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J134" s="7" t="inlineStr"/>
-      <c r="K134" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L134" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M134" s="7" t="inlineStr">
+      <c r="J135" s="7" t="inlineStr"/>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
         <is>
           <t>Phố ẩm thực đêm sôi động bậc nhất Tri Tôn. Nơi hội tụ các món ngon bản địa như cháo bò trái trúc, bánh xèo tép đồng, bánh bò thốt nốt nướng than củi, chè thốt nốt và bún cá củ ngải Khmer thanh ngọt (không mắm) Khmer.</t>
         </is>
       </c>
-      <c r="N134" s="7" t="inlineStr">
+      <c r="N135" s="7" t="inlineStr">
         <is>
           <t>Khu Ẩm Thực Chợ Đêm &amp; Phố Đi Bộ Tri Tôn – Tâm Điểm Vui Chơi, Ăn Vặt Sôi Động Về Đêm Xứ Núi  Khi ánh hoàng hôn buông xuống sau dãy núi Cô Tô và Tà Pạ, Thị trấn Tri Tôn khoác lên mình một diện mạo hoàn toàn mới đầy sức sống với Khu Ẩm Thực Chợ Đêm và Quảng Trường Phố Đi Bộ Trung Tâm. Đây là nơi hội tụ đông đảo người dân địa phương, bạn trẻ và du khách thập phương đến dạo mát, thưởng thức hàng chục món ăn vặt đường phố hấp dẫn và cảm nhận nhịp sống đêm thân thiện, ấm áp của vùng Bảy Núi.  1. Vị Trí &amp; Không Gian Khu Chợ Đêm • Vị trí hành chính: Khu vực Quảng trường Trung tâm Tri Tôn và dọc tuyến đường Trần Hưng Đạo – đường 3 Tháng 2, Thị trấn Tri Tôn. • Không gian thoáng đãng: Nằm cạnh quảng trường công viên cây xanh rộng rãi, chợ đêm có không gian mở lộng gió núi mát rượi, vỉa hè rộng rãi bố trí hàng chục quầy ẩm thực sáng rực ánh đèn lung linh.  2. Thiên Đường Ăn Vặt &amp; Nước Uống Bản Địa Độc Đáo • Nước thốt nốt tươi ướp lạnh &amp; Thốt nốt sữa: Món giải khát "quốc dân" của Tri Tôn với nước thốt nốt ngọt lịm từ vòi hoa, kèm cùi thốt nốt dẻo giòn sần sật ướp trong xô đá mát lạnh, hoặc thốt nốt dầm sữa tươi béo ngậy. • Bánh kẹp nướng thốt nốt &amp; Bánh cống giòn rụm: Mùi thơm ngào ngạt của bột gạo, nước cốt dừa và đường thốt nốt nướng trên khuôn gang lan tỏa khắp các góc phố. • Xiên que nướng sa tế &amp; Bắp nướng mỡ hành: Đầy đủ các loại xiên thịt nướng, chân gà nướng muối ớt, bắp nướng chan mỡ hành thơm phức nóng hổi vừa thổi vừa ăn. • Chè thốt nốt &amp; Sâm bổ lượng cốt dừa: Những ly chè mát lạnh với đủ loại thạch, hạt sen, nhãn nhục và cùi thốt nốt ngọt thanh giúp giải nhiệt sau một ngày dài leo núi trekking.  3. Không Gian Giao Lưu Văn Hóa &amp; Đời Sống Về Đêm • Giao lưu văn hóa cộng đồng: Chợ đêm là nơi bạn dễ dàng bắt gặp nụ cười đôn hậu, hiếu khách của bà con người Kinh, Khmer và Hoa cùng chung sống hòa thuận. • Khu vui chơi trẻ em &amp; Phố đi bộ: Quảng trường trung tâm thường xuyên có các hoạt động vui chơi như xe điện mini, trượt patin, tô tượng và biểu diễn âm nhạc đường phố vào dịp cuối tuần.  4. Hướng Dẫn Trải Nghiệm Trọn Vẹn • Khung giờ vàng: 18:30 – 21:30 là thời điểm chợ đêm nhộn nhịp và đông vui nhất. • Gợi ý lịch trình buổi tối: Sau khi ngắm hoàng hôn tại Hồ Tà Pạ hoặc Đu đủ đâm RiNa, bạn có thể về khách sạn tắm rửa nghỉ ngơi rồi ra chợ đêm Tri Tôn dạo mát, uống nước thốt nốt và thưởng thức đồ nướng.  5. Thông Tin Cần Thiết Cho Du Khách • Giờ hoạt động: 16:30 – 22:30 hàng đêm. • Mức giá: Cực kỳ bình dân, chỉ từ 10.000đ – 35.000đ cho mỗi món ăn vặt hoặc ly nước giải khát. • Gửi xe: Có bãi giữ xe máy có người trông coi ngay đầu quảng trường với giá 5.000đ/lượt.</t>
         </is>
       </c>
-      <c r="O134" s="7" t="inlineStr"/>
-      <c r="P134" s="8" t="inlineStr">
+      <c r="O135" s="7" t="inlineStr"/>
+      <c r="P135" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4138,105.0075</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="3" t="n">
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>cee4075f-lang-lang-coffee-&amp;-t</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>Lang Lang Coffee &amp; Tea</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr"/>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr"/>
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F135" s="4" t="n"/>
-      <c r="G135" s="3" t="n">
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>10.412, 105.008</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>78 Đường Trần Hưng Đạo, Khóm 3, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J135" s="4" t="inlineStr"/>
-      <c r="K135" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M135" s="4" t="inlineStr">
+      <c r="J136" s="4" t="inlineStr"/>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M136" s="4" t="inlineStr">
         <is>
           <t>Quán cà phê và trà trái cây check-in hiện đại tại Thị trấn Tri Tôn. Không gian máy lạnh kết hợp ban công sân vườn ngắm phố đêm, phục vụ trà thốt nốt tươi và bánh ngọt.</t>
         </is>
       </c>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>Lang Lang Coffee &amp; Tea – Tiệm Trà Tone Trắng Hàn Quốc Xinh Xắn &amp; Bánh Ngọt Nướng Mỗi Ngày  Nằm trên đường Trần Hưng Đạo tại Thị trấn Tri Tôn, Lang Lang Coffee &amp; Tea là một trong những quán trà và cà phê mang phong cách Hàn Quốc ngọt ngào, tinh tế với tone màu trắng kem pastel, ngập tràn ánh sáng tự nhiên và nhiều góc check-in dễ thương cho giới trẻ.  1. Vị Trí &amp; Không Gian Pastel Dễ Thương • Vị trí: 78 Đường Trần Hưng Đạo, Khóm 3, Thị trấn Tri Tôn, tỉnh An Giang. • Thiết kế: Tone trắng kem nhẹ nhàng, nội thất gỗ sồi sáng màu, gương soi sống ảo toàn thân và ánh sáng dịu mắt.  2. Thực Đơn Bánh &amp; Trà Trái Cây Đa Dạng • Bánh ngọt tươi nướng trong ngày: Croissant bơ tỏi, bánh bông lan trứng muối, tiramisu mềm béo. • Trà trái cây &amp; Trà sữa béo ngậy: Trà dâu tây tươi, trà ổi hồng macchiato, trà sữa kem cheese.  3. Thông Tin Chi Tiết • Giờ mở cửa: 07:30 – 22:00 mỗi ngày. • Mức giá: 22.000đ – 45.000đ / món.</t>
         </is>
       </c>
-      <c r="O135" s="4" t="inlineStr"/>
-      <c r="P135" s="5" t="inlineStr">
+      <c r="O136" s="4" t="inlineStr"/>
+      <c r="P136" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.412,105.008</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="24" customHeight="1">
-      <c r="A136" s="6" t="n">
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B137" s="7" t="inlineStr">
         <is>
           <t>d2759ee4-ny-coffee-&amp;-tea-tri-</t>
         </is>
       </c>
-      <c r="C136" s="7" t="inlineStr">
+      <c r="C137" s="7" t="inlineStr">
         <is>
           <t>NY Coffee &amp; Tea Tri Tôn</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr"/>
-      <c r="E136" s="7" t="inlineStr">
+      <c r="D137" s="7" t="inlineStr"/>
+      <c r="E137" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F136" s="7" t="n"/>
-      <c r="G136" s="6" t="n">
+      <c r="F137" s="7" t="n"/>
+      <c r="G137" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>10.414, 105.006</t>
         </is>
       </c>
-      <c r="I136" s="7" t="inlineStr">
+      <c r="I137" s="7" t="inlineStr">
         <is>
           <t>66 Đường Trần Phú, Khóm 2, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J136" s="7" t="inlineStr"/>
-      <c r="K136" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L136" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M136" s="7" t="inlineStr">
+      <c r="J137" s="7" t="inlineStr"/>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="inlineStr">
         <is>
           <t>Quán trà sữa &amp; đồ uống hiện đại tại trung tâm Tri Tôn, mở muộn với menu đa dạng trà trái cây nhiệt đới, kem thốt nốt và đồ ăn vặt.</t>
         </is>
       </c>
-      <c r="N136" s="7" t="inlineStr">
+      <c r="N137" s="7" t="inlineStr">
         <is>
           <t>Quán trà sữa &amp; đồ uống hiện đại tại trung tâm Tri Tôn, mở muộn với menu đa dạng trà trái cây nhiệt đới, kem thốt nốt và đồ ăn vặt.</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr"/>
-      <c r="P136" s="8" t="inlineStr">
+      <c r="O137" s="7" t="inlineStr"/>
+      <c r="P137" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.414,105.006</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="3" t="n">
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>d1bd3ece-quy-coffee-house-tri</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>Quy Coffee House Tri Tôn (Quý's Coffee)</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr"/>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="D138" s="4" t="inlineStr"/>
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F137" s="4" t="inlineStr">
+      <c r="F138" s="4" t="inlineStr">
         <is>
           <t>Quán Cà Phê</t>
         </is>
       </c>
-      <c r="G137" s="3" t="n">
+      <c r="G138" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>10.413, 105.007</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr">
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>34 Đường Nguyễn Trãi, Khóm 3, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J137" s="4" t="inlineStr"/>
-      <c r="K137" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M137" s="4" t="inlineStr">
+      <c r="J138" s="4" t="inlineStr"/>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M138" s="4" t="inlineStr">
         <is>
           <t>Quán cà phê phong cách mộc gỗ ấm cúng tại Thị trấn Tri Tôn. Điểm hẹn quen thuộc của giới trẻ địa phương vào buổi tối với cà phê pha máy và đêm nhạc mộc cuối tuần.</t>
         </is>
       </c>
-      <c r="N137" s="4" t="inlineStr">
+      <c r="N138" s="4" t="inlineStr">
         <is>
           <t>Quy Coffee House Tri Tôn (Quý's Coffee) – Không Gian Retro Hoài Niệm &amp; Cà Phê Phin Đậm Đà  Tọa lạc tại số 34 đường Nguyễn Trãi ở trung tâm Thị trấn Tri Tôn, Quy Coffee House (thường gọi là Quý's Coffee) là địa chỉ cà phê quen thuộc và lâu năm của người dân địa phương. Quán mang phong cách Retro cổ điển, ấm cúng với những bản nhạc Trịnh êm dịu và ly cà phê pha phin truyền thống đậm đặc.  1. Vị Trí &amp; Không Gian Retro Cổ Điển • Vị trí: 34 Đường Nguyễn Trãi, Khóm 3, Thị trấn Tri Tôn, tỉnh An Giang. • Không gian hoài niệm: Bàn ghế gỗ xưa, tranh ảnh tư liệu đen trắng về vùng đất Bảy Núi và tiếng nhạc acoustic du dương.  2. Cà Phê Đậm Vị Nam Bộ • Cà phê hạt rang mộc: Cà phê nguyên chất rang xay tại chỗ, pha phin nhỏ giọt đậm đà hương thơm nồng nàn. • Các loại nước ép &amp; Sinh tố nhiệt đới: Nước ép cóc, ổi, cam tươi nguyên chất.  3. Thông Tin Quán • Giờ mở cửa: 06:00 – 21:30 mỗi ngày. • Mức giá: 18.000đ – 35.000đ / ly.</t>
         </is>
       </c>
-      <c r="O137" s="4" t="inlineStr"/>
-      <c r="P137" s="5" t="inlineStr">
+      <c r="O138" s="4" t="inlineStr"/>
+      <c r="P138" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.413,105.007</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="24" customHeight="1">
-      <c r="A138" s="6" t="n">
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B139" s="7" t="inlineStr">
         <is>
           <t>bfa8bcbf-tiệm-cà-phê-nhà-quê</t>
         </is>
       </c>
-      <c r="C138" s="7" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>Tiệm Cà Phê Nhà Quê Tri Tôn</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr"/>
-      <c r="E138" s="7" t="inlineStr">
+      <c r="D139" s="7" t="inlineStr"/>
+      <c r="E139" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
+      <c r="F139" s="7" t="inlineStr">
         <is>
           <t>Quán Cà Phê</t>
         </is>
       </c>
-      <c r="G138" s="6" t="n">
+      <c r="G139" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H139" s="6" t="inlineStr">
         <is>
           <t>10.411, 105.005</t>
         </is>
       </c>
-      <c r="I138" s="7" t="inlineStr">
+      <c r="I139" s="7" t="inlineStr">
         <is>
           <t>Chân Cầu Số 10, Khóm 6, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J138" s="7" t="inlineStr"/>
-      <c r="K138" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M138" s="7" t="inlineStr">
+      <c r="J139" s="7" t="inlineStr"/>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M139" s="7" t="inlineStr">
         <is>
           <t>Không gian cà phê sân vườn hoài niệm tại Tri Tôn, rợp bóng cây xanh và yên tĩnh để trò chuyện buổi tối.</t>
         </is>
       </c>
-      <c r="N138" s="7" t="inlineStr">
+      <c r="N139" s="7" t="inlineStr">
         <is>
           <t>Tiệm Cà Phê Nhà Quê Tri Tôn – Ngôi Nhà Gỗ Vintage Giữa Đồng &amp; Chòi "Chữa Lành" Bình Yên  Tọa lạc tại khu vực Cầu Số 10 thuộc Xã Tà Đảnh giáp ranh Thị trấn Tri Tôn, Tiệm Cà Phê Nhà Quê là một điểm đến mang đậm phong cách vintage hoài niệm, bình yên giữa bạt ngàn đồng ruộng. Ngôi nhà gỗ cổ kính kết hợp cùng cây cầu ván gỗ dài dẫn ra chiếc chòi nhỏ giữa đồng đã trở thành tọa độ "chữa lành" tâm hồn quen thuộc của giới trẻ và du khách yêu thích vẻ đẹp an nhiên, mộc mạc.  1. Vị Trí &amp; Không Gian Nhà Gỗ Hoài Niệm • Vị trí hành chính: Khu vực Cầu Số 10, Khóm 6, Thị trấn Tri Tôn (giáp Xã Tà Đảnh), tỉnh An Giang. • Kiến trúc nhà gỗ Nam Bộ: Quán được dựng theo lối nhà rường gỗ cổ xưa với mái ngói rêu phong, cửa sổ lá sách bằng gỗ mộc và các vật dụng trang trí nhuốm màu thời gian như máy cassette cổ, bàn máy may, đèn bão và tivi đen trắng. • Chòi lá "chữa lành" giữa ruộng: Từ gian nhà chính có một cây cầu ván gỗ dẫn thẳng ra một chiếc chòi lá nhỏ đơn độc giữa cánh đồng lúa, nơi du khách có thể ngồi buông thõng chân ngắm gió đồng thổi lồng lộng.  2. Cảnh Quan Đồng Quê Thơ Mộng • Không gian tĩnh lặng tuyệt đối: Tách biệt hoàn toàn khỏi tiếng còi xe phố thị, đến đây bạn chỉ nghe thấy tiếng chim hót, tiếng ếch nhái râm ran và tiếng gió lướt qua từng kẽ lá. • Hàng cây thốt nốt soi bóng: Xa xa quanh quán là những hàng cây thốt nốt cổ thụ cao vút vươn mình lên nền trời trong xanh.  3. Thực Đơn Dân Dã &amp; Trà Thảo Mộc • Cà phê phin bơ truyền thống: Cà phê được pha bằng phin nhôm truyền thống, thơm lừng mùi bơ và đậm đà vị đắng nguyên chất. • Trà thảo mộc &amp; Nước mát quê: Trà hoa cúc mật ong, nước sâm rong biển, nước dừa tươi nguyên trái và sữa đậu nành lá dứa nấu thủ công. • Bánh quê ăn kèm: Bánh chuối hấp nước cốt dừa, bánh da lợn, khoai mì luộc chấm muối mè.  4. Hướng Dẫn Check-in Sống Ảo • Góc ban công nhà gỗ: Ngồi bên khung cửa sổ gỗ ngắm nhìn ra cánh đồng lúa xanh. • Cầu ván gỗ &amp; Chòi giữa đồng: Khung giờ 16:00 – 17:30 chiều là lúc ánh nắng xiên tạo nên tone màu ảnh vintage cổ điển cực kỳ xuất sắc.  5. Thông Tin Phục Vụ • Giờ mở cửa: 07:00 – 18:30 hàng ngày. • Mức giá bình dân: 18.000đ – 35.000đ / món.</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr"/>
-      <c r="P138" s="8" t="inlineStr">
+      <c r="O139" s="7" t="inlineStr"/>
+      <c r="P139" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.411,105.005</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="24" customHeight="1">
-      <c r="A139" s="3" t="n">
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>tritoni</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>Tritoni Coffee &amp; Tea (Cà Phê Tritoni)</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr"/>
-      <c r="E139" s="4" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr"/>
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F139" s="4" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>cafe</t>
         </is>
       </c>
-      <c r="G139" s="3" t="n">
+      <c r="G140" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>10.4238852, 105.001011</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>92 Trần Hưng Đạo, Khóm 4, Thị trấn Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J139" s="4" t="inlineStr"/>
-      <c r="K139" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr">
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>Điểm đến 'Tritoni' là một tọa độ không nên bỏ lỡ khi ghé thăm Tri Tôn. (Đặc trưng: hoành tráng hơn cả thành phố).</t>
         </is>
       </c>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>1. Tổng quan Tritoni Coffee &amp; Tea là điểm hẹn cà phê và giải khát hiện đại nổi bật bậc nhất ngay trung tâm Thị trấn Tri Tôn (số 92 Trần Hưng Đạo, cách Chùa Xvayton 300m). Quán có không gian máy lạnh tầng trệt và ban công tầng lầu thoáng đãng nhìn ra trục đường sầm uất.  2. Menu &amp; Trải nghiệm • Phục vụ cà phê pha máy, cà phê truyền thống, trà sữa trân châu, trà trái cây nhiệt đới, matcha và các loại bánh ngọt giải khát. • Mức giá: 20.000đ – 45.000đ/món. • Giờ mở cửa: 06:30 – 22:00 hàng ngày.</t>
         </is>
       </c>
-      <c r="O139" s="4" t="inlineStr"/>
-      <c r="P139" s="5" t="inlineStr">
+      <c r="O140" s="4" t="inlineStr"/>
+      <c r="P140" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4238852,105.001011</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="6" t="n">
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>3ef4f129-quán-cà-phê-&amp;-điểm-c</t>
         </is>
       </c>
-      <c r="C140" s="7" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
         <is>
           <t>Quán Cà Phê &amp; Điểm Check-in Bờ Hồ Ô Tà Lọt</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr"/>
-      <c r="E140" s="7" t="inlineStr">
+      <c r="D141" s="7" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>Xã An Tức</t>
         </is>
       </c>
-      <c r="F140" s="7" t="n"/>
-      <c r="G140" s="6" t="n">
+      <c r="F141" s="7" t="n"/>
+      <c r="G141" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="H141" s="6" t="inlineStr">
         <is>
           <t>10.478, 104.962</t>
         </is>
       </c>
-      <c r="I140" s="7" t="inlineStr">
+      <c r="I141" s="7" t="inlineStr">
         <is>
           <t>Khu vực Hồ Ô Tà Lọt, Xã An Hảo, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J140" s="7" t="inlineStr"/>
-      <c r="K140" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L140" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M140" s="7" t="inlineStr">
+      <c r="J141" s="7" t="inlineStr"/>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M141" s="7" t="inlineStr">
         <is>
           <t>Quán cà phê chòi gỗ mộc mạc bên bờ Hồ Ô Tà Lọt, xã An Tức. Điểm ngắm cảnh hồ nước phẳng lặng giữa thung lũng đồi núi hùng vĩ.</t>
         </is>
       </c>
-      <c r="N140" s="7" t="inlineStr">
+      <c r="N141" s="7" t="inlineStr">
         <is>
           <t>Quán cà phê chòi gỗ mộc mạc bên bờ Hồ Ô Tà Lọt, xã An Tức. Điểm ngắm cảnh hồ nước phẳng lặng giữa thung lũng đồi núi hùng vĩ.</t>
         </is>
       </c>
-      <c r="O140" s="7" t="inlineStr"/>
-      <c r="P140" s="8" t="inlineStr">
+      <c r="O141" s="7" t="inlineStr"/>
+      <c r="P141" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.478,104.962</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="24" customHeight="1">
-      <c r="A141" s="3" t="n">
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>ca-phe-suoi-da-o-ta-soc</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>Cà Phê Suối Đá Ô Tà Sóc</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr"/>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr"/>
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>Xã Lương Phi</t>
         </is>
       </c>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="3" t="n">
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>10.451, 104.931</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr">
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>Khu di tích Ô Tà Sóc, Xã Lương Phi, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J141" s="4" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="J142" s="4" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>Khám phá vẻ đẹp kỳ vĩ của Tri Tôn - Bảy Núi qua hương vị bản địa và niềm tự hào cà phê Việt.</t>
         </is>
       </c>
-      <c r="N141" s="4" t="inlineStr">
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>Cà Phê Suối Đá Ô Tà Sóc – Không Gian Rừng Tầm Vông &amp; Suối Đá Mát Lạnh Dưới Chân Núi Dài  Tọa lạc trong khuôn viên Khu du lịch Căn cứ Ô Tà Sóc thuộc Xã Lương Phi, Cà Phê Suối Đá Ô Tà Sóc mang lại trải nghiệm thưởng thức cà phê độc đáo ngay bên dòng suối đá tự nhiên tuôn chảy róc rách dưới tán rừng tầm vông xanh ngắt, nhiệt độ mát mẻ quanh năm.  1. Vị Trí &amp; Không Gian Rừng Suối • Vị trí: Khu du lịch Căn cứ Ô Tà Sóc, Xã Lương Phi, tỉnh An Giang. • Không gian mát lạnh: Bàn ghế gỗ đặt trực tiếp trên các phiến đá ven suối, tiếng nước chảy róc rách hòa cùng tiếng gió xào xạc qua vòm tre tầm vông.  2. Trải Nghiệm Dã Ngoại &amp; Thư Giãn • Ngâm chân nước suối mát lạnh: Vừa nhâm nhi tách cà phê nóng vừa ngâm chân dưới dòng suối đá tự nhiên xua tan mọi mệt mỏi. • Đồ uống phong phú: Cà phê phin, trà đào cam sả, dừa tươi nguyên trái.  3. Thông Tin Quán • Giờ mở cửa: 07:00 – 17:30 mỗi ngày. • Mức giá: 20.000đ – 40.000đ / món.</t>
         </is>
       </c>
-      <c r="O141" s="4" t="inlineStr"/>
-      <c r="P141" s="5" t="inlineStr">
+      <c r="O142" s="4" t="inlineStr"/>
+      <c r="P142" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.451,104.931</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="24" customHeight="1">
-      <c r="A142" s="6" t="n">
+    <row r="143" ht="24" customHeight="1">
+      <c r="A143" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>ca-phe-thot-not-ta-pa-view</t>
         </is>
       </c>
-      <c r="C142" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>Cà Phê Thốt Nốt Tà Pạ View</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr"/>
-      <c r="E142" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F142" s="7" t="n"/>
-      <c r="G142" s="6" t="n">
+      <c r="F143" s="7" t="n"/>
+      <c r="G143" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H143" s="6" t="inlineStr">
         <is>
           <t>10.415, 105.003</t>
         </is>
       </c>
-      <c r="I142" s="7" t="inlineStr">
+      <c r="I143" s="7" t="inlineStr">
         <is>
           <t>Chân đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J142" s="7" t="inlineStr"/>
-      <c r="K142" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L142" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M142" s="7" t="inlineStr">
+      <c r="J143" s="7" t="inlineStr"/>
+      <c r="K143" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M143" s="7" t="inlineStr">
         <is>
           <t>Khám phá vùng đất Bảy Núi với Cà Phê Thốt Nốt Tà Pạ View, nơi kết hợp ẩm thực, văn hóa và thiên nhiên.</t>
         </is>
       </c>
-      <c r="N142" s="7" t="inlineStr">
+      <c r="N143" s="7" t="inlineStr">
         <is>
           <t>Cà Phê Thốt Nốt Tà Pạ View – Chòi Lá Mộc Mạc View Chùa Núi Tà Pạ &amp; Đồng Lúa Ô Vuông  Nằm ngay dưới chân Đồi Tà Pạ thuộc Xã Núi Tô, Cà Phê Thốt Nốt Tà Pạ View là điểm dừng chân bình dị nơi du khách có thể ngồi dưới những chòi lá thốt nốt râm mát, thưởng thức ly nước thốt nốt tươi ngọt mát và ngắm nhìn ngôi chùa Khmer Tà Pạ cổ kính uy nghi trên đỉnh đồi.  1. Vị Trí &amp; Tầm Nhìn Ngắm Chùa Tà Pạ • Vị trí: Chân đồi Tà Pạ, Xã Núi Tô, tỉnh An Giang. • Tầm nhìn trực diện: Ngắm nhìn toàn cảnh cánh đồng lúa Tà Pạ ô vuông bàn cờ và mái chùa Tà Pạ chóp nhọn vàng rực vươn cao trên nền trời.  2. Thức Uống Bản Địa Nguyên Chất • Nước thốt nốt tươi lấy từ vòi hoa: Nước ngọt lịm tự nhiên, kèm cùi thốt nốt dẻo giòn ướp lạnh. • Cà phê đá miền Tây: Đậm đà, thơm béo bùi vị quê hương.  3. Thông Tin Phục Vụ • Giờ mở cửa: 06:30 – 18:00 mỗi ngày. • Mức giá: 15.000đ – 30.000đ / ly.</t>
         </is>
       </c>
-      <c r="O142" s="7" t="inlineStr"/>
-      <c r="P142" s="8" t="inlineStr">
+      <c r="O143" s="7" t="inlineStr"/>
+      <c r="P143" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.415,105.003</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="24" customHeight="1">
-      <c r="A143" s="3" t="n">
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>b56c95ef-mây-coffee-&amp;-tea-hồ-</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>Mây Coffee &amp; Tea Hồ Soài Chék (Mây Sơn Garden)</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr"/>
-      <c r="E143" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr"/>
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F143" s="4" t="n"/>
-      <c r="G143" s="3" t="n">
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="H143" s="3" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>10.4165, 105.0185</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr">
+      <c r="I144" s="4" t="inlineStr">
         <is>
           <t>Ven bờ Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J143" s="4" t="inlineStr"/>
-      <c r="K143" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M143" s="4" t="inlineStr">
+      <c r="J144" s="4" t="inlineStr"/>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M144" s="4" t="inlineStr">
         <is>
           <t>Quán cà phê ngắm cảnh ven Hồ Soài Chek, đón gió hồ trong lành và phục vụ đồ uống thư giãn buổi tối.</t>
         </is>
       </c>
-      <c r="N143" s="4" t="inlineStr">
+      <c r="N144" s="4" t="inlineStr">
         <is>
           <t>Mây Coffee &amp; Tea Hồ Soài Chék – Quán Cà Phê Sân Vườn Ôm Trọn Bờ Hồ Ngắm Hoàng Hôn Nước Biếc  Nằm sát mép bờ hồ nước ngọt Soài Chék thuộc Xã Núi Tô, Mây Coffee &amp; Tea (Mây Sơn Garden) là một trong những quán cà phê sân vườn có vị trí ngắm mặt nước hồ đẹp nhất của Tri Tôn. Quán sở hữu không gian mở lộng gió nhìn thẳng ra lòng hồ phẳng lặng và triền núi Cô Tô xanh biếc phía sau.  1. Vị Trí &amp; Không Gian Bên Mép Nước • Vị trí: Ven bờ Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, tỉnh An Giang. • Sân vườn sát mép hồ: Bàn ghế gỗ mộc mạc đặt dưới tán cây râm mát, sát bờ kè hồ nước trong xanh.  2. Điểm Ngắm Hoàng Hôn &amp; Săn Mây • Săn mây sáng sớm: Mặt hồ phẳng lặng in bóng mây bay lượn trên nền trời. • Hoàng hôn rực rỡ (16:30 – 17:30): Ánh hoàng hôn phản chiếu lung linh trên mặt hồ tạo nên không gian vô cùng lãng mạn.  3. Thông Tin Quán • Giờ mở cửa: 07:00 – 18:30 hàng ngày. • Mức giá: 20.000đ – 40.000đ / ly.</t>
         </is>
       </c>
-      <c r="O143" s="4" t="inlineStr"/>
-      <c r="P143" s="5" t="inlineStr">
+      <c r="O144" s="4" t="inlineStr"/>
+      <c r="P144" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4165,105.0185</t>
         </is>
       </c>
     </row>
-    <row r="144"/>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="13" t="inlineStr">
+    <row r="145"/>
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>🏡 VI. LƯU TRÚ, HOMESTAY &amp; KHÁCH SẠN — TỔNG SỐ: 7 ĐỊA ĐIỂM</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="24" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Mã ID</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
         <is>
           <t>Tên Địa Điểm</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tên Tiếng Anh (EN)</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Xã / Thị Trấn</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Phân Loại Phụ</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Đánh Giá (⭐)</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Tọa Độ GPS (Lat, Lng)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Địa Chỉ Thực Địa</t>
         </is>
       </c>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Điện Thoại / Hotline</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K147" s="2" t="inlineStr">
         <is>
           <t>Mức Giá</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="L147" s="2" t="inlineStr">
         <is>
           <t>Giờ Mở Cửa / Giờ Vàng</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr">
+      <c r="M147" s="2" t="inlineStr">
         <is>
           <t>Mô Tả Tổng Quan</t>
         </is>
       </c>
-      <c r="N146" s="2" t="inlineStr">
+      <c r="N147" s="2" t="inlineStr">
         <is>
           <t>Sự Tích &amp; Di Sản Thực Địa</t>
         </is>
       </c>
-      <c r="O146" s="2" t="inlineStr">
+      <c r="O147" s="2" t="inlineStr">
         <is>
           <t>Mẹo Thực Địa</t>
         </is>
       </c>
-      <c r="P146" s="2" t="inlineStr">
+      <c r="P147" s="2" t="inlineStr">
         <is>
           <t>Link Google Maps Dẫn Đường</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="24" customHeight="1">
-      <c r="A147" s="3" t="n">
+    <row r="148" ht="24" customHeight="1">
+      <c r="A148" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>b62d0291-nhà-nghi-&amp;-khách-sạn</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Nhà Nghỉ &amp; Khách Sạn Triệu Gia Tri Tôn</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr"/>
-      <c r="E147" s="4" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr"/>
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F147" s="4" t="n"/>
-      <c r="G147" s="3" t="n">
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>10.415, 105.008</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr">
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>Đường Trần Hưng Đạo, Khóm 3, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J147" s="4" t="inlineStr"/>
-      <c r="K147" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M147" s="4" t="inlineStr">
+      <c r="J148" s="4" t="inlineStr"/>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="inlineStr">
         <is>
           <t>Khách sạn phòng sạch sẽ tiện nghi trung tâm Thị trấn Tri Tôn.</t>
         </is>
       </c>
-      <c r="N147" s="4" t="inlineStr">
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>1. Tổng quan Nhà Nghi &amp; Khách Sạn Triệu Gia Tri Tôn là một địa điểm lý tưởng cho những ai yêu thích ẩm thực địa phương. Nằm ở trung tâm của Thị trấn Tri Tôn, An Giang, nhà hàng này mang đến một trải nghiệm ẩm thực tuyệt vời với đa dạng các món ăn truyền thống Việt Nam.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách nào, vì vậy chúng tôi sẽ cung cấp một số thông tin chung về địa điểm này. Nhà Nghi &amp; Khách Sạn Triệu Gia Tri Tôn có thể đáp ứng được nhu cầu của nhiều người với đa dạng các món ăn và dịch vụ. Tuy nhiên, chúng tôi không có thông tin cụ thể về ưu và nhược điểm của nhà hàng này.  3. Lời khuyên Nếu bạn đang tìm kiếm một địa điểm ẩm thực tốt ở Tri Tôn, An Giang, có thể bạn nên cân nhắc đến Nhà Nghi &amp; Khách Sạn Triệu Gia Tri Tôn. • Nhà hàng này mở cửa từ 08: 00 • đến 20: 00, cho phép bạn thưởng thức bữa sáng, trưa hoặc tối tại đây. Tuy nhiên, chúng tôi khuyên bạn nên kiểm tra giá cả trước khi đến để tránh bất ngờ.</t>
         </is>
       </c>
-      <c r="O147" s="4" t="inlineStr"/>
-      <c r="P147" s="5" t="inlineStr">
+      <c r="O148" s="4" t="inlineStr"/>
+      <c r="P148" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.415,105.008</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="24" customHeight="1">
-      <c r="A148" s="6" t="n">
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B149" s="7" t="inlineStr">
         <is>
           <t>nha-tro-quoc-tien</t>
         </is>
       </c>
-      <c r="C148" s="7" t="inlineStr">
+      <c r="C149" s="7" t="inlineStr">
         <is>
           <t>Nhà Trọ Quốc tiến</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr">
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F148" s="7" t="n"/>
-      <c r="G148" s="6" t="n">
+      <c r="F149" s="7" t="n"/>
+      <c r="G149" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="H149" s="6" t="inlineStr">
         <is>
           <t>10.4107275, 104.9037236</t>
         </is>
       </c>
-      <c r="I148" s="7" t="inlineStr">
+      <c r="I149" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J148" s="7" t="inlineStr"/>
-      <c r="K148" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L148" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M148" s="7" t="inlineStr">
+      <c r="J149" s="7" t="inlineStr"/>
+      <c r="K149" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M149" s="7" t="inlineStr">
         <is>
           <t>Khám phá Nhà Trọ Quốc Tiến – điểm dừng chân văn hóa độc đáo giữa lòng Bảy Núi hùng vĩ.</t>
         </is>
       </c>
-      <c r="N148" s="7" t="inlineStr"/>
-      <c r="O148" s="7" t="inlineStr"/>
-      <c r="P148" s="8" t="inlineStr">
+      <c r="N149" s="7" t="inlineStr"/>
+      <c r="O149" s="7" t="inlineStr"/>
+      <c r="P149" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.4107275,104.9037236</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="24" customHeight="1">
-      <c r="A149" s="3" t="n">
+    <row r="150" ht="24" customHeight="1">
+      <c r="A150" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>ac550583-soài-chek-homestay-&amp;</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>Soài Chek Homestay &amp; Coffee</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr"/>
-      <c r="E149" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr"/>
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F149" s="4" t="n"/>
-      <c r="G149" s="3" t="n">
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>10.411, 105.018</t>
         </is>
       </c>
-      <c r="I149" s="4" t="inlineStr">
+      <c r="I150" s="4" t="inlineStr">
         <is>
           <t>Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J149" s="4" t="inlineStr"/>
-      <c r="K149" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M149" s="4" t="inlineStr">
+      <c r="J150" s="4" t="inlineStr"/>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
         <is>
           <t>Khám phá Soài Chek Homestay &amp; Coffee - điểm đến lý tưởng cho những ai đam mê ẩm thực và không khí yên bình.</t>
         </is>
       </c>
-      <c r="N149" s="4" t="inlineStr">
+      <c r="N150" s="4" t="inlineStr">
         <is>
           <t>Soài • Chek Homestay &amp; Coffee: Điểm đến ẩm thực lý tưởng ở Bảy Núi  Tọa lạc tại Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang, Soài Chek Homestay &amp; Coffee là một điểm đến lý tưởng cho những ai đam mê ẩm thực và không khí yên bình. Với không gian rộng rãi và đẹp mắt, nơi đây là một điểm dừng chân tuyệt vời để thư giãn và thưởng thức những món ăn ngon.  Thực đơn đa dạng và phong phú  Soài Chek Homestay &amp; Coffee có một thực đơn đa dạng và phong phú, với các món ăn từ các vùng miền khác nhau. Mỗi món ăn đều được nấu theo công thức truyền thống và sử dụng nguyên liệu tươi ngon. Từ các món ăn truyền thống đến các món ăn hiện đại, nơi đây có thể đáp ứng mọi nhu cầu của khách hàng.  Lựa chọn tuyệt vời cho những ai yêu thích ẩm thực  Soài Chek Homestay &amp; Coffee không chỉ là một điểm đến ẩm thực lý tưởng mà còn là một lựa chọn tuyệt vời cho những ai yêu thích ẩm thực. Với không gian rộng rãi và đẹp mắt, nơi đây là một điểm dừng chân tuyệt vời để thư giãn và thưởng thức những món ăn ngon. Đừng bỏ qua cơ hội để khám phá Soài Chek Homestay &amp; Coffee - điểm đến ẩm thực lý tưởng ở Bảy Núi!</t>
         </is>
       </c>
-      <c r="O149" s="4" t="inlineStr"/>
-      <c r="P149" s="5" t="inlineStr">
+      <c r="O150" s="4" t="inlineStr"/>
+      <c r="P150" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.411,105.018</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="24" customHeight="1">
-      <c r="A150" s="6" t="n">
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>7440fc2d-tuyết-anh-homestay-&amp;</t>
         </is>
       </c>
-      <c r="C150" s="7" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>Tuyết Anh Homestay &amp; Coffee</t>
         </is>
       </c>
-      <c r="D150" s="7" t="inlineStr"/>
-      <c r="E150" s="7" t="inlineStr">
+      <c r="D151" s="7" t="inlineStr"/>
+      <c r="E151" s="7" t="inlineStr">
         <is>
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F150" s="7" t="n"/>
-      <c r="G150" s="6" t="n">
+      <c r="F151" s="7" t="n"/>
+      <c r="G151" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H150" s="6" t="inlineStr">
+      <c r="H151" s="6" t="inlineStr">
         <is>
           <t>10.411, 105.0095</t>
         </is>
       </c>
-      <c r="I150" s="7" t="inlineStr">
+      <c r="I151" s="7" t="inlineStr">
         <is>
           <t>86 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J150" s="7" t="inlineStr"/>
-      <c r="K150" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M150" s="7" t="inlineStr">
+      <c r="J151" s="7" t="inlineStr"/>
+      <c r="K151" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L151" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M151" s="7" t="inlineStr">
         <is>
           <t>Tìm kiếm sự ấm áp và bình yên tại Tuyết Anh Homestay &amp; Coffee - nơi đón chào bạn trong vùng đất Bảy Núi</t>
         </is>
       </c>
-      <c r="N150" s="7" t="inlineStr">
+      <c r="N151" s="7" t="inlineStr">
         <is>
           <t>Tuyết Anh Homestay &amp; Coffee – Sân Vườn Phong Cách Địa Trung Hải &amp; Hồ Cá Koi Thư Giãn  Nằm tại số 86 đường Nguyễn Thị Minh Khai tại Thị trấn Tri Tôn, Tuyết Anh Homestay &amp; Coffee là mô hình nghỉ dưỡng kết hợp không gian cà phê sân vườn hiện đại theo phong cách Địa Trung Hải với tường trắng, giàn hoa giấy rực rỡ và hồ cá Koi bơi lội tung tăng mát mắt.  1. Vị Trí &amp; Không Gian Sân Vườn Nghỉ Dưỡng • Vị trí: 86 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, tỉnh An Giang. • Thiết kế Địa Trung Hải: Tường sơn trắng muốt kết hợp các vòm cong mềm mại, hồ cá Koi lớn giữa sân và giàn hoa giấy hồng rực rỡ tỏa bóng mát.  2. Thức Uống Đa Dạng &amp; Thư Giãn • Đồ uống phong phú: Cà phê muối, trà dâu tằm, nước ép bưởi hồng và các dòng sinh tố bơ sáp béo ngậy. • Dịch vụ lưu trú: Phòng homestay tiện nghi, sạch sẽ, máy lạnh đầy đủ cho khách lưu trú qua đêm tại Tri Tôn.  3. Thông Tin Quán • Giờ mở cửa: 06:30 – 22:00 mỗi ngày. • Mức giá: 20.000đ – 45.000đ / ly.</t>
         </is>
       </c>
-      <c r="O150" s="7" t="inlineStr"/>
-      <c r="P150" s="8" t="inlineStr">
+      <c r="O151" s="7" t="inlineStr"/>
+      <c r="P151" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.411,105.0095</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="24" customHeight="1">
-      <c r="A151" s="3" t="n">
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>ho-soai-so</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>Hồ Soài So</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr"/>
-      <c r="E151" s="4" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
         <is>
           <t>Xã Cô Tô</t>
         </is>
       </c>
-      <c r="F151" s="4" t="n"/>
-      <c r="G151" s="3" t="n">
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H152" s="3" t="inlineStr">
         <is>
           <t>10.42, 105.0</t>
         </is>
       </c>
-      <c r="I151" s="4" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>Xã Cô Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J151" s="4" t="inlineStr"/>
-      <c r="K151" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L151" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M151" s="4" t="inlineStr">
+      <c r="J152" s="4" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="inlineStr">
         <is>
           <t>Viên Ngọc Bích Thanh Bình Dưới Chân Núi Cô Tô</t>
         </is>
       </c>
-      <c r="N151" s="4" t="inlineStr">
+      <c r="N152" s="4" t="inlineStr">
         <is>
           <t>Khám Phá Hồ Soài So – Viên Ngọc Bích Thanh Bình Dưới Chân Núi Cô Tô Nằm e ấp bên sườn phía Đông của ngọn Phụng Hoàng Sơn (Núi Cô Tô), Hồ Soài So là hồ nước nhân tạo lớn và nổi tiếng hàng đầu của vùng Thất Sơn – An Giang. Với cảnh sắc sơn thủy hữu tình, không khí trong lành và không gian tĩnh lặng, nơi đây là điểm dừng chân lý tưởng để dã ngoại, cắm trại và tìm lại sự thư thái cho tâm hồn.  1. Vị trí, • Quy mô &amp; Nguồn gốc • Vị trí: Thuộc xã Núi Tô, huyện Tri Tôn, tỉnh An Giang (cách trung tâm TP. Châu Đốc khoảng gần 50 km). • Quy mô: Hồ có diện tích mặt nước khoảng 5 ha với dung tích chứa lên tới hơn 400.000 m³, là một trong những hồ chứa nước ngọt nhân tạo lớn nhất vùng Bảy Núi. • Nguồn gốc: Hồ được xây dựng nhằm chặn dòng chảy tự nhiên của suối Vàng và suối Bạc từ trên đỉnh núi Cô Tô đổ xuống, phục vụ cung cấp nước tưới tiêu nông nghiệp và sinh hoạt cho người dân trong vùng.  2. Cảnh quan thiên nhiên nổi bật • Bức tranh sơn thủy hữu tình: Nước hồ trong veo, phẳng lặng như một tấm gương khổng lồ soi bóng đỉnh núi Cô Tô sừng sững. Tiếng suối Bạc róc rách hòa cùng tiếng gió xào xạc qua các rặng cây tạo nên thanh âm bình yên của chốn rừng núi. • Cây cầu ngắm cảnh ven hồ: Chạy men theo mép hồ có chiếc cầu nhỏ – vị trí hoàn hảo để thu trọn toàn cảnh núi non bao la, những khóm hoa dại ven đường và cảm nhận từng làn gió núi mát rượi. • Vườn cây ăn trái quanh hồ: Dạo sâu vào khuôn viên quanh hồ, bạn sẽ bắt gặp những vườn xoài cổ thụ, vườn điều và vườn rau xanh mướt của bà con địa phương. Vào mùa thu hoạch, bạn có thể xin phép tham quan và mua trái cây tươi hái tại vườn.  3. Thời điểm lý tưởng để ghé thăm • Mùa nước nổi (Tháng 9 – Tháng 11): Đây là thời điểm hồ đẹp nhất trong năm. Mực nước dâng cao, lòng hồ mở rộng mênh mông, trong xanh biếc và thi thoảng xuất hiện những chiếc thuyền con của người dân đánh cá, tạo nên nét đẹp đồng quê đậm chất Tây Nam Bộ. • Thời gian trong ngày:- Sáng sớm: Đón ánh nắng ban mai tinh khôi khi sương sớm còn vương trên mặt hồ. • Chiều tà (16h30 – 18h00): Chiêm ngưỡng hoàng hôn nhuộm sắc vàng hồng rực rỡ trên mặt nước lấp lánh.  4. Hoạt động trải nghiệm &amp; • Dã ngoại  Picnic thư giãn cuối tuần: Địa hình bằng phẳng rợp bóng mát dưới chân núi rất thích hợp để trải thảm dã ngoại cùng gia đình và bạn bè. • Cắm trại qua đêm: Tận hưởng đêm rừng thanh vắng, nghe tiếng côn trùng rả rích, ngắm bầu trời sao và đón bình minh thức giấc trên mặt hồ. • Kết hợp tham quan: Dễ dàng kết hợp viếng các ngôi chùa, miếu thanh tịnh quanh núi Cô Tô hoặc ghé thăm Khu du lịch Suối Vàng Soài So ngay cạnh.  5. Lưu • ý quan trọng cho chuyến đi • An toàn: Lòng hồ sâu và nước khá lạnh, du khách tuyệt đối không tự ý tắm hồ nếu không có trang bị bảo hộ an toàn. • Chuẩn bị cắm trại: Nếu ở lại qua đêm, cần chuẩn bị đầy đủ lều trại, đèn chiếu sáng, thuốc chống muỗi/côn trùng và áo ấm (ban đêm nhiệt độ ven chân núi hạ khá thấp). • Ý thức bảo vệ môi trường: Sau khi vui chơi hoặc ăn uống, hãy gom sạch toàn bộ rác thải để giữ gìn cảnh quan tự nhiên trong lành, sạch đẹp.</t>
         </is>
       </c>
-      <c r="O151" s="4" t="inlineStr"/>
-      <c r="P151" s="5" t="inlineStr">
+      <c r="O152" s="4" t="inlineStr"/>
+      <c r="P152" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.42,105.0</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="6" t="n">
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B152" s="7" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>78da5b5f-ruộng-coffee-&amp;-homes</t>
         </is>
       </c>
-      <c r="C152" s="7" t="inlineStr">
+      <c r="C153" s="7" t="inlineStr">
         <is>
           <t>RUỘNG Coffee &amp; Tea Tri Tôn</t>
         </is>
       </c>
-      <c r="D152" s="7" t="inlineStr"/>
-      <c r="E152" s="7" t="inlineStr">
+      <c r="D153" s="7" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr">
         <is>
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F152" s="7" t="n"/>
-      <c r="G152" s="6" t="n">
+      <c r="F153" s="7" t="n"/>
+      <c r="G153" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H152" s="6" t="inlineStr">
+      <c r="H153" s="6" t="inlineStr">
         <is>
           <t>10.415, 105.018</t>
         </is>
       </c>
-      <c r="I152" s="7" t="inlineStr">
+      <c r="I153" s="7" t="inlineStr">
         <is>
           <t>Đường vào Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J152" s="7" t="inlineStr"/>
-      <c r="K152" s="7" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L152" s="7" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M152" s="7" t="inlineStr">
+      <c r="J153" s="7" t="inlineStr"/>
+      <c r="K153" s="7" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M153" s="7" t="inlineStr">
         <is>
           <t>Quán cà phê giữa cánh đồng lúa Tà Pạ thơ mộng. Cầu gỗ dài lung linh ánh đèn về chiều tối, là nơi ngắm hoàng hôn buông sau rặng thốt nốt đẹp nhất Tri Tôn.</t>
         </is>
       </c>
-      <c r="N152" s="7" t="inlineStr">
+      <c r="N153" s="7" t="inlineStr">
         <is>
           <t>RUỘNG Coffee &amp; Tea Tri Tôn – Cây Cầu Gỗ Sống Ảo Giữa Biển Lúa &amp; Tầm Nhìn Ôm Trọn Núi Tô  Nằm trên con đường dẫn vào Hồ Soài Chék thuộc Xã Núi Tô, RUỘNG Coffee &amp; Tea là một trong những quán cà phê biểu tượng có không gian mở đẹp và hút khách nhất của vùng Bảy Núi An Giang. Quán sở hữu cây cầu ván gỗ mộc mạc vươn dài ra giữa cánh đồng lúa bao la, mở ra tầm nhìn panorama ngoạn mục hướng thẳng về ngọn núi Phụng Hoàng Sơn (Núi Cô Tô) kỳ vĩ.  1. Vị Trí &amp; Không Gian Mở Hòa Cùng Thiên Nhiên • Vị trí hành chính: Đường vào Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, tỉnh An Giang. • Phong cách thiết kế: Quán được dựng bằng gỗ, tre nứa và mái lá thốt nốt mộc mạc, hoàn toàn không sử dụng vách ngăn kín để đón trọn từng cơn gió đồng mát rượi. • Cầu gỗ sống ảo giữa đồng: Điểm nhấn độc bản của quán là cây cầu ván gỗ dài hàng chục mét uốn lượn xẻ thẳng vào lòng ruộng lúa, nơi du khách có thể bước đi giữa những nhánh lúa trĩu bông và chụp những bức ảnh sống ảo triệu view.  2. Tầm Nhìn Bốn Mùa Rực Rỡ Sắc Màu • Mùa lúa xanh non &amp; Mùa vàng óng ả: Cảnh sắc tại Ruộng Coffee biến chuyển kỳ diệu theo từng mùa vụ. Khi lúa non, cả không gian là một màu xanh ngọc bích mát rượi; khi lúa chín (tháng 4, tháng 8, tháng 11–12), cả cánh đồng chuyển sang màu vàng óng ả, hương lúa mới ngọt ngào lan tỏa khắp quán. • Bóng núi Cô Tô sừng sững: Phía sau cánh đồng là triền núi Cô Tô xanh thẳm, tạo nên một hậu cảnh thiên nhiên tráng lệ cho mọi góc máy.  3. Thực Đơn Đồ Uống &amp; Trà Trái Cây Đa Dạng • Các dòng nước thốt nốt: Nước thốt nốt tươi ướp lạnh, cà phê thốt nốt sữa dừa béo ngậy, thốt nốt dầm hạt chia thanh mát. • Trà trái cây nhiệt đới: Trà dâu tằm Bảy Núi, trà đào cam sả, trà vải hoa hồng mát lạnh giải nhiệt sau chuyến đi dạo đồng quê. • Cà phê pha phin truyền thống: Cà phê đen đá, cà phê sữa đá đậm đà hương vị miền Tây.  4. Hướng Dẫn Sống Ảo &amp; Khung Giờ Vàng • Săn hoàng hôn lãng mạn (16:00 – 17:45): Đây là thời điểm vàng khi ánh mặt trời buông xuống sau rặng núi, nhuộm vàng cả cánh đồng và cây cầu gỗ, mang lại những bức ảnh ngược sáng (silhouette) tuyệt đẹp. • Sáng sớm trong lành (06:30 – 08:30): Không khí se lạnh, sương sớm long lanh trên ngọn lúa, thích hợp cho việc nhâm nhi ly cà phê sáng tĩnh lặng. • Trang phục gợi ý: Váy maxi màu trắng, vàng, cam hoặc trang phục áo bà ba, nón lá truyền thống.  5. Thông Tin Phục Vụ &amp; Mức Giá • Giờ mở cửa: 06:30 – 18:30 mỗi ngày. • Mức giá đồ uống: 20.000đ – 45.000đ / món. • Bãi đỗ xe: Có bãi giữ xe máy và bãi đậu ô tô rộng rãi, bằng phẳng ngay trước quán.</t>
         </is>
       </c>
-      <c r="O152" s="7" t="inlineStr"/>
-      <c r="P152" s="8" t="inlineStr">
+      <c r="O153" s="7" t="inlineStr"/>
+      <c r="P153" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.415,105.018</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="24" customHeight="1">
-      <c r="A153" s="3" t="n">
+    <row r="154" ht="24" customHeight="1">
+      <c r="A154" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>f7f5ca30-windy-hill-coffee-&amp;-</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>Windy Hill Coffee &amp; Homestay Tri Tôn</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr"/>
-      <c r="E153" s="4" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
         <is>
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="3" t="n">
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H154" s="3" t="inlineStr">
         <is>
           <t>10.417, 105.0195</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>Khu vực Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
-      <c r="J153" s="4" t="inlineStr"/>
-      <c r="K153" s="4" t="inlineStr">
-        <is>
-          <t>Miễn phí</t>
-        </is>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>07:00 - 18:00</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr">
+      <c r="J154" s="4" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>Tọa độ cà phê trên sườn đồi lộng gió, đón gió núi mát rượi và ngắm nhìn toàn cảnh ánh đèn thị trấn Tri Tôn lung linh về đêm.</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr">
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>Windy Hill Coffee &amp; Homestay Tri Tôn – Quán Cà Phê Lưng Chừng Đồi Ngắm Toàn Cảnh Cánh Đồng Tà Pạ  Tọa lạc trên một triền đồi dốc thoai thoải gần khu vực Hồ Soài Chék thuộc Xã Núi Tô, Windy Hill Coffee &amp; Homestay đúng như tên gọi của mình là "ngọn đồi lộng gió" với tầm nhìn bao quát từ trên cao ngắm trọn vẹn bức tranh đồng lúa Tà Pạ và triền núi đá Bảy Núi nhấp nhô trong mây ngàn.  1. Vị Trí &amp; Kiến Trúc Đồi Cao Đón Gió • Vị trí hành chính: Khu vực Hồ Soài Chék, Ấp Kè Sen, Xã Núi Tô, tỉnh An Giang. • Địa thế lưng chừng đồi: Nằm ở cao độ lý tưởng, quán đón nhận những luồng gió núi mát rượi thổi qua thung lũng suốt cả ngày, tạo cảm giác se lạnh dễ chịu tựa như các quán cafe đồi dốc tại Đà Lạt. • Không gian thiết kế: Quán kết hợp hài hòa giữa chất liệu gỗ thông mộc mạc và những ô cửa kính lớn nhìn thẳng ra thung lũng lúa bên dưới.  2. Tầm Nhìn Panorama 180 Độ Tuyệt Đẹp • Góc ngắm cánh đồng Tà Pạ từ trên cao: Ngồi tại quán, du khách có thể phóng tầm mắt bao trọn những ô ruộng Tà Pạ muôn màu muôn sắc và những mái chùa Khmer ẩn hiện trong rặng cây. • Săn mây sáng sớm: Vào những buổi sáng mùa mưa, thung lũng dưới chân đồi chìm trong làn sương mờ ảo bồng bềnh trôi qua sườn núi.  3. Thực Đơn Đồ Uống Hiện Đại • Cà phê máy &amp; Cà phê thủ công: Espresso, Cappuccino, Latte, Cà phê muối béo ngậy. • Trà sữa &amp; Sinh tố trái cây tươi: Trà sữa ô long nướng, sinh tố bơ núi Núi Tô béo dẻo, sinh tố mãng cầu tươi.  4. Hướng Dẫn Trải Nghiệm &amp; Chụp Ảnh • Khung giờ đẹp nhất: 06:30 – 08:30 sáng săn sương mây, hoặc 16:30 – 18:00 chiều ngắm hoàng hôn buông xuống thung lũng. • Góc check-in: Bệ cửa sổ gỗ ngắm đồi, xích đu ngoài trời và góc ban công vươn ra sườn dốc.  5. Thông Tin Chi Tiết • Giờ mở cửa: 06:30 – 21:00 mỗi ngày. • Mức giá: 25.000đ – 50.000đ / món.</t>
         </is>
       </c>
-      <c r="O153" s="4" t="inlineStr"/>
-      <c r="P153" s="5" t="inlineStr">
+      <c r="O154" s="4" t="inlineStr"/>
+      <c r="P154" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.417,105.0195</t>
         </is>
@@ -9944,11 +10010,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A118:P118"/>
+    <mergeCell ref="A146:P146"/>
+    <mergeCell ref="A119:P119"/>
     <mergeCell ref="A77:P77"/>
-    <mergeCell ref="A145:P145"/>
+    <mergeCell ref="A130:P130"/>
     <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A129:P129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId1"/>
@@ -10059,7 +10125,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P114" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P115" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P116" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P120" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P117" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P121" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P122" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P123" r:id="rId112"/>
@@ -10067,7 +10133,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P125" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P126" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P127" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P131" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P128" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P132" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P133" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P134" r:id="rId120"/>
@@ -10080,13 +10146,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P141" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P142" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P143" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P147" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P144" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P148" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P149" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P150" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P151" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P152" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P153" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P154" r:id="rId137"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14952,7 +15019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -14965,7 +15032,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="55" customWidth="1" min="14" max="14"/>
@@ -14976,7 +15043,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>🏞️ DANH SÁCH CHI TIẾT: 🏞️ DANH THẮNG NÚI HỒ (38 ĐỊA ĐIỂM)</t>
+          <t>🏞️ DANH SÁCH CHI TIẾT: 🏞️ DANH THẮNG NÚI HỒ (39 ĐỊA ĐIỂM)</t>
         </is>
       </c>
     </row>
@@ -15852,12 +15919,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>nha-trung-bay-van-hoa-khmer-tri-ton</t>
+          <t>nha-thieu-nhi</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Nhà Trưng Bày Văn Hóa Dân Tộc Khmer Tri Tôn</t>
+          <t>Nhà Thiếu Nhi Huyện Tri Tôn</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -15866,45 +15933,49 @@
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Trung tâm Văn hóa &amp; Vui chơi</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>10.4285, 104.998</t>
+          <t>10.4230431, 105.0014886</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Trung tâm Văn hóa Thể thao, Thị trấn Tri Tôn, An Giang</t>
+          <t>Số 89 Đường Trần Hưng Đạo, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Miễn phí</t>
+          <t>Miễn phí vé vào cổng</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>07:00 - 18:00</t>
+          <t>07:00 - 21:00</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Không gian bảo tồn và trưng bày hàng trăm hiện vật quý giá về đời sống, tín ngưỡng, nông cụ, trang phục cưới và nhạc cụ cổ truyền của đồng bào Khmer Bảy Núi.</t>
+          <t>Trung tâm sinh hoạt văn hóa, vui chơi giải trí và rèn luyện năng khiếu rộng hơn 1,5 ha tại trung tâm thị trấn Tri Tôn. Điểm đến dạo chơi lý tưởng cho các gia đình có trẻ nhỏ và thanh thiếu niên vào buổi chiều tối.</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Nơi đây lưu giữ trọn vẹn bộ sưu tập Dàn nhạc Ngũ Âm (Pinpeat), trống Chhay-dăm, các bộ trang phục sân khấu Dù Kê (Robam), mô hình thuyền đua Ngo, nông cụ bừa cày cổ truyền và tư liệu về các kỳ Lễ hội Đua bò Bảy Núi qua nhiều thập kỷ.</t>
+          <t>Khám Phá Nhà Thiếu Nhi Huyện Tri Tôn – Không Gian Văn Hóa &amp; Vui Chơi Năng Động Xứ Bảy Núi  1. Lịch Sử &amp; Quy Mô Công Trình: • Địa chỉ: Số 89, đường Trần Hưng Đạo, Khóm 1, Thị trấn Tri Tôn, An Giang. • Khánh thành ngày 20/9/2013, đây là công trình Nhà thiếu nhi cấp huyện đầu tiên được xây dựng tại tỉnh An Giang với tổng diện tích khuôn viên hơn 15.280 m². • Quy mô bao gồm khu hành chính, hệ thống phòng học năng khiếu (võ thuật Taekwondo, Karatedo, Vovinam, thể dục nhịp điệu, âm nhạc, hội họa), hội trường lớn, sân khấu biểu diễn và khu vui chơi ngoài trời rộng rãi.  2. Hoạt Động &amp; Trải Nghiệm Thực Địa: • Không gian vui chơi rộng rãi, thoáng mát rợp bóng cây xanh, là điểm hẹn quen thuộc của các gia đình địa phương và du khách đưa con em đến vui chơi, chạy nhảy thư giãn mỗi buổi chiều tà. • Nơi thường xuyên diễn ra các hội thi văn nghệ, giao lưu văn hóa thiếu nhi Khmer - Kinh, các giải thi đấu thể thao phong trào và chương trình Tết Trung Thu, Quốc tế Thiếu nhi rộn rã.</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr"/>
       <c r="P15" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.998</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4230431,105.0014886</t>
         </is>
       </c>
     </row>
@@ -15914,12 +15985,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>nui-dai</t>
+          <t>nha-trung-bay-van-hoa-khmer-tri-ton</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Núi Dài</t>
+          <t>Nhà Trưng Bày Văn Hóa Dân Tộc Khmer Tri Tôn</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -15928,22 +15999,18 @@
           <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="F16" s="7" t="n"/>
       <c r="G16" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>10.4759134, 104.942797</t>
+          <t>10.4285, 104.998</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Núi Dài, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Trung tâm Văn hóa Thể thao, Thị trấn Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -15959,18 +16026,18 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Núi Dài, điểm đến kỳ vĩ tại Bảy Núi An Giang</t>
+          <t>Không gian bảo tồn và trưng bày hàng trăm hiện vật quý giá về đời sống, tín ngưỡng, nông cụ, trang phục cưới và nhạc cụ cổ truyền của đồng bào Khmer Bảy Núi.</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Khám Phá Núi Dài (Ngọa Long Sơn) – Dải "Rồng Nằm" Hùng Vĩ Xứ Bảy Núi Trong quần thể Thất Sơn (Bảy Núi) của An Giang, nếu Núi Cấm (Thiên Cấm Sơn) được mệnh danh là ngọn núi cao nhất thì Núi Dài chính là ngọn núi có chiều dài đồ sộ nhất. Với dáng hình uốn lượn tựa như một con rồng khổng lồ đang nằm phục giữa đồng bằng, núi được đặt tên chữ là Ngọa Long Sơn.  1. Vị Trí &amp; • Đặc Điểm Địa LýVị trí hành ch  ính: Nằm chạy dọc theo tuyến Tỉnh lộ 955B, trải dài qua địa phận 3 xã là Châu Lăng, Lương Phi, Lê Trì và một phần thị trấn Ba Chúc thuộc huyện Tri Tôn, tỉnh An Giang. • Quy mô: Chiều dài lên tới khoảng 8.000 m (8 km) – dài nhất trong vùng Thất Sơn. Độ cao đỉnh núi đạt khoảng 580 m. • Lưu ý phân biệt: Trong hệ thống Thất Sơn có hai ngọn núi mang tên "Núi Dài": • Núi Dài Lớn (Ngọa Long Sơn): Ngọn núi dài 8km tại Tri Tôn. Núi Dài • Nhỏ (Ngũ Hồ Sơn / Núi Dài Năm Giếng): Ngọn núi cao 265m nằm bên thị xã Tịnh Biên.  2. Cảnh Quan Sinh Thái &amp; Đời Sống Sơn • Dân • Rừng tầm vông &amp; Vườn cây ăn trái: Men theo các triền dốc lên núi Dài là những cánh rừng tầm vông xanh ngắt bạt ngàn, đan xen cùng những vườn xoài cổ thụ, mít, chuối, bưởi, hồng quân và sầu riêng của bà con người Kinh và Khmer. Hệ thống suối &amp; • Điểm tập kết nông sản: Núi có nhiều dòng suối tự nhiên len lỏi qua các khe đá như Ô Sình, Ô Vàng (dưới chân có dòng suối Vàng, suối Bạc). Vào mùa mưa, núi rừng khoác lên màu xanh mướt mát mắt, suối chảy róc rách và người dân lên núi thu hoạch măng le, nấm rừng cùng hoa quả.  3. Di Tích Lịch Sử &amp; Điểm Đến Tâm Linh  Núi Dài không chỉ có thiên nhiên trù phú mà còn là vùng đất thiêng liêng gắn liền với lịch sử cách mạng hào hùng:Khu • Căn cứ Cách mạng Ô Tà Sóc: Tọa lạc bên sườn núi thuộc xã Lương Phi. Nơi đây là căn cứ địa kiên cố của Tỉnh ủy An Giang thời kháng chiến chống Mỹ, đã được xếp hạng là Di tích lịch sử cách mạng cấp quốc gia. Đồi Ma Thiên Lãnh &amp; Hang Quân Y, • Điện Trời Gầm: Những hang đá granite hiểm trở ghi dấu sự hy sinh anh dũng của các chiến sĩ và thanh niên xung phong tuyến đường 1C. • Hồ Ô Tà Sóc: Hồ nước ngọt phẳng lặng, trong xanh tựa lưng vào vách núi Dài, là điểm cắm trại và check-in dã ngoại rất được yêu thích. • Điện Tàu Cau &amp; Các am cốc tu tập: Nằm rải rác trên sườn núi, là chốn tu thiền thanh tịnh giữa thiên nhiên thâm u của miền biên viễn.  4. Hướng Dẫn • Trải Nghiệm &amp; Khám Phá • Phương tiện: Du khách có thể chạy xe máy men theo các cung đường bê tông dốc thoai thoải từ chân núi (hướng Ô Tà Sóc - Lương Phi hoặc hướng Ba Chúc), hoặc thuê xe ôm bản địa chở lên các điện thờ lưng chừng núi. • Trekking khám phá: Cung đường mòn xuyên qua rừng tầm vông và vườn xoài rất thích hợp cho những ai đam mê trekking nhẹ nhàng, vừa đi bộ vừa hít thở không khí thanh sạch. • Thưởng thức ẩm thực: Dưới chân núi có nhiều hàng quán phục vụ gỏi sầu đâu khô cá lóc/cá sặc, bánh xèo rau rừng, gà đốt đất và nước thốt nốt tươi mát lạnh.  5. • Lưu Ý Khi Tham Quan • An toàn: Đường dốc núi quanh co, nếu tự lái xe máy cần kiểm tra phanh kỹ lưỡng và đi số thấp (số 1, số 2). • Tôn nghiêm &amp; Môi trường: Giữ trật tự khi ghé thăm các khu vực di tích lịch sử, am điện thờ cúng và tuyệt đối không vứt rác, không tự ý đốt lửa gây nguy cơ cháy rừng trên sườn núi.</t>
+          <t>Nơi đây lưu giữ trọn vẹn bộ sưu tập Dàn nhạc Ngũ Âm (Pinpeat), trống Chhay-dăm, các bộ trang phục sân khấu Dù Kê (Robam), mô hình thuyền đua Ngo, nông cụ bừa cày cổ truyền và tư liệu về các kỳ Lễ hội Đua bò Bảy Núi qua nhiều thập kỷ.</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr"/>
       <c r="P16" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4759134,104.942797</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.998</t>
         </is>
       </c>
     </row>
@@ -15980,12 +16047,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>nui-nuoc</t>
+          <t>nui-dai</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Núi Nước</t>
+          <t>Núi Dài</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
@@ -15996,7 +16063,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>place</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
@@ -16004,12 +16071,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>10.492604, 104.8905659</t>
+          <t>10.4759134, 104.942797</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Núi Nước, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Núi Dài, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr"/>
@@ -16025,18 +16092,18 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Nước - điểm tham quan độc đáo tại Bảy Núi</t>
+          <t>Khám phá Núi Dài, điểm đến kỳ vĩ tại Bảy Núi An Giang</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Núi • Nước: Điểm Hẹn Độc Đáo tại Bảy Núi  Trong dãy Thất Sơn hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa và những dải núi đá granite trùng điệp, Núi Nước là một điểm tham quan đặc biệt không thể bỏ qua. Vùng đất này mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương.  Khi đến đây, du khách có thể thưởng thức đặc sản nước thốt nốt tươi và bánh bò thốt nốt, được biết đến qua các đánh giá thực tế của du khách đã đến đây. Những trải nghiệm này không chỉ giúp bạn hiểu hơn về văn hóa phong phú của đồng bào Khmer mà còn là cơ hội để bạn khám phá bản sắc của vùng đất này.  Tìm Kiếm Cảnh Sắc Yên Bình và Phong Hóa Văn Hóa  Núi Nước là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn. Với sự kết hợp hài hòa giữa thiên nhiên và văn hóa, Núi Nước mang đến cho du khách những trải nghiệm đáng nhớ và một cảm giác thư giãn tuyệt vời.</t>
+          <t>Khám Phá Núi Dài (Ngọa Long Sơn) – Dải "Rồng Nằm" Hùng Vĩ Xứ Bảy Núi Trong quần thể Thất Sơn (Bảy Núi) của An Giang, nếu Núi Cấm (Thiên Cấm Sơn) được mệnh danh là ngọn núi cao nhất thì Núi Dài chính là ngọn núi có chiều dài đồ sộ nhất. Với dáng hình uốn lượn tựa như một con rồng khổng lồ đang nằm phục giữa đồng bằng, núi được đặt tên chữ là Ngọa Long Sơn.  1. Vị Trí &amp; • Đặc Điểm Địa LýVị trí hành ch  ính: Nằm chạy dọc theo tuyến Tỉnh lộ 955B, trải dài qua địa phận 3 xã là Châu Lăng, Lương Phi, Lê Trì và một phần thị trấn Ba Chúc thuộc huyện Tri Tôn, tỉnh An Giang. • Quy mô: Chiều dài lên tới khoảng 8.000 m (8 km) – dài nhất trong vùng Thất Sơn. Độ cao đỉnh núi đạt khoảng 580 m. • Lưu ý phân biệt: Trong hệ thống Thất Sơn có hai ngọn núi mang tên "Núi Dài": • Núi Dài Lớn (Ngọa Long Sơn): Ngọn núi dài 8km tại Tri Tôn. Núi Dài • Nhỏ (Ngũ Hồ Sơn / Núi Dài Năm Giếng): Ngọn núi cao 265m nằm bên thị xã Tịnh Biên.  2. Cảnh Quan Sinh Thái &amp; Đời Sống Sơn • Dân • Rừng tầm vông &amp; Vườn cây ăn trái: Men theo các triền dốc lên núi Dài là những cánh rừng tầm vông xanh ngắt bạt ngàn, đan xen cùng những vườn xoài cổ thụ, mít, chuối, bưởi, hồng quân và sầu riêng của bà con người Kinh và Khmer. Hệ thống suối &amp; • Điểm tập kết nông sản: Núi có nhiều dòng suối tự nhiên len lỏi qua các khe đá như Ô Sình, Ô Vàng (dưới chân có dòng suối Vàng, suối Bạc). Vào mùa mưa, núi rừng khoác lên màu xanh mướt mát mắt, suối chảy róc rách và người dân lên núi thu hoạch măng le, nấm rừng cùng hoa quả.  3. Di Tích Lịch Sử &amp; Điểm Đến Tâm Linh  Núi Dài không chỉ có thiên nhiên trù phú mà còn là vùng đất thiêng liêng gắn liền với lịch sử cách mạng hào hùng:Khu • Căn cứ Cách mạng Ô Tà Sóc: Tọa lạc bên sườn núi thuộc xã Lương Phi. Nơi đây là căn cứ địa kiên cố của Tỉnh ủy An Giang thời kháng chiến chống Mỹ, đã được xếp hạng là Di tích lịch sử cách mạng cấp quốc gia. Đồi Ma Thiên Lãnh &amp; Hang Quân Y, • Điện Trời Gầm: Những hang đá granite hiểm trở ghi dấu sự hy sinh anh dũng của các chiến sĩ và thanh niên xung phong tuyến đường 1C. • Hồ Ô Tà Sóc: Hồ nước ngọt phẳng lặng, trong xanh tựa lưng vào vách núi Dài, là điểm cắm trại và check-in dã ngoại rất được yêu thích. • Điện Tàu Cau &amp; Các am cốc tu tập: Nằm rải rác trên sườn núi, là chốn tu thiền thanh tịnh giữa thiên nhiên thâm u của miền biên viễn.  4. Hướng Dẫn • Trải Nghiệm &amp; Khám Phá • Phương tiện: Du khách có thể chạy xe máy men theo các cung đường bê tông dốc thoai thoải từ chân núi (hướng Ô Tà Sóc - Lương Phi hoặc hướng Ba Chúc), hoặc thuê xe ôm bản địa chở lên các điện thờ lưng chừng núi. • Trekking khám phá: Cung đường mòn xuyên qua rừng tầm vông và vườn xoài rất thích hợp cho những ai đam mê trekking nhẹ nhàng, vừa đi bộ vừa hít thở không khí thanh sạch. • Thưởng thức ẩm thực: Dưới chân núi có nhiều hàng quán phục vụ gỏi sầu đâu khô cá lóc/cá sặc, bánh xèo rau rừng, gà đốt đất và nước thốt nốt tươi mát lạnh.  5. • Lưu Ý Khi Tham Quan • An toàn: Đường dốc núi quanh co, nếu tự lái xe máy cần kiểm tra phanh kỹ lưỡng và đi số thấp (số 1, số 2). • Tôn nghiêm &amp; Môi trường: Giữ trật tự khi ghé thăm các khu vực di tích lịch sử, am điện thờ cúng và tuyệt đối không vứt rác, không tự ý đốt lửa gây nguy cơ cháy rừng trên sườn núi.</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.492604,104.8905659</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4759134,104.942797</t>
         </is>
       </c>
     </row>
@@ -16046,12 +16113,12 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>c7d6fabf-rồng-vàng-resort-tri</t>
+          <t>nui-nuoc</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Rồng Vàng Resort Tri Tôn</t>
+          <t>Núi Nước</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -16062,20 +16129,20 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Resort</t>
+          <t>place</t>
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>10.41, 105.01</t>
+          <t>10.492604, 104.8905659</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Núi Nước, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -16091,18 +16158,18 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>Rồng Vàng Resort Tri Tôn - Nơi Hấp Dẫn Của Bảy Núi</t>
+          <t>Khám phá Núi Nước - điểm tham quan độc đáo tại Bảy Núi</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Rồng Vàng Resort Tri Tôn - Một điểm du lịch lý tưởng nằm ở trung tâm thị trấn Tri Tôn, tỉnh An Giang. Resort này tọa lạc ở 19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang. Đây là một điểm đến lý tưởng để thư giãn và khám phá vẻ đẹp của vùng đất Bảy Núi.  Rồng Vàng Resort Tri Tôn mở cửa 24/7, với mức giá khoảng 500k - 900k. Đây là một lựa chọn tuyệt vời cho những ai muốn khám phá vẻ đẹp của Bảy Núi mà không cần lo lắng về chi phí.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng một số du khách đã chia sẻ về những trải nghiệm của mình. "Rồng Vàng Resort Tri Tôn là một nơi tuyệt vời để nghỉ ngơi và thư giãn. Tôi đã có một thời gian tuyệt vời tại đây và tôi chắc chắn sẽ trở lại."  3. Lời khuyên • Hãy đặt phòng trước để đảm bảo có chỗ ở. • Hãy khám phá vẻ đẹp của Bảy Núi bằng nhiều cách khác nhau, chẳng hạn như đi bộ, đạp xe, hoặc tham gia tour du lịch. • Hãy thử các món ăn địa phương và thưởng thức không khí mát mẻ của vùng đất Bảy Núi.</t>
+          <t>Núi • Nước: Điểm Hẹn Độc Đáo tại Bảy Núi  Trong dãy Thất Sơn hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa và những dải núi đá granite trùng điệp, Núi Nước là một điểm tham quan đặc biệt không thể bỏ qua. Vùng đất này mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương.  Khi đến đây, du khách có thể thưởng thức đặc sản nước thốt nốt tươi và bánh bò thốt nốt, được biết đến qua các đánh giá thực tế của du khách đã đến đây. Những trải nghiệm này không chỉ giúp bạn hiểu hơn về văn hóa phong phú của đồng bào Khmer mà còn là cơ hội để bạn khám phá bản sắc của vùng đất này.  Tìm Kiếm Cảnh Sắc Yên Bình và Phong Hóa Văn Hóa  Núi Nước là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn. Với sự kết hợp hài hòa giữa thiên nhiên và văn hóa, Núi Nước mang đến cho du khách những trải nghiệm đáng nhớ và một cảm giác thư giãn tuyệt vời.</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.41,105.01</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.492604,104.8905659</t>
         </is>
       </c>
     </row>
@@ -16112,12 +16179,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>tho-mo-muc-cave-hang-tho-mo-muc</t>
+          <t>c7d6fabf-rồng-vàng-resort-tri</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Tho Mo Muc Cave (Hang Tho Mo Muc)</t>
+          <t>Rồng Vàng Resort Tri Tôn</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
@@ -16128,20 +16195,20 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>attraction</t>
+          <t>Resort</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>10.374438, 104.9655284</t>
+          <t>10.41, 105.01</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Tho Mo Muc Cave (Hang Tho Mo Muc), Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
@@ -16157,18 +16224,18 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Hang Thọ Mộc: Lối vào thiên đường tĩnh lặng giữa đại ngàn Thất Sơn</t>
+          <t>Rồng Vàng Resort Tri Tôn - Nơi Hấp Dẫn Của Bảy Núi</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Tìm Hiểu Hang Tho-Mo-Múc – Dấu Ấn Lịch Sử Trong Lòng Đồi Tức Dụp  Hang Tho-Mo-Múc (hay Tho Mo Múc) là một hang đá tự nhiên mang giá trị lịch sử đặc biệt, nằm trong hệ thống hang động chằng chịt của ngọn đồi Tức Dụp (ngọn đồi 2 triệu đô la huyền thoại).  1. • Vị Trí &amp; Nguồn Gốc Địa Danh • Vị trí: Tọa lạc tại xã Ô Lâm, huyện Tri Tôn, tỉnh An Giang (thuộc cụm di tích Đồi Tức Dụp, nằm ngay triền phía Tây ngọn núi Cô Tô). • Nguồn gốc tên gọi: Tên gọi "Tho-Mo-Múc" (hay Thmâ Mốk / Thmâ Múk) bắt nguồn từ tiếng Khmer bản địa dùng để chỉ các khối đá, hốc đá đặc thù trên triền đồi Tức Dụp.  2. Dấu Ấn Lịch Sử Trong Kháng ChiếnTrong suốt những năm kháng chiến chống Mỹ (đặc biệt là trận đánh 128 ngày đêm huyền thoại bảo vệ đồi Tức • Dụp cuối năm 1968 – đầu năm 1969): Nơi trú • ẩn &amp; Trạm dã chiến: Cùng với các hang C.16, hang Quân y, hang Tỉnh ủy, hang Phụ nữ... Hang Tho-Mo-Múc là một trong những hốc đá kiên cố được quân dân cách mạng, lực lượng thanh niên xung phong (tuyến đường 1C huyền thoại) và các nữ chiến sĩ sử dụng làm nơi trú ẩn, hội họp dã chiến và che giấu thương binh trước các đợt oanh kích ác liệt của pháo binh và máy bay địch. • Cấu trúc hiểm trở: Hang được tạo thành bởi hàng trăm tảng đá granite khổng lồ xếp chồng lên nhau tự nhiên, bên trong có nhiều ngóc ngách, khe gió mát lạnh và luồng thông hiểm trở, giúp bộ đội bám trụ kiên cường dưới lòng đất.  3. Trải Nghiệm Khám Phá Hiện NayKhông gian hoang sơ, huyền bí: Hang vẫn giữ nguyên nét kiến tạo gập ghềnh tự nhiên của đá núi Thất Sơn. Bước vào bên trong, không khí lập tức hạ nhiệt mát lạnh, bóng tối mờ ảo tạo cảm giác hồi hộp, kỳ bí cho những ai thích khám phá mạo hiểm. • Hành trình về nguồn: Nằm trong quần thể di tích lịch sử Đồi Tức Dụp, du khách có thể kết hợp tham quan khu di tích, bảo tàng trưng bày chứng tích chiến tranh và trải nghiệm luồn lách qua các hốc đá tự nhiên.  4. Gợi Ý Lịch Trình Kết Hợp Quanh Khu Vực Xã Ô LâmKhu di tích Đồi Tức Dụp (Hang Tho-Mo-Múc) \longrightarrow Hồ Ô Thum (Ăn gà đốt lá chúc) \longrightarrow Cây thốt nốt trái tim / Cầu khỉ An Tức.  5. Lưu • Ý Dành Cho Người Khám PháTrang bị: Cần chuẩn bị đèn pin cầm tay có độ sáng tốt và đi giày thể thao có độ bám cao để tránh trượt ngã trên các bề mặt đá ẩm ướt. • An toàn: Lối vào hang hẹp, có nhiều đoạn phải khom lưng hoặc trườn qua khe đá; không nên tự ý đi sâu một mình vào những ngách tối chưa có biển chỉ dẫn.</t>
+          <t>1. Tổng quan Rồng Vàng Resort Tri Tôn - Một điểm du lịch lý tưởng nằm ở trung tâm thị trấn Tri Tôn, tỉnh An Giang. Resort này tọa lạc ở 19 Đường Nguyễn Thị Minh Khai, Khóm 4, Thị trấn Tri Tôn, Tri Tôn, An Giang. Đây là một điểm đến lý tưởng để thư giãn và khám phá vẻ đẹp của vùng đất Bảy Núi.  Rồng Vàng Resort Tri Tôn mở cửa 24/7, với mức giá khoảng 500k - 900k. Đây là một lựa chọn tuyệt vời cho những ai muốn khám phá vẻ đẹp của Bảy Núi mà không cần lo lắng về chi phí.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng một số du khách đã chia sẻ về những trải nghiệm của mình. "Rồng Vàng Resort Tri Tôn là một nơi tuyệt vời để nghỉ ngơi và thư giãn. Tôi đã có một thời gian tuyệt vời tại đây và tôi chắc chắn sẽ trở lại."  3. Lời khuyên • Hãy đặt phòng trước để đảm bảo có chỗ ở. • Hãy khám phá vẻ đẹp của Bảy Núi bằng nhiều cách khác nhau, chẳng hạn như đi bộ, đạp xe, hoặc tham gia tour du lịch. • Hãy thử các món ăn địa phương và thưởng thức không khí mát mẻ của vùng đất Bảy Núi.</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr"/>
       <c r="P19" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.374438,104.9655284</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.41,105.01</t>
         </is>
       </c>
     </row>
@@ -16178,12 +16245,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>dong-nhin-len-chu-tri-ton</t>
+          <t>tho-mo-muc-cave-hang-tho-mo-muc</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN</t>
+          <t>Tho Mo Muc Cave (Hang Tho Mo Muc)</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr"/>
@@ -16194,7 +16261,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>artwork</t>
+          <t>attraction</t>
         </is>
       </c>
       <c r="G20" s="6" t="n">
@@ -16202,12 +16269,12 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>10.4016818, 105.0014948</t>
+          <t>10.374438, 104.9655284</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Tho Mo Muc Cave (Hang Tho Mo Muc), Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -16223,18 +16290,18 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>Khám phá vẻ đẹp yên bình của vùng đất Tri Tôn với Điểm check-in chữ Tri Tôn.</t>
+          <t>Hang Thọ Mộc: Lối vào thiên đường tĩnh lặng giữa đại ngàn Thất Sơn</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Đồng Nhin Len Chữ Tri Tôn là một điểm du lịch độc đáo ở huyện Tri Tôn, tỉnh An Giang. Địa điểm này nằm trong hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo của vùng đất này. Vùng đất Tri Tôn nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  2. Đánh giá từ du khách • Đường đi đến điểm check-in dễ dàng, chỉ cần đi bộ khoảng 1200-1500 bước hoặc thuê xe ôm để xuống. • Điểm check-in chữ Tri Tôn là một địa điểm sống ảo nổi bật với view núi non và cánh đồng rộng lớn. • Khung cảnh thoáng đãng và bảng chữ lớn đặc trưng thu hút nhiều bạn trẻ đến chụp ảnh. • Phong cảnh hùng vĩ, không khí mát mẻ trong lành. • Là một điểm du lịch lý thú và đáng trải nghiệm.  3. Lời khuyên • Khi đến đây, bạn có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer. • Hãy đi bộ lên khoảng 1200-1500 bước để có thể ngắm nhìn vẻ đẹp yên bình của cánh đồng rộng lớn và núi non hùng vĩ. • Để có thể ghi lại được những bức ảnh sống ảo đẹp nhất, hãy thuê xe ôm để xuống và chụp ảnh ở những góc cạnh đặc trưng. • Hãy tận hưởng phong cảnh hùng vĩ, không khí mát mẻ trong lành và lòng hiếu khách của người dân địa phương.</t>
+          <t>Tìm Hiểu Hang Tho-Mo-Múc – Dấu Ấn Lịch Sử Trong Lòng Đồi Tức Dụp  Hang Tho-Mo-Múc (hay Tho Mo Múc) là một hang đá tự nhiên mang giá trị lịch sử đặc biệt, nằm trong hệ thống hang động chằng chịt của ngọn đồi Tức Dụp (ngọn đồi 2 triệu đô la huyền thoại).  1. • Vị Trí &amp; Nguồn Gốc Địa Danh • Vị trí: Tọa lạc tại xã Ô Lâm, huyện Tri Tôn, tỉnh An Giang (thuộc cụm di tích Đồi Tức Dụp, nằm ngay triền phía Tây ngọn núi Cô Tô). • Nguồn gốc tên gọi: Tên gọi "Tho-Mo-Múc" (hay Thmâ Mốk / Thmâ Múk) bắt nguồn từ tiếng Khmer bản địa dùng để chỉ các khối đá, hốc đá đặc thù trên triền đồi Tức Dụp.  2. Dấu Ấn Lịch Sử Trong Kháng ChiếnTrong suốt những năm kháng chiến chống Mỹ (đặc biệt là trận đánh 128 ngày đêm huyền thoại bảo vệ đồi Tức • Dụp cuối năm 1968 – đầu năm 1969): Nơi trú • ẩn &amp; Trạm dã chiến: Cùng với các hang C.16, hang Quân y, hang Tỉnh ủy, hang Phụ nữ... Hang Tho-Mo-Múc là một trong những hốc đá kiên cố được quân dân cách mạng, lực lượng thanh niên xung phong (tuyến đường 1C huyền thoại) và các nữ chiến sĩ sử dụng làm nơi trú ẩn, hội họp dã chiến và che giấu thương binh trước các đợt oanh kích ác liệt của pháo binh và máy bay địch. • Cấu trúc hiểm trở: Hang được tạo thành bởi hàng trăm tảng đá granite khổng lồ xếp chồng lên nhau tự nhiên, bên trong có nhiều ngóc ngách, khe gió mát lạnh và luồng thông hiểm trở, giúp bộ đội bám trụ kiên cường dưới lòng đất.  3. Trải Nghiệm Khám Phá Hiện NayKhông gian hoang sơ, huyền bí: Hang vẫn giữ nguyên nét kiến tạo gập ghềnh tự nhiên của đá núi Thất Sơn. Bước vào bên trong, không khí lập tức hạ nhiệt mát lạnh, bóng tối mờ ảo tạo cảm giác hồi hộp, kỳ bí cho những ai thích khám phá mạo hiểm. • Hành trình về nguồn: Nằm trong quần thể di tích lịch sử Đồi Tức Dụp, du khách có thể kết hợp tham quan khu di tích, bảo tàng trưng bày chứng tích chiến tranh và trải nghiệm luồn lách qua các hốc đá tự nhiên.  4. Gợi Ý Lịch Trình Kết Hợp Quanh Khu Vực Xã Ô LâmKhu di tích Đồi Tức Dụp (Hang Tho-Mo-Múc) \longrightarrow Hồ Ô Thum (Ăn gà đốt lá chúc) \longrightarrow Cây thốt nốt trái tim / Cầu khỉ An Tức.  5. Lưu • Ý Dành Cho Người Khám PháTrang bị: Cần chuẩn bị đèn pin cầm tay có độ sáng tốt và đi giày thể thao có độ bám cao để tránh trượt ngã trên các bề mặt đá ẩm ướt. • An toàn: Lối vào hang hẹp, có nhiều đoạn phải khom lưng hoặc trườn qua khe đá; không nên tự ý đi sâu một mình vào những ngách tối chưa có biển chỉ dẫn.</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr"/>
       <c r="P20" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4016818,105.0014948</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.374438,104.9655284</t>
         </is>
       </c>
     </row>
@@ -16244,36 +16311,36 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>3383c54e-con-đường-vòm-còng-c</t>
+          <t>dong-nhin-len-chu-tri-ton</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Vòm Còng Châu Lăng</t>
+          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Xã Châu Lăng</t>
+          <t>Thị trấn Tri Tôn</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Con đường nhiếp ảnh</t>
+          <t>artwork</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>10.4355, 105.0015</t>
+          <t>10.4016818, 105.0014948</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Tuyến đường Hàng Còng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>ĐỒNG NHÌN LÊN CHỮ TRI TÔN, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -16289,18 +16356,18 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Vòm Còng Châu Lăng: Một dấu ấn văn hóa độc đáo tại Bảy Núi</t>
+          <t>Khám phá vẻ đẹp yên bình của vùng đất Tri Tôn với Điểm check-in chữ Tri Tôn.</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Khám Phá Con Đường Vòm Còng Châu Lăng (Chùa Hàng Còng – Krăng Krốch)1. • Vị Trí &amp; Tên GọiĐịa chỉ: Ấp An Hòa, xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Tên gọi địa phương: Chùa có tên chữ là Prochum Meáp Chhưm Kiriram (nghĩa là "Ngôi chùa ở giữa núi").Người Khmer gọi là Krăng Krốch (Krăng là "gò cao", Krốch là "bưởi rừng").Do nét đặc trưng độc nhất vô nhị của hàng cây cổ thụ dẫn vào chùa, người dân bản địa lẫn du khách quen gọi bằng cái tên thân thuộc: Chùa Hàng Còng hay Con đường Hàng Còng Châu Lăng.  2. Điểm Độc Đáo Của "Con Đường Vòm Còng"Mái vòm tự nhiên hàng trăm năm tuổi: Con đường dài hàng trăm mét dẫn từ cổng vào sâu trong sân chùa được che phủ bởi khoảng 60 – 70 cây còng cổ thụ (còn gọi là cây me tây/muồng tím). Các nhánh cây vươn dài, đan cài vào nhau tạo thành một "mái vòm xanh mát" khổng lồ, tách biệt hoàn toàn khỏi cái nắng gắt của vùng đồng bằng. • Thân cây cổ thụ độc lạ: Những gốc còng to lớn đến 2 – 3 người ôm mới xuể, thân cây xù xì, nổi nhiều u sần và rễ cây cuồn cuộn trồi lên mặt đất tạo thành những hình khối điêu khắc tự nhiên rất ấn tượng. • Vẻ đẹp biến chuyển theo mùa: Mùa xuân – hè: Tán lá xanh um tùm, ánh nắng xuyên qua kẽ lá rọi xuống mặt đường tạo nên khung cảnh thanh bình, thơ mộng. • Mùa thay lá: Hàng còng trút lá để lại những cành nhánh khẳng khiu, trầm mặc, mang lại cảm giác ma mị, huyền bí rất đậm chất điện ảnh.  3. Hướng Dẫn Di Chuyển &amp; • Gợi Ý Lịch Trình Kết HợpHướng đi: Từ trung tâm thị trấn Tri Tôn hoặc từ TP. Châu Đốc đi theo hướng về ngã ba Ba Chúc/Châu Lăng. Lối vào chùa nằm ven tuyến đường giao thông ở ấp An Hòa (cổng chùa hơi khuất sau nhà dân, bạn có thể hỏi người dân quanh đó đường vào "Chùa Hàng Còng").Cung đường check-in liên hoàn tại • Châu Lăng: Chùa Hàng Còng (Krăng Krốch) \longrightarrow Cổng trời Tri Tôn (Chùa Koh Kas - cách chừng 2km) \longrightarrow Tuyến tránh Tri Tôn săn hoàng hôn.  4. Lưu Ý Dành • Cho Du KháchKhông gian tôn nghiêm: Đây là lối đi vào chốn tu tập Phật giáo Nam tông Khmer. Du khách đến chụp ảnh nên giữ trật tự, đi đứng nhẹ nhàng, không xả rác và không bẻ cành/khắc tên lên thân cây cổ thụ. • Thời điểm chụp ảnh đẹp nhất: Sáng sớm (khoảng 7h00 – 9h00) khi ánh nắng xiên rọi qua vòm lá tạo hiệu ứng luồng sáng (ray sáng), hoặc buổi chiều dịu mát lúc 15h30 – 17h00.</t>
+          <t>1. Tổng quan Đồng Nhin Len Chữ Tri Tôn là một điểm du lịch độc đáo ở huyện Tri Tôn, tỉnh An Giang. Địa điểm này nằm trong hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo của vùng đất này. Vùng đất Tri Tôn nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  2. Đánh giá từ du khách • Đường đi đến điểm check-in dễ dàng, chỉ cần đi bộ khoảng 1200-1500 bước hoặc thuê xe ôm để xuống. • Điểm check-in chữ Tri Tôn là một địa điểm sống ảo nổi bật với view núi non và cánh đồng rộng lớn. • Khung cảnh thoáng đãng và bảng chữ lớn đặc trưng thu hút nhiều bạn trẻ đến chụp ảnh. • Phong cảnh hùng vĩ, không khí mát mẻ trong lành. • Là một điểm du lịch lý thú và đáng trải nghiệm.  3. Lời khuyên • Khi đến đây, bạn có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer. • Hãy đi bộ lên khoảng 1200-1500 bước để có thể ngắm nhìn vẻ đẹp yên bình của cánh đồng rộng lớn và núi non hùng vĩ. • Để có thể ghi lại được những bức ảnh sống ảo đẹp nhất, hãy thuê xe ôm để xuống và chụp ảnh ở những góc cạnh đặc trưng. • Hãy tận hưởng phong cảnh hùng vĩ, không khí mát mẻ trong lành và lòng hiếu khách của người dân địa phương.</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr"/>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4355,105.0015</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4016818,105.0014948</t>
         </is>
       </c>
     </row>
@@ -16310,12 +16377,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>d3e73741-cánh-đồng-thốt-nốt-c</t>
+          <t>3383c54e-con-đường-vòm-còng-c</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Cánh Đồng Thốt Nốt Châu Lăng</t>
+          <t>Con Đường Vòm Còng Châu Lăng</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -16326,20 +16393,20 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng</t>
+          <t>Con đường nhiếp ảnh</t>
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>10.437, 105.003</t>
+          <t>10.4355, 105.0015</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Tuyến đường Hàng Còng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -16355,18 +16422,18 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>Danh từ cánh Bộ phận trong thân thể chim và một số côn trùng, dùng để bay. Chim vỗ cánh. Thẳng cánh cò bay. Bộ phận hình như cánh …</t>
+          <t>Khám phá Con Đường Vòm Còng Châu Lăng: Một dấu ấn văn hóa độc đáo tại Bảy Núi</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Cánh Đồng Thốt Nốt Châu Lăng - Một Thiên Nhiên Huyền Bí Tại Tri Tôn  1. Tổng quan Cánh Đồng Thốt Nốt Châu Lăng tọa lạc tại Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang. Nơi đây là một thiên nhiên huyền bí, mang dấu ấn đặc trưng của vùng đất An Giang. Với mô hình cánh đồng thốt nốt độc đáo, Cánh Đồng Thốt Nốt Châu Lăng trở thành một điểm đến thú vị cho những ai yêu thích thiên nhiên và muốn khám phá vẻ đẹp nguyên sơ của Việt Nam.  2. Đánh giá từ du khách Chưa có đánh giá cụ thể từ du khách, nhưng với vẻ đẹp nguyên sơ và độc đáo, Cánh Đồng Thốt Nốt Châu Lăng chắc chắn sẽ mang lại những trải nghiệm thú vị và đáng nhớ cho du khách. Du khách sẽ được tận hưởng không gian mở, cảm nhận được sự yên tĩnh và hòa mình với thiên nhiên.  3. Lời khuyên Trước khi đến Cánh Đồng Thốt Nốt Châu Lăng, bạn nên tìm hiểu thêm về địa điểm này để có những chuẩn bị cần thiết. Ngoài ra, nên mang theo đủ nước, thức ăn và trang thiết bị cần thiết để có một chuyến đi thoải mái và an toàn.</t>
+          <t>Khám Phá Con Đường Vòm Còng Châu Lăng (Chùa Hàng Còng – Krăng Krốch)1. • Vị Trí &amp; Tên GọiĐịa chỉ: Ấp An Hòa, xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Tên gọi địa phương: Chùa có tên chữ là Prochum Meáp Chhưm Kiriram (nghĩa là "Ngôi chùa ở giữa núi").Người Khmer gọi là Krăng Krốch (Krăng là "gò cao", Krốch là "bưởi rừng").Do nét đặc trưng độc nhất vô nhị của hàng cây cổ thụ dẫn vào chùa, người dân bản địa lẫn du khách quen gọi bằng cái tên thân thuộc: Chùa Hàng Còng hay Con đường Hàng Còng Châu Lăng.  2. Điểm Độc Đáo Của "Con Đường Vòm Còng"Mái vòm tự nhiên hàng trăm năm tuổi: Con đường dài hàng trăm mét dẫn từ cổng vào sâu trong sân chùa được che phủ bởi khoảng 60 – 70 cây còng cổ thụ (còn gọi là cây me tây/muồng tím). Các nhánh cây vươn dài, đan cài vào nhau tạo thành một "mái vòm xanh mát" khổng lồ, tách biệt hoàn toàn khỏi cái nắng gắt của vùng đồng bằng. • Thân cây cổ thụ độc lạ: Những gốc còng to lớn đến 2 – 3 người ôm mới xuể, thân cây xù xì, nổi nhiều u sần và rễ cây cuồn cuộn trồi lên mặt đất tạo thành những hình khối điêu khắc tự nhiên rất ấn tượng. • Vẻ đẹp biến chuyển theo mùa: Mùa xuân – hè: Tán lá xanh um tùm, ánh nắng xuyên qua kẽ lá rọi xuống mặt đường tạo nên khung cảnh thanh bình, thơ mộng. • Mùa thay lá: Hàng còng trút lá để lại những cành nhánh khẳng khiu, trầm mặc, mang lại cảm giác ma mị, huyền bí rất đậm chất điện ảnh.  3. Hướng Dẫn Di Chuyển &amp; • Gợi Ý Lịch Trình Kết HợpHướng đi: Từ trung tâm thị trấn Tri Tôn hoặc từ TP. Châu Đốc đi theo hướng về ngã ba Ba Chúc/Châu Lăng. Lối vào chùa nằm ven tuyến đường giao thông ở ấp An Hòa (cổng chùa hơi khuất sau nhà dân, bạn có thể hỏi người dân quanh đó đường vào "Chùa Hàng Còng").Cung đường check-in liên hoàn tại • Châu Lăng: Chùa Hàng Còng (Krăng Krốch) \longrightarrow Cổng trời Tri Tôn (Chùa Koh Kas - cách chừng 2km) \longrightarrow Tuyến tránh Tri Tôn săn hoàng hôn.  4. Lưu Ý Dành • Cho Du KháchKhông gian tôn nghiêm: Đây là lối đi vào chốn tu tập Phật giáo Nam tông Khmer. Du khách đến chụp ảnh nên giữ trật tự, đi đứng nhẹ nhàng, không xả rác và không bẻ cành/khắc tên lên thân cây cổ thụ. • Thời điểm chụp ảnh đẹp nhất: Sáng sớm (khoảng 7h00 – 9h00) khi ánh nắng xiên rọi qua vòm lá tạo hiệu ứng luồng sáng (ray sáng), hoặc buổi chiều dịu mát lúc 15h30 – 17h00.</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
       <c r="P22" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.437,105.003</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4355,105.0015</t>
         </is>
       </c>
     </row>
@@ -16376,12 +16443,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>a810d441-cây-thốt-nốt-cô-độc-</t>
+          <t>d3e73741-cánh-đồng-thốt-nốt-c</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Cây Thốt Nốt Cô Độc Châu Lăng</t>
+          <t>Cánh Đồng Thốt Nốt Châu Lăng</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
@@ -16392,7 +16459,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Điểm check-in độc đáo</t>
+          <t>Cánh đồng</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
@@ -16400,12 +16467,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>10.439, 105.0035</t>
+          <t>10.437, 105.003</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Cây thốt nốt cô độc, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
@@ -16421,18 +16488,18 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Thông Tin Thực Tế Về "Cây Thốt Nốt Cô Độc" (Châu Lăng)</t>
+          <t>Danh từ cánh Bộ phận trong thân thể chim và một số côn trùng, dùng để bay. Chim vỗ cánh. Thẳng cánh cò bay. Bộ phận hình như cánh …</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Tương tự như nhiều góc check-in tự nhiên tại vùng Bảy Núi, "Cây thốt nốt cô độc" không có ban quản lý, không bán vé và không có biển chỉ dẫn chính thức.  Tên gọi từ cộng • đồng nhiếp ảnh và phượt thủ: Tên gọi này do các nhiếp ảnh gia và bạn trẻ đam mê du lịch đặt ra khi săn ảnh phong cảnh vùng Tri Tôn. Điểm đặc biệt là giữa cánh đồng lúa mênh mông, thay vì mọc thành hàng hoặc cụm dày đặc như thông thường, cây này đứng lẻ loi một mình giữa bờ ruộng, tạo nên bố cục "cô độc" cực kỳ đắt giá cho khung hình.  2. Vị trí thực tế &amp; • Cách tiếp cận  Khu vực: Nằm giữa các cánh đồng lúa thuộc địa phận xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Trục đường: Nằm dọc theo các con đường đan, đường nội đồng cắt ngang cánh đồng nối giữa khu vực Chùa Hàng Còng (ấp An Hòa) và hướng đi về Cổng trời Chùa Koh Kas. • Nhận diện thực tế: Giữa một khoảng ruộng trống trải, tầm nhìn thoáng đãng không bị vướng nhà dân hay cột điện lớn, một thân thốt nốt thẳng đứng vươn cao với tán lá tròn xòe rộng, phía hậu cảnh là bóng mờ của các dãy núi thuộc vùng Thất Sơn.  3. Vì sao góc chụp này nổi tiếng trong giới nhiếp ảnh? • Bố cục tối giản (Minimalism): Cảnh quan xung quanh chỉ có trời, thảm lúa phẳng lì và một bóng cây duy nhất. Bố cục này giúp chủ thể chụp ảnh nổi bật hoàn toàn mà không bị rối mắt. • Hiệu ứng bóng đổ và Silhouette:  Vào buổi chiều tà (khoảng 17h15 – 18h00), khi mặt trời lặn sau dãy núi phía Tây, chụp ngược sáng sẽ bắt trọn dáng hình cây thốt nốt in bóng đen cắt ngang bầu trời ráng chiều đỏ rực hoặc tím biếc.  Vào mùa nước nổi, mặt ruộng ngập nước in bóng cây xuống như một chiếc gương khổng lồ.  4. Lưu ý thực tế khi ghé thăm • Địa hình bờ ruộng: Lối đi vào sát gốc cây là bờ đất nhỏ của ruộng lúa, vào mùa mưa hoặc mùa nước có thể trơn trượt hoặc lầy lội; nên cẩn thận khi bước đi và ưu tiên giày dép có độ bám tốt. • Tôn trọng bà con làm nông: Cây nằm trong đất canh tác lúa của người dân địa phương. Tuyệt đối không giẫm đạp lên lúa, không bẻ lá hay khắc tên lên thân cây và mang toàn bộ rác cá nhân ra ngoài.</t>
+          <t>Cánh Đồng Thốt Nốt Châu Lăng - Một Thiên Nhiên Huyền Bí Tại Tri Tôn  1. Tổng quan Cánh Đồng Thốt Nốt Châu Lăng tọa lạc tại Cánh đồng thốt nốt Châu Lăng, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang. Nơi đây là một thiên nhiên huyền bí, mang dấu ấn đặc trưng của vùng đất An Giang. Với mô hình cánh đồng thốt nốt độc đáo, Cánh Đồng Thốt Nốt Châu Lăng trở thành một điểm đến thú vị cho những ai yêu thích thiên nhiên và muốn khám phá vẻ đẹp nguyên sơ của Việt Nam.  2. Đánh giá từ du khách Chưa có đánh giá cụ thể từ du khách, nhưng với vẻ đẹp nguyên sơ và độc đáo, Cánh Đồng Thốt Nốt Châu Lăng chắc chắn sẽ mang lại những trải nghiệm thú vị và đáng nhớ cho du khách. Du khách sẽ được tận hưởng không gian mở, cảm nhận được sự yên tĩnh và hòa mình với thiên nhiên.  3. Lời khuyên Trước khi đến Cánh Đồng Thốt Nốt Châu Lăng, bạn nên tìm hiểu thêm về địa điểm này để có những chuẩn bị cần thiết. Ngoài ra, nên mang theo đủ nước, thức ăn và trang thiết bị cần thiết để có một chuyến đi thoải mái và an toàn.</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr"/>
       <c r="P23" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.439,105.0035</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.437,105.003</t>
         </is>
       </c>
     </row>
@@ -16442,12 +16509,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>lang-nghe-tho-cam-chau-lang</t>
+          <t>a810d441-cây-thốt-nốt-cô-độc-</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Làng Nghề Dệt Thổ Cẩm Khmer Truyền Thống Châu Lăng</t>
+          <t>Cây Thốt Nốt Cô Độc Châu Lăng</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
@@ -16456,18 +16523,22 @@
           <t>Xã Châu Lăng</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Điểm check-in độc đáo</t>
+        </is>
+      </c>
       <c r="G24" s="6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>10.4412, 104.975</t>
+          <t>10.439, 105.0035</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Cây thốt nốt cô độc, Ấp An Hòa, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -16483,18 +16554,18 @@
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>Làng nghề dệt thổ cẩm truyền thống lâu đời của phụ nữ Khmer xã Châu Lăng, lưu giữ kỹ thuật dệt hoa văn Thất Sơn tinh xảo trên khung cửi gỗ cổ truyền.</t>
+          <t>Thông Tin Thực Tế Về "Cây Thốt Nốt Cô Độc" (Châu Lăng)</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Thổ cẩm Khmer Châu Lăng nổi tiếng với màu sắc tự nhiên chiết xuất từ vỏ cây, củ nghệ và trái mặc nưa. Các sản phẩm đặc trưng gồm khăn Krama (khăn rằn Khmer), xà-rông, túi thổ cẩm và trang phục dạ hội truyền thống với các hoa văn hoa sen, rắn thần Naga và thần chim Garuda.</t>
+          <t>Tương tự như nhiều góc check-in tự nhiên tại vùng Bảy Núi, "Cây thốt nốt cô độc" không có ban quản lý, không bán vé và không có biển chỉ dẫn chính thức.  Tên gọi từ cộng • đồng nhiếp ảnh và phượt thủ: Tên gọi này do các nhiếp ảnh gia và bạn trẻ đam mê du lịch đặt ra khi săn ảnh phong cảnh vùng Tri Tôn. Điểm đặc biệt là giữa cánh đồng lúa mênh mông, thay vì mọc thành hàng hoặc cụm dày đặc như thông thường, cây này đứng lẻ loi một mình giữa bờ ruộng, tạo nên bố cục "cô độc" cực kỳ đắt giá cho khung hình.  2. Vị trí thực tế &amp; • Cách tiếp cận  Khu vực: Nằm giữa các cánh đồng lúa thuộc địa phận xã Châu Lăng, huyện Tri Tôn, tỉnh An Giang. • Trục đường: Nằm dọc theo các con đường đan, đường nội đồng cắt ngang cánh đồng nối giữa khu vực Chùa Hàng Còng (ấp An Hòa) và hướng đi về Cổng trời Chùa Koh Kas. • Nhận diện thực tế: Giữa một khoảng ruộng trống trải, tầm nhìn thoáng đãng không bị vướng nhà dân hay cột điện lớn, một thân thốt nốt thẳng đứng vươn cao với tán lá tròn xòe rộng, phía hậu cảnh là bóng mờ của các dãy núi thuộc vùng Thất Sơn.  3. Vì sao góc chụp này nổi tiếng trong giới nhiếp ảnh? • Bố cục tối giản (Minimalism): Cảnh quan xung quanh chỉ có trời, thảm lúa phẳng lì và một bóng cây duy nhất. Bố cục này giúp chủ thể chụp ảnh nổi bật hoàn toàn mà không bị rối mắt. • Hiệu ứng bóng đổ và Silhouette:  Vào buổi chiều tà (khoảng 17h15 – 18h00), khi mặt trời lặn sau dãy núi phía Tây, chụp ngược sáng sẽ bắt trọn dáng hình cây thốt nốt in bóng đen cắt ngang bầu trời ráng chiều đỏ rực hoặc tím biếc.  Vào mùa nước nổi, mặt ruộng ngập nước in bóng cây xuống như một chiếc gương khổng lồ.  4. Lưu ý thực tế khi ghé thăm • Địa hình bờ ruộng: Lối đi vào sát gốc cây là bờ đất nhỏ của ruộng lúa, vào mùa mưa hoặc mùa nước có thể trơn trượt hoặc lầy lội; nên cẩn thận khi bước đi và ưu tiên giày dép có độ bám tốt. • Tôn trọng bà con làm nông: Cây nằm trong đất canh tác lúa của người dân địa phương. Tuyệt đối không giẫm đạp lên lúa, không bẻ lá hay khắc tên lên thân cây và mang toàn bộ rác cá nhân ra ngoài.</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr"/>
       <c r="P24" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4412,104.975</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.439,105.0035</t>
         </is>
       </c>
     </row>
@@ -16504,12 +16575,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>nui-nam-quy</t>
+          <t>lang-nghe-tho-cam-chau-lang</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Núi Nam Quy</t>
+          <t>Làng Nghề Dệt Thổ Cẩm Khmer Truyền Thống Châu Lăng</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -16518,22 +16589,18 @@
           <t>Xã Châu Lăng</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>10.4525302, 105.0037006</t>
+          <t>10.4412, 104.975</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Núi Nam Quy, Xã Châu Lăng, Tri Tôn, An Giang</t>
+          <t>Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
@@ -16549,18 +16616,18 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Nam Quy, điểm đến thiên nhiên độc đáo tại Bảy Núi, An Giang.</t>
+          <t>Làng nghề dệt thổ cẩm truyền thống lâu đời của phụ nữ Khmer xã Châu Lăng, lưu giữ kỹ thuật dệt hoa văn Thất Sơn tinh xảo trên khung cửi gỗ cổ truyền.</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Núi • Nam Quy: Điểm đến thiên nhiên độc đáo tại Bảy Núi  Vùng đất Tri Tôn, thuộc dãy Thất Sơn (Bảy Núi) hùng vĩ, mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Núi Nam Quy là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang.  Hoàng sơ và bình yên  Núi Nam Quy nằm trong khu vực đồng bằng phù sa, với những dải núi đá granite trùng điệp. Cảnh sắc yên bình và không khí trong lành tạo nên một bức tranh tuyệt đẹp. Du khách có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về kinh nghiệm của mình khi đến với Núi Nam Quy. Một người đã nhận xét rằng công viên có nơi vui chơi dành cho trẻ em và cảnh quan thiên nhiên đẹp của núi rừng về chiều lén công viên ngồi gió mát. Tuy nhiên, cũng có một số người nhận xét rằng công viên này chủ yếu để buôn bán quà vặt và tập thể dục, chứ nếu đến để chơi là phụ thôi.  Lưu ý  Du khách cần lưu ý rằng có nhiều rắn sinh sống trong khu vực này, vì vậy cần cẩn thận khi di chuyển. Ngoài ra, không có đường lên núi cao 213m, vì có nhiều rắn dữ.  Kết luận  Núi Nam Quy là một điểm đến tuyệt vời cho những ai muốn khám phá cảnh sắc thiên nhiên độc đáo và trải nghiệm văn hóa phong phú của người Khmer. Hãy đến và khám phá!</t>
+          <t>Thổ cẩm Khmer Châu Lăng nổi tiếng với màu sắc tự nhiên chiết xuất từ vỏ cây, củ nghệ và trái mặc nưa. Các sản phẩm đặc trưng gồm khăn Krama (khăn rằn Khmer), xà-rông, túi thổ cẩm và trang phục dạ hội truyền thống với các hoa văn hoa sen, rắn thần Naga và thần chim Garuda.</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr"/>
       <c r="P25" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4525302,105.0037006</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4412,104.975</t>
         </is>
       </c>
     </row>
@@ -16570,12 +16637,12 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>ho-latina</t>
+          <t>nui-nam-quy</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>hồ latina</t>
+          <t>Núi Nam Quy</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr"/>
@@ -16586,7 +16653,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>camp_site</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G26" s="6" t="n">
@@ -16594,12 +16661,12 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>10.4240344, 104.9999364</t>
+          <t>10.4525302, 105.0037006</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>hồ latina, Xã An Hảo (Ranh giới giáp TX. Tịnh Biên), Tri Tôn, An Giang</t>
+          <t>Núi Nam Quy, Xã Châu Lăng, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
@@ -16615,18 +16682,18 @@
       </c>
       <c r="M26" s="7" t="inlineStr">
         <is>
-          <t>Hồ Đá Latina (Vách Đá Latina) — Tuyệt tác vách đá dựng đứng soi bóng mặt nước tĩnh lặng, nằm tại khu vực Xã An Hảo, ngay cung đường giáp ranh TX. Tịnh Biên và Tri Tôn. Điểm check-in chụp ảnh vách đá hùng vĩ nổi tiếng.</t>
+          <t>Khám phá Núi Nam Quy, điểm đến thiên nhiên độc đáo tại Bảy Núi, An Giang.</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Vị trí và Ranh giới Thực địa Hồ Đá Latina nằm dưới chân núi Cấm, thuộc địa phận Xã An Hảo (tiếp giáp ranh giới giữa TX. Tịnh Biên và Tri Tôn). Du khách cần chú ý định vị chính xác vì khu vực này nằm trên trục đường liên ranh giới.  Trải nghiệm &amp; Cảnh quan Điểm nhấn ấn tượng nhất là vách đá hoa cương dựng đứng sừng sững bên hồ nước trong xanh. Đây là góc săn ảnh check-in thiên nhiên độc đáo, mang vẻ đẹp hoang sơ kỳ vĩ.</t>
+          <t>Núi • Nam Quy: Điểm đến thiên nhiên độc đáo tại Bảy Núi  Vùng đất Tri Tôn, thuộc dãy Thất Sơn (Bảy Núi) hùng vĩ, mang đến cho du khách cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Núi Nam Quy là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang.  Hoàng sơ và bình yên  Núi Nam Quy nằm trong khu vực đồng bằng phù sa, với những dải núi đá granite trùng điệp. Cảnh sắc yên bình và không khí trong lành tạo nên một bức tranh tuyệt đẹp. Du khách có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về kinh nghiệm của mình khi đến với Núi Nam Quy. Một người đã nhận xét rằng công viên có nơi vui chơi dành cho trẻ em và cảnh quan thiên nhiên đẹp của núi rừng về chiều lén công viên ngồi gió mát. Tuy nhiên, cũng có một số người nhận xét rằng công viên này chủ yếu để buôn bán quà vặt và tập thể dục, chứ nếu đến để chơi là phụ thôi.  Lưu ý  Du khách cần lưu ý rằng có nhiều rắn sinh sống trong khu vực này, vì vậy cần cẩn thận khi di chuyển. Ngoài ra, không có đường lên núi cao 213m, vì có nhiều rắn dữ.  Kết luận  Núi Nam Quy là một điểm đến tuyệt vời cho những ai muốn khám phá cảnh sắc thiên nhiên độc đáo và trải nghiệm văn hóa phong phú của người Khmer. Hãy đến và khám phá!</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr"/>
       <c r="P26" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4240344,104.9999364</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4525302,105.0037006</t>
         </is>
       </c>
     </row>
@@ -16636,36 +16703,36 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2ac3fb9a-con-đường-thốt-nốt-ô</t>
+          <t>ho-latina</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Thốt Nốt Ô Lâm - Cô Tô</t>
+          <t>hồ latina</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Xã Cô Tô</t>
+          <t>Xã Châu Lăng</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Con đường nhiếp ảnh</t>
+          <t>camp_site</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>10.38, 104.995</t>
+          <t>10.4240344, 104.9999364</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Tuyến đường liên xã Ô Lâm - Núi Tô, Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>hồ latina, Xã An Hảo (Ranh giới giáp TX. Tịnh Biên), Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
@@ -16681,18 +16748,18 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Thốt Nốt Ô Lâm - Cô Tô, một điểm đến văn hóa độc đáo tại vùng Bảy Núi</t>
+          <t>Hồ Đá Latina (Vách Đá Latina) — Tuyệt tác vách đá dựng đứng soi bóng mặt nước tĩnh lặng, nằm tại khu vực Xã An Hảo, ngay cung đường giáp ranh TX. Tịnh Biên và Tri Tôn. Điểm check-in chụp ảnh vách đá hùng vĩ nổi tiếng.</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Con Đường Thốt Nốt Ô Lâm – Cô Tô: Hàng Cây Biểu Tượng Triệu View Của Miền Tây Nam Bộ  Trải dài men theo con đường làng liên xã nối liền giữa Xã Ô Lâm và Xã Cô Tô, Con Đường Thốt Nốt Ô Lâm – Cô Tô là một trong những biểu tượng phong cảnh đặc trưng và đẹp mắt bậc nhất của vùng đất Tri Tôn An Giang. Hàng trăm thân cây thốt nốt cổ thụ cao vút mọc thẳng tắp hai bên lối đi đất đỏ xẻ dọc qua cánh đồng lúa bạt ngàn, tạo nên bối cảnh sống ảo triệu view đã từng xuất hiện trong vô số bộ ảnh cưới, phóng sự du lịch và video âm nhạc nổi tiếng.  1. Vị Trí &amp; Nét Đặc Biệt Của Tuyến Đường Thốt Nốt • Vị trí hành chính: Tuyến đường liên xã kết nối Xã Ô Lâm và Xã Cô Tô, tỉnh An Giang. • Khoảng cách: Cách trung tâm Thị trấn Tri Tôn khoảng 8 km về phía Tây Nam. • Mật độ thốt nốt dày đặc nhất Bảy Núi: Khác với những cây thốt nốt mọc rải rác đơn lẻ trên đồng, tại cung đường Ô Lâm – Cô Tô, hàng trăm cây thốt nốt hàng chục năm tuổi mọc thẳng hàng tăm tắp hai bên đường, tán lá xòe tròn như những chiếc quạt khổng lồ vươn lên nền trời xanh biếc.  2. Bức Tranh Đồng Quê Đậm Đà Bản Sắc Khmer • Sự hòa quyện giữa cây thốt nốt &amp; ruộng lúa: Dưới gốc những hàng thốt nốt là những thửa ruộng lúa bậc thang thoai thoải của đồng bào người Khmer. Tùy theo mùa vụ, mặt ruộng khoác lên màu xanh non mơn mởn, màu vàng rực rỡ của lúa chín, hoặc màu nước bạc lấp lánh mùa nước nổi. • Khai thác mật hoa thốt nốt truyền thống: Đi dạo trên cung đường này vào buổi sáng sớm hoặc xế chiều, du khách sẽ bắt gặp hình ảnh những người đàn ông Khmer thoăn thoắt leo lên ngọn thốt nốt cao vút bằng những thân tre gai để thu hoạch những ống tre đựng nước mật hoa ngọt lịm. • Những gánh hàng thốt nốt tươi ven đường: Dọc theo tuyến đường có nhiều quầy hàng mộc mạc của bà con địa phương bán nước thốt nốt tươi ướp lạnh, cùi thốt nốt dẻo giòn và đường thốt nốt nguyên chất gói trong lá thốt nốt khô thơm nức.  3. Tọa Độ Sống Ảo Triệu View Cho Giới Trẻ • Khung cảnh điện ảnh: Góc máy chụp dọc theo con đường với hàng thốt nốt chạy dài tít tắp về phía chân núi Cô Tô tạo nên chiều sâu phối cảnh hoàn hảo cho mọi bức ảnh. • Bối cảnh lý tưởng cho trang phục truyền thống: Cung đường rất thích hợp để chụp ảnh cùng tà áo bà ba, nón lá, khăn rằn Nam Bộ, trang phục xăm-pốt truyền thống Khmer hoặc phong cách du mục tự do.  4. Hướng Dẫn Khung Giờ Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm tuyệt vời nhất khi mặt trời đỏ ối dần lặn xuống sau rặng cây thốt nốt, bóng những hàng cây đổ dài trên mặt đất tạo nên những bức ảnh ngược sáng (silhouette) đầy tính nghệ thuật. • Bình minh dịu dàng (06:00 – 07:30 sáng): Khi sương sớm còn vương trên những tán lá và ánh nắng ban mai chiếu rọi nghiêng nghiêng qua kẽ lá. • Mùa lúa chín vàng: Tháng 4, Tháng 8 và Tháng 11–12 hàng năm là lúc cánh đồng hai bên đường rực vàng đẹp nhất.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Giao thông an toàn: Đường liên xã có xe máy và xe máy cày của bà con lưu thông, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào mép cỏ để đảm bảo an toàn. • Thưởng thức đặc sản: Đừng quên dừng chân mua ủng hộ bà con một ly nước thốt nốt tươi mát lạnh (giá chỉ 10.000đ – 15.000đ/ly) để tiếp thêm năng lượng cho hành trình khám phá.</t>
+          <t>Vị trí và Ranh giới Thực địa Hồ Đá Latina nằm dưới chân núi Cấm, thuộc địa phận Xã An Hảo (tiếp giáp ranh giới giữa TX. Tịnh Biên và Tri Tôn). Du khách cần chú ý định vị chính xác vì khu vực này nằm trên trục đường liên ranh giới.  Trải nghiệm &amp; Cảnh quan Điểm nhấn ấn tượng nhất là vách đá hoa cương dựng đứng sừng sững bên hồ nước trong xanh. Đây là góc săn ảnh check-in thiên nhiên độc đáo, mang vẻ đẹp hoang sơ kỳ vĩ.</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr"/>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.38,104.995</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4240344,104.9999364</t>
         </is>
       </c>
     </row>
@@ -16702,12 +16769,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>d8731ae3-cầu-khỉ-giữa-cánh-đồ</t>
+          <t>2ac3fb9a-con-đường-thốt-nốt-ô</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Cầu Khỉ Giữa Cánh Đồng Thốt Nốt</t>
+          <t>Con Đường Thốt Nốt Ô Lâm - Cô Tô</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
@@ -16718,7 +16785,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Điểm check-in mộc mạc</t>
+          <t>Con đường nhiếp ảnh</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
@@ -16726,12 +16793,12 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>10.388, 104.986</t>
+          <t>10.38, 104.995</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang</t>
+          <t>Tuyến đường liên xã Ô Lâm - Núi Tô, Xã Ô Lâm, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
@@ -16747,18 +16814,18 @@
       </c>
       <c r="M28" s="7" t="inlineStr">
         <is>
-          <t>Ngày nay, các loại cầu bằng bêtông trở nên phổ biến cùng với cầu thép. Nhịp cầu ngày càng được kéo dài, từ vài trăm mét như loại cầu …</t>
+          <t>Khám phá Con Đường Thốt Nốt Ô Lâm - Cô Tô, một điểm đến văn hóa độc đáo tại vùng Bảy Núi</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>1. Tổng quan Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm du lịch độc đáo và thú vị, tọa lạc tại Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang. Đây là một địa điểm văn hóa đặc sắc, mang lại trải nghiệm độc đáo cho du khách.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng chúng tôi tin rằng Cầu Khỉ Giữa Cánh Đồng Thốt Nốt sẽ mang lại cho bạn một trải nghiệm đáng nhớ. Với sự độc đáo và thú vị, nơi đây hứa hẹn sẽ khiến bạn không thể rời mắt.  3. Lời khuyên Khi đến Cầu Khỉ Giữa Cánh Đồng Thốt Nốt, bạn nên mang theo camera để chụp những bức ảnh độc đáo và thú vị. Cũng như, đừng quên mang theo nước uống và thực phẩm nhẹ để phục vụ cho chuyến tham quan của mình. Với mức giá Miễn phí, nơi đây là một địa điểm du lịch lý tưởng và đáng trải nghiệm.  Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm độc đáo và thú vị, mang lại cho bạn một trải nghiệm đáng nhớ. Với sự mở cửa tự do, nơi đây là một lựa chọn lý tưởng cho những ai muốn khám phá văn hóa và vẻ đẹp của An Giang. Hãy đến và trải nghiệm Cầu Khỉ Giữa Cánh Đồng Thốt Nốt để khám phá những điều thú vị và độc đáo!</t>
+          <t>Con Đường Thốt Nốt Ô Lâm – Cô Tô: Hàng Cây Biểu Tượng Triệu View Của Miền Tây Nam Bộ  Trải dài men theo con đường làng liên xã nối liền giữa Xã Ô Lâm và Xã Cô Tô, Con Đường Thốt Nốt Ô Lâm – Cô Tô là một trong những biểu tượng phong cảnh đặc trưng và đẹp mắt bậc nhất của vùng đất Tri Tôn An Giang. Hàng trăm thân cây thốt nốt cổ thụ cao vút mọc thẳng tắp hai bên lối đi đất đỏ xẻ dọc qua cánh đồng lúa bạt ngàn, tạo nên bối cảnh sống ảo triệu view đã từng xuất hiện trong vô số bộ ảnh cưới, phóng sự du lịch và video âm nhạc nổi tiếng.  1. Vị Trí &amp; Nét Đặc Biệt Của Tuyến Đường Thốt Nốt • Vị trí hành chính: Tuyến đường liên xã kết nối Xã Ô Lâm và Xã Cô Tô, tỉnh An Giang. • Khoảng cách: Cách trung tâm Thị trấn Tri Tôn khoảng 8 km về phía Tây Nam. • Mật độ thốt nốt dày đặc nhất Bảy Núi: Khác với những cây thốt nốt mọc rải rác đơn lẻ trên đồng, tại cung đường Ô Lâm – Cô Tô, hàng trăm cây thốt nốt hàng chục năm tuổi mọc thẳng hàng tăm tắp hai bên đường, tán lá xòe tròn như những chiếc quạt khổng lồ vươn lên nền trời xanh biếc.  2. Bức Tranh Đồng Quê Đậm Đà Bản Sắc Khmer • Sự hòa quyện giữa cây thốt nốt &amp; ruộng lúa: Dưới gốc những hàng thốt nốt là những thửa ruộng lúa bậc thang thoai thoải của đồng bào người Khmer. Tùy theo mùa vụ, mặt ruộng khoác lên màu xanh non mơn mởn, màu vàng rực rỡ của lúa chín, hoặc màu nước bạc lấp lánh mùa nước nổi. • Khai thác mật hoa thốt nốt truyền thống: Đi dạo trên cung đường này vào buổi sáng sớm hoặc xế chiều, du khách sẽ bắt gặp hình ảnh những người đàn ông Khmer thoăn thoắt leo lên ngọn thốt nốt cao vút bằng những thân tre gai để thu hoạch những ống tre đựng nước mật hoa ngọt lịm. • Những gánh hàng thốt nốt tươi ven đường: Dọc theo tuyến đường có nhiều quầy hàng mộc mạc của bà con địa phương bán nước thốt nốt tươi ướp lạnh, cùi thốt nốt dẻo giòn và đường thốt nốt nguyên chất gói trong lá thốt nốt khô thơm nức.  3. Tọa Độ Sống Ảo Triệu View Cho Giới Trẻ • Khung cảnh điện ảnh: Góc máy chụp dọc theo con đường với hàng thốt nốt chạy dài tít tắp về phía chân núi Cô Tô tạo nên chiều sâu phối cảnh hoàn hảo cho mọi bức ảnh. • Bối cảnh lý tưởng cho trang phục truyền thống: Cung đường rất thích hợp để chụp ảnh cùng tà áo bà ba, nón lá, khăn rằn Nam Bộ, trang phục xăm-pốt truyền thống Khmer hoặc phong cách du mục tự do.  4. Hướng Dẫn Khung Giờ Chụp Ảnh Đẹp Nhất • Săn hoàng hôn lãng mạn (16:30 – 17:45): Đây là thời điểm tuyệt vời nhất khi mặt trời đỏ ối dần lặn xuống sau rặng cây thốt nốt, bóng những hàng cây đổ dài trên mặt đất tạo nên những bức ảnh ngược sáng (silhouette) đầy tính nghệ thuật. • Bình minh dịu dàng (06:00 – 07:30 sáng): Khi sương sớm còn vương trên những tán lá và ánh nắng ban mai chiếu rọi nghiêng nghiêng qua kẽ lá. • Mùa lúa chín vàng: Tháng 4, Tháng 8 và Tháng 11–12 hàng năm là lúc cánh đồng hai bên đường rực vàng đẹp nhất.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Giao thông an toàn: Đường liên xã có xe máy và xe máy cày của bà con lưu thông, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào mép cỏ để đảm bảo an toàn. • Thưởng thức đặc sản: Đừng quên dừng chân mua ủng hộ bà con một ly nước thốt nốt tươi mát lạnh (giá chỉ 10.000đ – 15.000đ/ly) để tiếp thêm năng lượng cho hành trình khám phá.</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr"/>
       <c r="P28" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.388,104.986</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.38,104.995</t>
         </is>
       </c>
     </row>
@@ -16768,12 +16835,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>833d6714-nấc-thang-thiên-đườn</t>
+          <t>d8731ae3-cầu-khỉ-giữa-cánh-đồ</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum</t>
+          <t>Cầu Khỉ Giữa Cánh Đồng Thốt Nốt</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
@@ -16784,20 +16851,20 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Tiểu cảnh check-in</t>
+          <t>Điểm check-in mộc mạc</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>10.3776, 104.9926</t>
+          <t>10.388, 104.986</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Khuôn viên Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
@@ -16813,18 +16880,18 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Tiểu cảnh check-in nấc thang vươn lên trời mây ngắm trọn cảnh mặt hồ Ô Thum thơ mộng tại khuôn viên Quán Kiều Tiên, Xã Ô Lâm.</t>
+          <t>Ngày nay, các loại cầu bằng bêtông trở nên phổ biến cùng với cầu thép. Nhịp cầu ngày càng được kéo dài, từ vài trăm mét như loại cầu …</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum – Tọa Độ 'Sống Ảo' Chạm Mây Bên Lòng Hồ Ô Thum  Nằm nổi bật bên triền hồ Ô Thum thuộc Xã Ô Lâm, Nấc Thang Thiên Đường Kiều Tiên là một trong những tiểu cảnh check-in mang tính biểu tượng thu hút đông đảo bạn trẻ và du khách yêu thích nhiếp ảnh khi ghé thăm Tri Tôn. Nấc thang màu trắng tinh khôi vươn thẳng lên nền trời xanh biếc, hòa cùng mặt nước hồ phẳng lặng và bóng núi Thất Sơn tạo nên khung cảnh lãng mạn như chốn bồng lai tiên cảnh.  1. Vị Trí &amp; Không Gian Khuôn Viên Kiều Tiên • Địa chỉ hành chính: Khuôn viên Quán Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, tỉnh An Giang. • Tầm nhìn khoáng đạt: Nấc thang được xây dựng kiên cố ven bờ hồ, hướng thẳng ra vùng lòng hồ bao la và rặng thốt nốt xanh ngát của Xã Ô Lâm. Đứng từ chân cầu thang nhìn lên, các bậc thang nối đuôi nhau như dẫn lối thẳng lên trời mây.  2. Trải Nghiệm Check-in &amp; Săn Ảnh Độc Bản • Góc chụp 'vô cực' chạm mây: Chụp từ dưới góc thấp lên mút bậc thang cao nhất, tạo cảm giác như người mẫu đang bước đi giữa không trung bồng bềnh mây trời. • Khung giờ vàng hoàng hôn (16:30 – 17:30): Bầu trời Ô Thum chuyển sang sắc cam hồng rực rỡ, ánh nắng hoàng hôn dát vàng lên từng bậc thang tạo nên những bức ảnh ngược sáng (silhouette) tuyệt mỹ. • Kết hợp check-in cầu gỗ Ô Thum: Du khách có thể dễ dàng dạo bước sang cây cầu gỗ mộc mạc bắc ngang bờ hồ ngay kế bên để chụp trọn bộ ảnh thiên nhiên Bảy Núi.  3. Kết Hợp Thưởng Thức Ẩm Thực Bản Địa • Gà đốt lá chúc Kiều Tiên: Ngay tại khuôn viên là quán gà đốt trứ danh lâu đời nhất Hồ Ô Thum. Du khách sau khi chụp ảnh có thể ngồi tại các chòi tre lợp lá mát rượi thưởng thức đĩa gà đốt nóng giòn chấm muối ớt lá chúc cay nồng.  4. Lưu Ý Dành Cho Du Khách • An toàn khi chụp ảnh: Từng người bước lên bậc thang chậm rãi, giữ thăng bằng và không chen lấn xô đẩy trên các bậc cao. • Trang phục gợi ý: Trang phục màu sáng (trắng, vàng, đỏ, váy maxi bay bổng) sẽ nổi bật nhất trên nền trời xanh và mặt hồ ngọc bích. • Giờ mở cửa: 08:00 – 19:00 hàng ngày (Miễn phí check-in chụp ảnh cho thực khách dùng bữa tại quán).</t>
+          <t>1. Tổng quan Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm du lịch độc đáo và thú vị, tọa lạc tại Cánh đồng thốt nốt An Tức, Ấp Ninh Hòa, Xã An Tức, Tri Tôn, An Giang. Đây là một địa điểm văn hóa đặc sắc, mang lại trải nghiệm độc đáo cho du khách.  2. Đánh giá từ du khách Chưa có đánh giá từ du khách, nhưng chúng tôi tin rằng Cầu Khỉ Giữa Cánh Đồng Thốt Nốt sẽ mang lại cho bạn một trải nghiệm đáng nhớ. Với sự độc đáo và thú vị, nơi đây hứa hẹn sẽ khiến bạn không thể rời mắt.  3. Lời khuyên Khi đến Cầu Khỉ Giữa Cánh Đồng Thốt Nốt, bạn nên mang theo camera để chụp những bức ảnh độc đáo và thú vị. Cũng như, đừng quên mang theo nước uống và thực phẩm nhẹ để phục vụ cho chuyến tham quan của mình. Với mức giá Miễn phí, nơi đây là một địa điểm du lịch lý tưởng và đáng trải nghiệm.  Cầu Khỉ Giữa Cánh Đồng Thốt Nốt là một địa điểm độc đáo và thú vị, mang lại cho bạn một trải nghiệm đáng nhớ. Với sự mở cửa tự do, nơi đây là một lựa chọn lý tưởng cho những ai muốn khám phá văn hóa và vẻ đẹp của An Giang. Hãy đến và trải nghiệm Cầu Khỉ Giữa Cánh Đồng Thốt Nốt để khám phá những điều thú vị và độc đáo!</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr"/>
       <c r="P29" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3776,104.9926</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.388,104.986</t>
         </is>
       </c>
     </row>
@@ -16834,12 +16901,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>6669ffb7-suối-vàng-soài-so</t>
+          <t>833d6714-nấc-thang-thiên-đườn</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Suối Vàng Soài So</t>
+          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr"/>
@@ -16850,7 +16917,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Suối sinh thái</t>
+          <t>Tiểu cảnh check-in</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
@@ -16858,12 +16925,12 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>10.4055, 105.0255</t>
+          <t>10.3776, 104.9926</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Khu vực Suối Vàng Soài So, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
+          <t>Khuôn viên Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
@@ -16879,18 +16946,18 @@
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>Dòng suối tự nhiên trong vắt bắt nguồn từ đỉnh Núi Cô Tô len lỏi qua các khe đá rợp bóng cây rừng, chảy về lòng Hồ Soài So, xã Núi Tô. Điểm dã ngoại, tắm mát và cắm trại lý tưởng.</t>
+          <t>Tiểu cảnh check-in nấc thang vươn lên trời mây ngắm trọn cảnh mặt hồ Ô Thum thơ mộng tại khuôn viên Quán Kiều Tiên, Xã Ô Lâm.</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Khám Phá Suối Vàng Soài So &amp; Dòng Suối Bạc – Dải Lụa Nước Khoáng Trong Vắt Dưới Chân Núi Cô Tô  Ẩn mình dưới chân ngọn núi Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ thuộc Xã Núi Tô, Khu du lịch Suối Vàng Soài So là một trong những điểm dã ngoại, tắm suối tự nhiên và cắm trại sinh thái mát lành bậc nhất của vùng Bảy Núi An Giang. Dòng suối đá tự nhiên tuôn trào từ các tầng địa chất granite trên đỉnh núi, len lỏi qua những cánh rừng tầm vông xanh ngắt và đổ dòng nước trong vắt về lòng Hồ Soài So thơ mộng.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Suối Vàng - Suối Bạc" • Vị trí hành chính: Nằm trong khuôn viên Khu du lịch Suối Vàng Soài So, chân Núi Cô Tô, Xã Núi Tô, tỉnh An Giang. • Cách di chuyển: Từ trung tâm Thị trấn Tri Tôn, du khách đi theo đường Trần Hưng Đạo khoảng 2 km về hướng Nam, rẽ vào cổng chào Khu du lịch Suối Vàng Soài So sẽ thấy con đường rợp bóng cây dẫn thẳng vào chân suối. • Sự tích tên gọi: Theo truyền tích của các bậc cao niên Bảy Núi, dòng suối này bắt nguồn từ các mạch nước ngầm tinh khiết trên đỉnh Cô Tô. Nước chảy qua các khe đá có chứa quặng khoáng tự nhiên lấp lánh dưới ánh mặt trời, tạo nên hai nhánh suối kỳ ảo được người xưa tôn kính đặt tên là Suối Vàng và Suối Bạc.  2. Cảnh Quan Thiên Nhiên &amp; Hệ Sinh Thái Núi Rừng • Tầng tầng lớp lớp đá granite: Dòng suối chảy qua những tảng đá hoa cương khổng lồ với đủ hình thù kỳ thú, tạo thành những hồ tắm thiên nhiên nhỏ với mực nước chỉ ngang đầu gối, nước trong vắt đến mức có thể nhìn thấy đàn cá nhỏ bơi lội dưới đáy. • Rừng cây rợp bóng mát rượi: Hai bên bờ suối là những tán rừng tầm vông, vườn xoài cổ thụ và cây dầu rái trăm năm tuổi tỏa bóng mát rượi, giữ cho nhiệt độ nơi đây luôn thấp hơn khu vực đồng bằng từ 3–5 độ C. • Hồ chứa nước Soài So: Dưới chân suối là lòng Hồ Soài So rộng lớn phẳng lặng như gương soi, phản chiếu bóng núi Cô Tô sừng sững giữa bầu trời xanh biếc.  3. Trải Nghiệm Thực Địa Hấp Dẫn Không Thể Bỏ Qua • Tắm suối đá khoáng mát lạnh: Đắm mình trong làn nước suối mát rượi, lắng nghe tiếng nước chảy róc rách và tiếng chim rừng hót líu lo là liệu pháp thư giãn tinh thần tuyệt vời sau chuỗi ngày làm việc căng thẳng. • Tổ chức picnic &amp; Cắm trại ven suối: Các phiến đá phẳng rộng lớn bên bờ suối là vị trí lý tưởng để trải bạt, nướng đồ ăn dã ngoại và quây quần bên gia đình, bạn bè. • Trekking ngược dòng suối lên sườn núi: Với những ai yêu thích khám phá, cung đường men theo vách đá suối dẫn lên các am điện tu tập và vườn cây ăn trái lưng chừng núi Cô Tô mang lại cảm giác chinh phục thiên nhiên hoang sơ.  4. Hướng Dẫn Góc Check-in &amp; Khung Giờ Vàng • Khung giờ chụp ảnh đẹp nhất: 08:00 – 10:30 sáng khi ánh nắng ban mai rọi qua tán lá tạo thành những vạt sáng lung linh trên mặt nước suối; hoặc 15:00 – 17:00 chiều để ngắm hoàng hôn buông xuống mặt Hồ Soài So. • Góc chụp sống ảo: Đứng trên các phiến đá giữa dòng suối lấy hậu cảnh là vách đá rêu phong và rừng tầm vông, hoặc chụp toàn cảnh bờ kè Hồ Soài So hướng về đỉnh Phụng Hoàng Sơn. • Mùa lý tưởng: Mùa mưa từ tháng 6 đến tháng 11 âm lịch là thời điểm suối nhiều nước và trong xanh đẹp nhất trong năm.  5. Lưu Ý An Toàn &amp; Bảo Vệ Cảnh Quan • Cảnh báo trơn trượt: Các phiến đá ven suối có rêu bám trơn trượt, du khách nên đi dép có độ bám tốt hoặc giày thể thao lội nước, cẩn thận khi bước nhảy qua các khe đá. • Vệ sinh môi trường: Tuyệt đối không xả rác, túi nilon hay chai nhựa xuống lòng suối; gom toàn bộ rác thải vào thùng rác sau khi ăn uống dã ngoại. • Giá vé: Vé vào cổng khu du lịch khoảng 10.000đ – 20.000đ/người (giữ xe máy 5.000đ).</t>
+          <t>Nấc Thang Thiên Đường Kiều Tiên Ô Thum – Tọa Độ 'Sống Ảo' Chạm Mây Bên Lòng Hồ Ô Thum  Nằm nổi bật bên triền hồ Ô Thum thuộc Xã Ô Lâm, Nấc Thang Thiên Đường Kiều Tiên là một trong những tiểu cảnh check-in mang tính biểu tượng thu hút đông đảo bạn trẻ và du khách yêu thích nhiếp ảnh khi ghé thăm Tri Tôn. Nấc thang màu trắng tinh khôi vươn thẳng lên nền trời xanh biếc, hòa cùng mặt nước hồ phẳng lặng và bóng núi Thất Sơn tạo nên khung cảnh lãng mạn như chốn bồng lai tiên cảnh.  1. Vị Trí &amp; Không Gian Khuôn Viên Kiều Tiên • Địa chỉ hành chính: Khuôn viên Quán Kiều Tiên Ô Thum, Ấp Phước Thọ, Xã Ô Lâm, tỉnh An Giang. • Tầm nhìn khoáng đạt: Nấc thang được xây dựng kiên cố ven bờ hồ, hướng thẳng ra vùng lòng hồ bao la và rặng thốt nốt xanh ngát của Xã Ô Lâm. Đứng từ chân cầu thang nhìn lên, các bậc thang nối đuôi nhau như dẫn lối thẳng lên trời mây.  2. Trải Nghiệm Check-in &amp; Săn Ảnh Độc Bản • Góc chụp 'vô cực' chạm mây: Chụp từ dưới góc thấp lên mút bậc thang cao nhất, tạo cảm giác như người mẫu đang bước đi giữa không trung bồng bềnh mây trời. • Khung giờ vàng hoàng hôn (16:30 – 17:30): Bầu trời Ô Thum chuyển sang sắc cam hồng rực rỡ, ánh nắng hoàng hôn dát vàng lên từng bậc thang tạo nên những bức ảnh ngược sáng (silhouette) tuyệt mỹ. • Kết hợp check-in cầu gỗ Ô Thum: Du khách có thể dễ dàng dạo bước sang cây cầu gỗ mộc mạc bắc ngang bờ hồ ngay kế bên để chụp trọn bộ ảnh thiên nhiên Bảy Núi.  3. Kết Hợp Thưởng Thức Ẩm Thực Bản Địa • Gà đốt lá chúc Kiều Tiên: Ngay tại khuôn viên là quán gà đốt trứ danh lâu đời nhất Hồ Ô Thum. Du khách sau khi chụp ảnh có thể ngồi tại các chòi tre lợp lá mát rượi thưởng thức đĩa gà đốt nóng giòn chấm muối ớt lá chúc cay nồng.  4. Lưu Ý Dành Cho Du Khách • An toàn khi chụp ảnh: Từng người bước lên bậc thang chậm rãi, giữ thăng bằng và không chen lấn xô đẩy trên các bậc cao. • Trang phục gợi ý: Trang phục màu sáng (trắng, vàng, đỏ, váy maxi bay bổng) sẽ nổi bật nhất trên nền trời xanh và mặt hồ ngọc bích. • Giờ mở cửa: 08:00 – 19:00 hàng ngày (Miễn phí check-in chụp ảnh cho thực khách dùng bữa tại quán).</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr"/>
       <c r="P30" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4055,105.0255</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3776,104.9926</t>
         </is>
       </c>
     </row>
@@ -16900,36 +16967,36 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>nui-sa-lon</t>
+          <t>6669ffb7-suối-vàng-soài-so</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn</t>
+          <t>Suối Vàng Soài So</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Xã Lương Phi</t>
+          <t>Xã Cô Tô</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>Suối sinh thái</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>10.4386816, 104.9624942</t>
+          <t>10.4055, 105.0255</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn, Xã Lương Phi, Tri Tôn, An Giang</t>
+          <t>Khu vực Suối Vàng Soài So, Khóm 1, Thị trấn Tri Tôn, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
@@ -16945,18 +17012,18 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Khám phá Núi Sà Lôn - điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang</t>
+          <t>Dòng suối tự nhiên trong vắt bắt nguồn từ đỉnh Núi Cô Tô len lỏi qua các khe đá rợp bóng cây rừng, chảy về lòng Hồ Soài So, xã Núi Tô. Điểm dã ngoại, tắm mát và cắm trại lý tưởng.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Núi Sà Lôn - Điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang  Núi Sà Lôn là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang. Vùng đất Tri Tôn nằm trong dãy Thất Sơn (Bảy Núi) hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  Khi đến Núi Sà Lôn, du khách có cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Đặc sản nước thốt nốt tươi, bánh bò thốt nốt là những món ăn bạn không thể bỏ qua khi đến đây. Du khách cũng có thể tìm hiểu các phong tục tập quán truyền thống của người dân địa phương.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về trải nghiệm của mình tại Núi Sà Lôn. Họ đã thưởng thức nước thốt nốt tươi ngon và bánh bò thốt nốt giòn tan. Họ cũng đã học hỏi được những phong tục tập quán truyền thống của người dân địa phương.  Khám phá Núi Sà Lôn  Núi Sà Lôn là một điểm đến không thể bỏ qua khi bạn đến thăm Tri Tôn, An Giang. Với cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương, Núi Sà Lôn chắc chắn sẽ mang lại cho bạn những trải nghiệm đáng nhớ.</t>
+          <t>Khám Phá Suối Vàng Soài So &amp; Dòng Suối Bạc – Dải Lụa Nước Khoáng Trong Vắt Dưới Chân Núi Cô Tô  Ẩn mình dưới chân ngọn núi Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ thuộc Xã Núi Tô, Khu du lịch Suối Vàng Soài So là một trong những điểm dã ngoại, tắm suối tự nhiên và cắm trại sinh thái mát lành bậc nhất của vùng Bảy Núi An Giang. Dòng suối đá tự nhiên tuôn trào từ các tầng địa chất granite trên đỉnh núi, len lỏi qua những cánh rừng tầm vông xanh ngắt và đổ dòng nước trong vắt về lòng Hồ Soài So thơ mộng.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Suối Vàng - Suối Bạc" • Vị trí hành chính: Nằm trong khuôn viên Khu du lịch Suối Vàng Soài So, chân Núi Cô Tô, Xã Núi Tô, tỉnh An Giang. • Cách di chuyển: Từ trung tâm Thị trấn Tri Tôn, du khách đi theo đường Trần Hưng Đạo khoảng 2 km về hướng Nam, rẽ vào cổng chào Khu du lịch Suối Vàng Soài So sẽ thấy con đường rợp bóng cây dẫn thẳng vào chân suối. • Sự tích tên gọi: Theo truyền tích của các bậc cao niên Bảy Núi, dòng suối này bắt nguồn từ các mạch nước ngầm tinh khiết trên đỉnh Cô Tô. Nước chảy qua các khe đá có chứa quặng khoáng tự nhiên lấp lánh dưới ánh mặt trời, tạo nên hai nhánh suối kỳ ảo được người xưa tôn kính đặt tên là Suối Vàng và Suối Bạc.  2. Cảnh Quan Thiên Nhiên &amp; Hệ Sinh Thái Núi Rừng • Tầng tầng lớp lớp đá granite: Dòng suối chảy qua những tảng đá hoa cương khổng lồ với đủ hình thù kỳ thú, tạo thành những hồ tắm thiên nhiên nhỏ với mực nước chỉ ngang đầu gối, nước trong vắt đến mức có thể nhìn thấy đàn cá nhỏ bơi lội dưới đáy. • Rừng cây rợp bóng mát rượi: Hai bên bờ suối là những tán rừng tầm vông, vườn xoài cổ thụ và cây dầu rái trăm năm tuổi tỏa bóng mát rượi, giữ cho nhiệt độ nơi đây luôn thấp hơn khu vực đồng bằng từ 3–5 độ C. • Hồ chứa nước Soài So: Dưới chân suối là lòng Hồ Soài So rộng lớn phẳng lặng như gương soi, phản chiếu bóng núi Cô Tô sừng sững giữa bầu trời xanh biếc.  3. Trải Nghiệm Thực Địa Hấp Dẫn Không Thể Bỏ Qua • Tắm suối đá khoáng mát lạnh: Đắm mình trong làn nước suối mát rượi, lắng nghe tiếng nước chảy róc rách và tiếng chim rừng hót líu lo là liệu pháp thư giãn tinh thần tuyệt vời sau chuỗi ngày làm việc căng thẳng. • Tổ chức picnic &amp; Cắm trại ven suối: Các phiến đá phẳng rộng lớn bên bờ suối là vị trí lý tưởng để trải bạt, nướng đồ ăn dã ngoại và quây quần bên gia đình, bạn bè. • Trekking ngược dòng suối lên sườn núi: Với những ai yêu thích khám phá, cung đường men theo vách đá suối dẫn lên các am điện tu tập và vườn cây ăn trái lưng chừng núi Cô Tô mang lại cảm giác chinh phục thiên nhiên hoang sơ.  4. Hướng Dẫn Góc Check-in &amp; Khung Giờ Vàng • Khung giờ chụp ảnh đẹp nhất: 08:00 – 10:30 sáng khi ánh nắng ban mai rọi qua tán lá tạo thành những vạt sáng lung linh trên mặt nước suối; hoặc 15:00 – 17:00 chiều để ngắm hoàng hôn buông xuống mặt Hồ Soài So. • Góc chụp sống ảo: Đứng trên các phiến đá giữa dòng suối lấy hậu cảnh là vách đá rêu phong và rừng tầm vông, hoặc chụp toàn cảnh bờ kè Hồ Soài So hướng về đỉnh Phụng Hoàng Sơn. • Mùa lý tưởng: Mùa mưa từ tháng 6 đến tháng 11 âm lịch là thời điểm suối nhiều nước và trong xanh đẹp nhất trong năm.  5. Lưu Ý An Toàn &amp; Bảo Vệ Cảnh Quan • Cảnh báo trơn trượt: Các phiến đá ven suối có rêu bám trơn trượt, du khách nên đi dép có độ bám tốt hoặc giày thể thao lội nước, cẩn thận khi bước nhảy qua các khe đá. • Vệ sinh môi trường: Tuyệt đối không xả rác, túi nilon hay chai nhựa xuống lòng suối; gom toàn bộ rác thải vào thùng rác sau khi ăn uống dã ngoại. • Giá vé: Vé vào cổng khu du lịch khoảng 10.000đ – 20.000đ/người (giữ xe máy 5.000đ).</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4386816,104.9624942</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4055,105.0255</t>
         </is>
       </c>
     </row>
@@ -16966,23 +17033,23 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>9616e5e5-con-đường-tơ-lụa-tà-</t>
+          <t>nui-sa-lon</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Con Đường Tơ Lụa Tà Pạ</t>
+          <t>Núi Sà Lôn</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Xã Núi Tô</t>
+          <t>Xã Lương Phi</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Con đường tơ lụa</t>
+          <t>peak</t>
         </is>
       </c>
       <c r="G32" s="6" t="n">
@@ -16990,12 +17057,12 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>10.4185, 105.0095</t>
+          <t>10.4386816, 104.9624942</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Tuyến đường lúa Tà Pạ, Ấp Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Núi Sà Lôn, Xã Lương Phi, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr"/>
@@ -17011,18 +17078,18 @@
       </c>
       <c r="M32" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Con Đường Tơ Lụa Tà Pạ - Di tích lịch sử văn hóa độc đáo ở An Giang</t>
+          <t>Khám phá Núi Sà Lôn - điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Con Đường Tơ Lụa Tà Pạ – Dải Lụa Nghìn Màu Uốn Lượn Giữa Cánh Đồng Thất Sơn  Được mệnh danh là một trong những cung đường đồng quê đẹp và lãng mạn nhất miền Tây Nam Bộ, Con Đường Tơ Lụa Tà Pạ là dải đường bê tông nhỏ uốn lượn mềm mại tựa như một dải lụa mềm xẻ dọc qua cánh đồng lúa Tà Pạ và Hồ Soài Chek thuộc Xã Núi Tô. Cung đường này đã trở thành nguồn cảm hứng bất tận cho các nhiếp ảnh gia, giới trẻ mê xê dịch và những ai trót say đắm vẻ đẹp mộc mạc, thanh bình của vùng đất Bảy Núi.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Con Đường Tơ Lụa" • Vị trí hành chính: Nằm tại cánh đồng Tà Pạ, kết nối giữa khu vực Hồ Soài Chek và chân Đồi Tà Pạ, Xã Núi Tô, tỉnh An Giang. • Sự tích tên gọi: Từ trên đỉnh Núi Tô hoặc chùa Tà Pạ nhìn xuống, con đường bê tông trắng uốn lượn nhiều khúc quanh co mềm mại, uốn quanh các bờ ruộng ô vuông bàn cờ như một dải lụa tơ tằm mềm mại vắt ngang qua bức tranh đồng lúa bạt ngàn. Du khách và các nhiếp ảnh gia đã ưu ái gọi tên cung đường này là "Con Đường Tơ Lụa Tri Tôn". • Hạ tầng hoàn thiện: Trước đây là đường đất bờ ruộng nhỏ hẹp, nay đã được chính quyền và bà con địa phương bê tông hóa phẳng phiu, giúp xe máy và xe đạp có thể di chuyển êm ái xuyên suốt cung đường.  2. Bức Họa Thiên Nhiên Rực Rỡ Bốn Mùa • Vũ điệu sắc màu theo mùa lúa:  • Mùa nước đổ &amp; Mạ non (Tháng 3, Tháng 7): Cả cánh đồng ngập tràn sắc xanh mướt mát mắt, mặt nước ruộng lúa phản chiếu mây trời lồng lộng. • Mùa lúa chín vàng (Tháng 4, Tháng 8, Tháng 11–12): Cung đường như chìm đắm giữa biển vàng óng ả, hương thơm ngọt ngào của lúa mới phảng phất khắp không gian. • Hàng cây thốt nốt &amp; Cây trâm cổ thụ: Dọc theo hai bên đ.  ường là những rặng cây thốt nốt vươn cao kiêu hãnh và những gốc trâm cổ thụ trăm năm tuổi tỏa bóng mát râm ran, tạo nên khung cảnh làng quê Khmer bình yên đến nao lòng. • Hậu cảnh núi non kỳ vĩ: Phía xa xa là bóng dáng hùng vĩ của Núi Tô và Núi Cấm che chắn, điểm xuyết những mái chùa Khmer chóp nhọn vàng rực ẩn hiện sau rặng cây.  3. Nhịp Sống Đồng Quê &amp; Nét Đẹp Đời Thường • Hình ảnh người nông dân Khmer trên đồng: Du khách sẽ dễ dàng bắt gặp hình ảnh những người nông dân Khmer đội nón lá cần mẫn gặt lúa, những đàn bò thong dong gặm cỏ trên bờ ruộng và các em nhỏ vui đùa thả diều mỗi buổi chiều tà. • Không gian tĩnh lặng, trong lành: Tách biệt hoàn toàn khỏi khói bụi và tiếng ồn của đô thị, nơi đây chỉ có tiếng gió lướt qua ngọn lúa xào xạc và tiếng chim hót rộn rã đầu cành.  4. Hướng Dẫn Check-in &amp; Khung Giờ Sống Ảo Triệu View • Săn bình minh rạng rỡ (06:00 – 07:30): Khi ánh mặt trời vừa ló rạng sau rặng núi, sương sớm còn đọng long lanh trên từng nhánh lúa, tạo nên một không gian mờ ảo, lung linh như cõi tiên. • Đón hoàng hôn ấm áp (16:30 – 17:45): Ánh nắng chiều tà nhuộm vàng rực rỡ cả cung đường, bóng những hàng cây thốt nốt đổ dài trên mặt ruộng là khoảnh khắc vàng để chụp ảnh ngược sáng (silhouette). • Góc chụp lý tưởng: Chụp từ góc thấp hướng dọc theo đường cong uốn lượn của cung đường; chụp cùng tà áo dài hoặc trang phục truyền thống Khmer; chụp toàn cảnh từ flycam trên cao.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Tôn trọng nông dân: Tuyệt đối không dẫm đạp lên lúa của bà con, không bẻ nhánh hay hái quả thốt nốt non của các hộ dân ven đường. • An toàn giao thông: Đường nhỏ vừa cho 2 xe máy tránh nhau, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào sát lề đường để không cản trở lối đi của bà con nông dân. • Chi phí: Hoàn toàn miễn phí tham quan và chụp ảnh tự do.</t>
+          <t>Núi Sà Lôn - Điểm đến thiên nhiên độc đáo tại Tri Tôn, An Giang  Núi Sà Lôn là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại huyện Tri Tôn, tỉnh An Giang. Vùng đất Tri Tôn nằm trong dãy Thất Sơn (Bảy Núi) hùng vĩ, nổi tiếng với sự kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer.  Khi đến Núi Sà Lôn, du khách có cơ hội khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Đặc sản nước thốt nốt tươi, bánh bò thốt nốt là những món ăn bạn không thể bỏ qua khi đến đây. Du khách cũng có thể tìm hiểu các phong tục tập quán truyền thống của người dân địa phương.  Trải nghiệm thực tế  Một số du khách đã chia sẻ về trải nghiệm của mình tại Núi Sà Lôn. Họ đã thưởng thức nước thốt nốt tươi ngon và bánh bò thốt nốt giòn tan. Họ cũng đã học hỏi được những phong tục tập quán truyền thống của người dân địa phương.  Khám phá Núi Sà Lôn  Núi Sà Lôn là một điểm đến không thể bỏ qua khi bạn đến thăm Tri Tôn, An Giang. Với cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương, Núi Sà Lôn chắc chắn sẽ mang lại cho bạn những trải nghiệm đáng nhớ.</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr"/>
       <c r="P32" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4185,105.0095</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4386816,104.9624942</t>
         </is>
       </c>
     </row>
@@ -17032,12 +17099,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ho-soai-chek</t>
+          <t>9616e5e5-con-đường-tơ-lụa-tà-</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Hồ Soài Chek</t>
+          <t>Con Đường Tơ Lụa Tà Pạ</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
@@ -17048,7 +17115,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>Con đường tơ lụa</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
@@ -17056,12 +17123,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>10.4285, 104.9924</t>
+          <t>10.4185, 105.0095</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Xã Ba Chúc, huyện Tri Tôn, An Giang</t>
+          <t>Tuyến đường lúa Tà Pạ, Ấp Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
@@ -17077,18 +17144,18 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Hồ thủy lợi thơ mộng dưới chân đồi Tà Pạ, xã Núi Tô. Không gian tĩnh lặng, thoáng đãng, là điểm cắm trại ngắm hoàng hôn buông trên đồi cát và rặng thốt nốt.</t>
+          <t>Khám phá Con Đường Tơ Lụa Tà Pạ - Di tích lịch sử văn hóa độc đáo ở An Giang</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Khám Phá Hồ Soài Chék – Điểm Hẹn Thơ Mộng Dưới Chân Dãy Phụng Hoàng Sơn  Nằm khép mình bên sườn phía Bắc ngọn Núi Cô Tô, Hồ Soài Chék (thuộc ấp Tô Hạ, xã Núi Tô, huyện Tri Tôn, An Giang) là một trong những hồ chứa nước ngọt nhân tạo lớn và ấn tượng của vùng Thất Sơn. Với sự hòa quyện giữa mặt nước trong xanh phẳng lặng, núi non trùng điệp và không gian văn hóa Khmer đặc sắc kề bên, nơi đây trở thành tọa độ dã ngoại và check-in ưa thích của du khách.  1. Vị Trí &amp; Cảnh Quan • Đặc SắcTọa độ tự nhiên tuyệt đẹp: Hồ nằm ngay dưới chân dãy Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ. Một bên hồ tựa vào vách núi, một bên mở ra tầm nhìn hướng về cánh đồng lúa bạt ngàn và những rặng thốt nốt vươn cao. • Cung đường ven hồ nên thơ: Con đường nhỏ chạy dọc theo bờ hồ có góc nhìn • đắt giá: một bên là mặt nước mênh mông in bóng mây trời, phía trước là đỉnh núi Cô Tô sừng sững, bên còn lại là thảm lúa xanh mát hoặc vàng ươm theo mùa. • Đồi cát &amp; Bãi cỏ ven hồ: Quanh hồ có các khoảng đồi thoai thoải và bãi cát tự nhiên phẳng phiu, tạo nên không gian mở lộng gió, thích hợp cho việc dựng lều cắm trại, dã ngoại hoặc chụp ảnh theo phong cách hoang sơ, tự nhiên.  2. Điểm Nhấn Văn Hóa &amp; Lễ Hội Kế CậnHồ Soài Chék không chỉ là thắng cảnh thiên nhiên mà còn nằm liền kề cụm công trình văn hóa – thể thao lớn của huyện • Tri Tôn: Sân • đua bò Bảy Núi: Tọa lạc ngay phía trước khu vực hồ với quy mô khoảng 5,5 ha. Đây chính là nơi diễn ra Lễ hội Đua bò Bảy Núi truyền thống vào dịp lễ Sen Dolta (khoảng cuối tháng 8 – đầu tháng 9 Âm lịch), thu hút hàng vạn du khách và đồng bào trong vùng về tham dự.Công viên văn hóa &amp; • Nhà truyền thống Soài Chék: Khuôn viên rộng hơn 6.000 m² được bài trí các tiểu cảnh mang đậm bản sắc Nam Bộ và văn hóa Khmer (tượng đôi bò đua, giếng cổ, cụm cây trâm, thốt nốt...), cùng nhà trưng bày nông cụ truyền thống và không gian diễn xướng nhạc ngũ âm, múa Dì kê.  3. Trải Nghiệm Thú Vị &amp; • Thời Điểm Lý TưởngSăn ảnh hoàng hôn: Vào buổi chiều tà (khoảng 16h30 – 17h45), mặt trời lặn sau rặng núi Cô Tô phản chiếu ánh ráng đỏ rực rỡ lên mặt gương hồ, tạo nên khung cảnh lãng mạn và yên ả. • Thưởng thức cà phê ngắm đồng: Gần hồ có các quán cà phê ngắm cảnh đồng ruộng thoáng mát, là nơi dừng chân nghỉ ngơi lý tưởng sau chuyến dạo quanh bờ hồ. • Thời gian trong năm: Mùa nước nổi &amp; mùa gặt (Tháng 9 – • Tháng 11): Mực nước hồ dâng cao trong xanh, hòa cùng sắc vàng rực của đồng lúa chín bao quanh. • Mùa khô (Tháng 12 – Tháng 4 năm sau): Thời tiết tạnh ráo, nắng ấm, rất thuận tiện cho các hoạt động cắm trại, dã ngoại ngoài trời.  4. Gợi Ý Lịch Trình Kết HợpTừ Hồ Soài Chék, bạn có thể dễ dàng kết nối tham quan theo cung • đường: Hồ Soài Chék \longrightarrow "Con đường tơ lụa" \&amp; Cánh đồng Tà Pạ \longrightarrow Hồ Tà Pạ / Chùa Tà Pạ \longrightarrow Vườn cây trâm cổ thụ5. • Lưu Ý Dành Cho Du Khách • An toàn: Nước hồ sâu và lạnh, không nên tự ý bơi lội hoặc leo trèo ra các mỏm đá chênh vênh ven hồ. • Bảo vệ môi trường: Khu vực hồ còn giữ nét hoang sơ, du khách khi tổ chức picnic hoặc cắm trại cần dọn dẹp sạch sẽ toàn bộ rác thải trước khi rời đi để bảo tồn cảnh quan tự nhiên.</t>
+          <t>Con Đường Tơ Lụa Tà Pạ – Dải Lụa Nghìn Màu Uốn Lượn Giữa Cánh Đồng Thất Sơn  Được mệnh danh là một trong những cung đường đồng quê đẹp và lãng mạn nhất miền Tây Nam Bộ, Con Đường Tơ Lụa Tà Pạ là dải đường bê tông nhỏ uốn lượn mềm mại tựa như một dải lụa mềm xẻ dọc qua cánh đồng lúa Tà Pạ và Hồ Soài Chek thuộc Xã Núi Tô. Cung đường này đã trở thành nguồn cảm hứng bất tận cho các nhiếp ảnh gia, giới trẻ mê xê dịch và những ai trót say đắm vẻ đẹp mộc mạc, thanh bình của vùng đất Bảy Núi.  1. Vị Trí &amp; Nguồn Gốc Tên Gọi "Con Đường Tơ Lụa" • Vị trí hành chính: Nằm tại cánh đồng Tà Pạ, kết nối giữa khu vực Hồ Soài Chek và chân Đồi Tà Pạ, Xã Núi Tô, tỉnh An Giang. • Sự tích tên gọi: Từ trên đỉnh Núi Tô hoặc chùa Tà Pạ nhìn xuống, con đường bê tông trắng uốn lượn nhiều khúc quanh co mềm mại, uốn quanh các bờ ruộng ô vuông bàn cờ như một dải lụa tơ tằm mềm mại vắt ngang qua bức tranh đồng lúa bạt ngàn. Du khách và các nhiếp ảnh gia đã ưu ái gọi tên cung đường này là "Con Đường Tơ Lụa Tri Tôn". • Hạ tầng hoàn thiện: Trước đây là đường đất bờ ruộng nhỏ hẹp, nay đã được chính quyền và bà con địa phương bê tông hóa phẳng phiu, giúp xe máy và xe đạp có thể di chuyển êm ái xuyên suốt cung đường.  2. Bức Họa Thiên Nhiên Rực Rỡ Bốn Mùa • Vũ điệu sắc màu theo mùa lúa:  • Mùa nước đổ &amp; Mạ non (Tháng 3, Tháng 7): Cả cánh đồng ngập tràn sắc xanh mướt mát mắt, mặt nước ruộng lúa phản chiếu mây trời lồng lộng. • Mùa lúa chín vàng (Tháng 4, Tháng 8, Tháng 11–12): Cung đường như chìm đắm giữa biển vàng óng ả, hương thơm ngọt ngào của lúa mới phảng phất khắp không gian. • Hàng cây thốt nốt &amp; Cây trâm cổ thụ: Dọc theo hai bên đ.  ường là những rặng cây thốt nốt vươn cao kiêu hãnh và những gốc trâm cổ thụ trăm năm tuổi tỏa bóng mát râm ran, tạo nên khung cảnh làng quê Khmer bình yên đến nao lòng. • Hậu cảnh núi non kỳ vĩ: Phía xa xa là bóng dáng hùng vĩ của Núi Tô và Núi Cấm che chắn, điểm xuyết những mái chùa Khmer chóp nhọn vàng rực ẩn hiện sau rặng cây.  3. Nhịp Sống Đồng Quê &amp; Nét Đẹp Đời Thường • Hình ảnh người nông dân Khmer trên đồng: Du khách sẽ dễ dàng bắt gặp hình ảnh những người nông dân Khmer đội nón lá cần mẫn gặt lúa, những đàn bò thong dong gặm cỏ trên bờ ruộng và các em nhỏ vui đùa thả diều mỗi buổi chiều tà. • Không gian tĩnh lặng, trong lành: Tách biệt hoàn toàn khỏi khói bụi và tiếng ồn của đô thị, nơi đây chỉ có tiếng gió lướt qua ngọn lúa xào xạc và tiếng chim hót rộn rã đầu cành.  4. Hướng Dẫn Check-in &amp; Khung Giờ Sống Ảo Triệu View • Săn bình minh rạng rỡ (06:00 – 07:30): Khi ánh mặt trời vừa ló rạng sau rặng núi, sương sớm còn đọng long lanh trên từng nhánh lúa, tạo nên một không gian mờ ảo, lung linh như cõi tiên. • Đón hoàng hôn ấm áp (16:30 – 17:45): Ánh nắng chiều tà nhuộm vàng rực rỡ cả cung đường, bóng những hàng cây thốt nốt đổ dài trên mặt ruộng là khoảnh khắc vàng để chụp ảnh ngược sáng (silhouette). • Góc chụp lý tưởng: Chụp từ góc thấp hướng dọc theo đường cong uốn lượn của cung đường; chụp cùng tà áo dài hoặc trang phục truyền thống Khmer; chụp toàn cảnh từ flycam trên cao.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Tôn trọng nông dân: Tuyệt đối không dẫm đạp lên lúa của bà con, không bẻ nhánh hay hái quả thốt nốt non của các hộ dân ven đường. • An toàn giao thông: Đường nhỏ vừa cho 2 xe máy tránh nhau, khi dừng lại chụp ảnh cần dựng xe gọn gàng vào sát lề đường để không cản trở lối đi của bà con nông dân. • Chi phí: Hoàn toàn miễn phí tham quan và chụp ảnh tự do.</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr"/>
       <c r="P33" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.9924</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4185,105.0095</t>
         </is>
       </c>
     </row>
@@ -17098,12 +17165,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>ho-ta-pa</t>
+          <t>ho-soai-chek</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Hồ Tà Pạ (Tuyệt Tình Cốc Bảy Núi)</t>
+          <t>Hồ Soài Chek</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr"/>
@@ -17122,12 +17189,12 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>10.4165, 105.0042</t>
+          <t>10.4285, 104.9924</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Xã Ba Chúc, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr"/>
@@ -17143,18 +17210,18 @@
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>Hồ nước ngọt trong xanh như ngọc bích trên đỉnh đồi Tà Pạ, xã Núi Tô, được mệnh danh là Tuyệt tình cốc Bảy Núi.</t>
+          <t>Hồ thủy lợi thơ mộng dưới chân đồi Tà Pạ, xã Núi Tô. Không gian tĩnh lặng, thoáng đãng, là điểm cắm trại ngắm hoàng hôn buông trên đồi cát và rặng thốt nốt.</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Hồ Đá Đồi Tà Pạ – "Tuyệt Tình Cốc" của An Giang  1. Vị trí và Nguồn gốc: • Địa chỉ: Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang (nằm cạnh cánh đồng lúa Tà Pạ). • Nguồn gốc: Hồ là tuyệt tác hình thành từ quá trình khai thác đá trước đây. Với độ sâu khoảng 17 mét, hồ chứa mạch nước ngầm tự nhiên trong vắt nhìn thấu tận đáy. • Cảnh quan: Lọt thỏm giữa những vách đá granite sừng sững, hồ đổi màu nước huyền ảo theo góc chiếu ánh nắng (từ xanh lam, ngọc bích đến vàng cam).  2. Hướng dẫn di chuyển &amp; Thời điểm đẹp nhất: • Cách đi: Từ chợ Tri Tôn theo đường Nguyễn Trãi lên chân đồi Tà Pạ ➔ Chạy theo đường bê tông dốc thoai thoải 1.2km lên đỉnh đồi. Xe máy và ô tô dưới 16 chỗ lên tận nơi. • Thời điểm check-in: 06:00 – 08:30 sáng đón nắng sớm hoặc 16:00 – 17:30 chiều ngắm hoàng hôn buông xuống thung lũng lúa.</t>
+          <t>Khám Phá Hồ Soài Chék – Điểm Hẹn Thơ Mộng Dưới Chân Dãy Phụng Hoàng Sơn  Nằm khép mình bên sườn phía Bắc ngọn Núi Cô Tô, Hồ Soài Chék (thuộc ấp Tô Hạ, xã Núi Tô, huyện Tri Tôn, An Giang) là một trong những hồ chứa nước ngọt nhân tạo lớn và ấn tượng của vùng Thất Sơn. Với sự hòa quyện giữa mặt nước trong xanh phẳng lặng, núi non trùng điệp và không gian văn hóa Khmer đặc sắc kề bên, nơi đây trở thành tọa độ dã ngoại và check-in ưa thích của du khách.  1. Vị Trí &amp; Cảnh Quan • Đặc SắcTọa độ tự nhiên tuyệt đẹp: Hồ nằm ngay dưới chân dãy Phụng Hoàng Sơn (Núi Cô Tô) hùng vĩ. Một bên hồ tựa vào vách núi, một bên mở ra tầm nhìn hướng về cánh đồng lúa bạt ngàn và những rặng thốt nốt vươn cao. • Cung đường ven hồ nên thơ: Con đường nhỏ chạy dọc theo bờ hồ có góc nhìn • đắt giá: một bên là mặt nước mênh mông in bóng mây trời, phía trước là đỉnh núi Cô Tô sừng sững, bên còn lại là thảm lúa xanh mát hoặc vàng ươm theo mùa. • Đồi cát &amp; Bãi cỏ ven hồ: Quanh hồ có các khoảng đồi thoai thoải và bãi cát tự nhiên phẳng phiu, tạo nên không gian mở lộng gió, thích hợp cho việc dựng lều cắm trại, dã ngoại hoặc chụp ảnh theo phong cách hoang sơ, tự nhiên.  2. Điểm Nhấn Văn Hóa &amp; Lễ Hội Kế CậnHồ Soài Chék không chỉ là thắng cảnh thiên nhiên mà còn nằm liền kề cụm công trình văn hóa – thể thao lớn của huyện • Tri Tôn: Sân • đua bò Bảy Núi: Tọa lạc ngay phía trước khu vực hồ với quy mô khoảng 5,5 ha. Đây chính là nơi diễn ra Lễ hội Đua bò Bảy Núi truyền thống vào dịp lễ Sen Dolta (khoảng cuối tháng 8 – đầu tháng 9 Âm lịch), thu hút hàng vạn du khách và đồng bào trong vùng về tham dự.Công viên văn hóa &amp; • Nhà truyền thống Soài Chék: Khuôn viên rộng hơn 6.000 m² được bài trí các tiểu cảnh mang đậm bản sắc Nam Bộ và văn hóa Khmer (tượng đôi bò đua, giếng cổ, cụm cây trâm, thốt nốt...), cùng nhà trưng bày nông cụ truyền thống và không gian diễn xướng nhạc ngũ âm, múa Dì kê.  3. Trải Nghiệm Thú Vị &amp; • Thời Điểm Lý TưởngSăn ảnh hoàng hôn: Vào buổi chiều tà (khoảng 16h30 – 17h45), mặt trời lặn sau rặng núi Cô Tô phản chiếu ánh ráng đỏ rực rỡ lên mặt gương hồ, tạo nên khung cảnh lãng mạn và yên ả. • Thưởng thức cà phê ngắm đồng: Gần hồ có các quán cà phê ngắm cảnh đồng ruộng thoáng mát, là nơi dừng chân nghỉ ngơi lý tưởng sau chuyến dạo quanh bờ hồ. • Thời gian trong năm: Mùa nước nổi &amp; mùa gặt (Tháng 9 – • Tháng 11): Mực nước hồ dâng cao trong xanh, hòa cùng sắc vàng rực của đồng lúa chín bao quanh. • Mùa khô (Tháng 12 – Tháng 4 năm sau): Thời tiết tạnh ráo, nắng ấm, rất thuận tiện cho các hoạt động cắm trại, dã ngoại ngoài trời.  4. Gợi Ý Lịch Trình Kết HợpTừ Hồ Soài Chék, bạn có thể dễ dàng kết nối tham quan theo cung • đường: Hồ Soài Chék \longrightarrow "Con đường tơ lụa" \&amp; Cánh đồng Tà Pạ \longrightarrow Hồ Tà Pạ / Chùa Tà Pạ \longrightarrow Vườn cây trâm cổ thụ5. • Lưu Ý Dành Cho Du Khách • An toàn: Nước hồ sâu và lạnh, không nên tự ý bơi lội hoặc leo trèo ra các mỏm đá chênh vênh ven hồ. • Bảo vệ môi trường: Khu vực hồ còn giữ nét hoang sơ, du khách khi tổ chức picnic hoặc cắm trại cần dọn dẹp sạch sẽ toàn bộ rác thải trước khi rời đi để bảo tồn cảnh quan tự nhiên.</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4165,105.0042</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4285,104.9924</t>
         </is>
       </c>
     </row>
@@ -17164,12 +17231,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>nui-ta-pa</t>
+          <t>ho-ta-pa</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Núi Tà Pạ</t>
+          <t>Hồ Tà Pạ (Tuyệt Tình Cốc Bảy Núi)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
@@ -17180,7 +17247,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
@@ -17188,12 +17255,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>10.4072869, 104.9747836</t>
+          <t>10.4165, 105.0042</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Núi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr"/>
@@ -17209,18 +17276,18 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Khám phá vẻ đẹp yên bình của Núi Tà Pạ và trải nghiệm nét văn hóa độc đáo tại vùng đất Bảy Núi</t>
+          <t>Hồ nước ngọt trong xanh như ngọc bích trên đỉnh đồi Tà Pạ, xã Núi Tô, được mệnh danh là Tuyệt tình cốc Bảy Núi.</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Núi • Tà Pạ: Trái tim của dãy Thất Sơn  Vùng đất Tri Tôn, nằm trong dãy Thất Sơn hùng vĩ, là nơi kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer. Núi Tà Pạ là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại đây.  Cảnh sắc yên bình và lòng hiếu khách  Khi đến đây, du khách có thể khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Du khách cũng có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Hồ • Tà Pạ: Tuyệt tình cốc của miền Tây  Theo đánh giá của du khách, hồ Tà Pạ tại Tri Tôn, An Giang được mệnh danh là "Tuyệt tình cốc" của miền Tây. Nước hồ rất trong, tạo nên một kiệt tác thiên nhiên đầy mê hoặc. Ngoài ra, cánh đồng Tà Pạ nằm dưới chân núi Tà Pạ và Cô Tô, cách thị trấn Tri Tôn khoảng 1km, cũng là một thắng cảnh tuyệt đẹp đáng tự hào của An Giang. Cánh đồng này là một bức tranh tuyệt đẹp khi có một cánh đồng xanh bát ngáy xen lẫn giữ những lùm cây, đường đi khá uốn lượn nên là đi tốc độ chậm chút.  Tuyệt vời khi có thể khám phá vẻ đẹp yên bình và văn hóa độc đáo của Núi Tà Pạ và vùng đất Bảy Núi!</t>
+          <t>Khám phá Hồ Đá Đồi Tà Pạ – "Tuyệt Tình Cốc" của An Giang  1. Vị trí và Nguồn gốc: • Địa chỉ: Đồi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang (nằm cạnh cánh đồng lúa Tà Pạ). • Nguồn gốc: Hồ là tuyệt tác hình thành từ quá trình khai thác đá trước đây. Với độ sâu khoảng 17 mét, hồ chứa mạch nước ngầm tự nhiên trong vắt nhìn thấu tận đáy. • Cảnh quan: Lọt thỏm giữa những vách đá granite sừng sững, hồ đổi màu nước huyền ảo theo góc chiếu ánh nắng (từ xanh lam, ngọc bích đến vàng cam).  2. Hướng dẫn di chuyển &amp; Thời điểm đẹp nhất: • Cách đi: Từ chợ Tri Tôn theo đường Nguyễn Trãi lên chân đồi Tà Pạ ➔ Chạy theo đường bê tông dốc thoai thoải 1.2km lên đỉnh đồi. Xe máy và ô tô dưới 16 chỗ lên tận nơi. • Thời điểm check-in: 06:00 – 08:30 sáng đón nắng sớm hoặc 16:00 – 17:30 chiều ngắm hoàng hôn buông xuống thung lũng lúa.</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr"/>
       <c r="P35" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4072869,104.9747836</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4165,105.0042</t>
         </is>
       </c>
     </row>
@@ -17230,12 +17297,12 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>san-dua-bo-ta-pa-soai-chek</t>
+          <t>nui-ta-pa</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Sân Đua Bò Thể Thao Tà Pạ - Soài Chek (Nơi Thi Đấu Chính Thức)</t>
+          <t>Núi Tà Pạ</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr"/>
@@ -17244,18 +17311,22 @@
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F36" s="7" t="n"/>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
       <c r="G36" s="6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>10.4215, 105.0085</t>
+          <t>10.4072869, 104.9747836</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Khu Thể Thao Tà Pạ - Soài Chek, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Núi Tà Pạ, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr"/>
@@ -17271,18 +17342,18 @@
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>Sân đua bò trung tâm quy mô lớn thuộc Khu Thể thao - Du lịch Tà Pạ - Soài Chek (Xã Núi Tô), nơi diễn ra Hội Đua Bò Bảy Núi tranh Cúp Truyền hình An Giang chính thức hàng năm với hàng vạn khán giả.</t>
+          <t>Khám phá vẻ đẹp yên bình của Núi Tà Pạ và trải nghiệm nét văn hóa độc đáo tại vùng đất Bảy Núi</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Để đáp ứng quy mô lễ hội ngày càng lớn mạnh (Di sản văn hóa phi vật thể Quốc gia), huyện Tri Tôn và tỉnh An Giang đã đầu tư sân đua bò chuyên dụng tại chân đồi Tà Pạ - Hồ Soài Chek với khán đài, bờ bao an toàn và đường đua bùn lầy đạt chuẩn 120m (gồm 1 vòng hô và 1 vòng thả về đích kịch tính).</t>
+          <t>Núi • Tà Pạ: Trái tim của dãy Thất Sơn  Vùng đất Tri Tôn, nằm trong dãy Thất Sơn hùng vĩ, là nơi kết hợp hài hòa giữa nét đẹp hoang sơ của đồng bằng phù sa, những dải núi đá granite trùng điệp và bản sắc văn hóa phong phú của đồng bào Khmer. Núi Tà Pạ là một trong những điểm thuộc hệ thống danh thắng, công trình văn hóa và cảnh quan thiên nhiên độc đáo tại đây.  Cảnh sắc yên bình và lòng hiếu khách  Khi đến đây, du khách có thể khám phá cảnh sắc yên bình, không khí trong lành và lòng hiếu khách của người dân địa phương. Du khách cũng có thể thưởng thức đặc sản nước thốt nốt tươi, bánh bò thốt nốt và tìm hiểu các phong tục tập quán truyền thống của người Khmer.  Hồ • Tà Pạ: Tuyệt tình cốc của miền Tây  Theo đánh giá của du khách, hồ Tà Pạ tại Tri Tôn, An Giang được mệnh danh là "Tuyệt tình cốc" của miền Tây. Nước hồ rất trong, tạo nên một kiệt tác thiên nhiên đầy mê hoặc. Ngoài ra, cánh đồng Tà Pạ nằm dưới chân núi Tà Pạ và Cô Tô, cách thị trấn Tri Tôn khoảng 1km, cũng là một thắng cảnh tuyệt đẹp đáng tự hào của An Giang. Cánh đồng này là một bức tranh tuyệt đẹp khi có một cánh đồng xanh bát ngáy xen lẫn giữ những lùm cây, đường đi khá uốn lượn nên là đi tốc độ chậm chút.  Tuyệt vời khi có thể khám phá vẻ đẹp yên bình và văn hóa độc đáo của Núi Tà Pạ và vùng đất Bảy Núi!</t>
         </is>
       </c>
       <c r="O36" s="7" t="inlineStr"/>
       <c r="P36" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4215,105.0085</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4072869,104.9747836</t>
         </is>
       </c>
     </row>
@@ -17292,12 +17363,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>30ac578e-vườn-mãng-cầu-núi-tô</t>
+          <t>san-dua-bo-ta-pa-soai-chek</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Vườn Mãng Cầu Ta Núi Tô</t>
+          <t>Sân Đua Bò Thể Thao Tà Pạ - Soài Chek (Nơi Thi Đấu Chính Thức)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
@@ -17306,22 +17377,18 @@
           <t>Xã Núi Tô</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Nông trại</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="n"/>
       <c r="G37" s="3" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>10.408, 105.021</t>
+          <t>10.4215, 105.0085</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Vườn mãng cầu sườn Núi Tô, Ấp Tô Thuận, Xã Núi Tô, Tri Tôn, An Giang</t>
+          <t>Khu Thể Thao Tà Pạ - Soài Chek, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr"/>
@@ -17337,18 +17404,18 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Nhà vườn sinh thái chuyên trồng giống mãng cầu ta (na Bảy Núi) thơm ngọt, trái to vỏ mỏng trên sườn đá bazan chân đồi Tà Pạ, xã Núi Tô.</t>
+          <t>Sân đua bò trung tâm quy mô lớn thuộc Khu Thể thao - Du lịch Tà Pạ - Soài Chek (Xã Núi Tô), nơi diễn ra Hội Đua Bò Bảy Núi tranh Cúp Truyền hình An Giang chính thức hàng năm với hàng vạn khán giả.</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Vườn Mãng Cầu Triền Đá Núi Tô – Trải Nghiệm Miệt Vườn Cây Ăn Trái Độc Đáo Bám Rễ Đá Granit  Trải dài trên các triền dốc đá thoai thoải của Núi Tô (Phụng Hoàng Sơn) thuộc Xã Núi Tô, Vườn Mãng Cầu Triền Đá là một điểm đến trải nghiệm nông nghiệp sinh thái đặc sắc mang đậm dấu ấn thích nghi kỳ diệu của người dân Bảy Núi. Từng gốc mãng cầu bám rễ sâu vào các kẽ đá hoa cương, chắt chiu dòng khoáng chất tinh khiết của đất núi để cho ra đời những trái mãng cầu dai ngọt lịm, vỏ mỏng, thịt chắc thơm nồng nàn không nơi nào sánh bằng.  1. Vị Trí &amp; Nghề Trồng Cây Ăn Trái Trên Đá • Vị trí hành chính: Triền dốc Núi Tô, Xã Núi Tô, tỉnh An Giang. • Thổ nhưỡng đá granite đặc thù: Núi Tô có cấu tạo địa chất chủ yếu là đá hoa cương xám. Người dân địa phương qua nhiều thế hệ đã cần mẫn đục đá, be đất trên sườn dốc để trồng mãng cầu ta (mãng cầu dai) và các loại cây ăn trái như xoài bưởi, bơ núi. • Hương vị đặc hữu: Nhờ sinh trưởng trên nền đất đá thoát nước tốt và hấp thụ khoáng chất tự nhiên từ đá granit, quả mãng cầu Núi Tô có mắt nở to đều, vỏ mỏng, cùi dày ít hạt, vị ngọt đậm đà và có mùi thơm thoang thoảng của hương rừng Bảy Núi.  2. Trải Nghiệm Khám Phá Miệt Vườn Triền Dốc • Dạo bước dưới tán vườn xanh mát: Du khách sẽ được leo men theo các lối mòn lát đá uốn lượn qua từng tầng vườn mãng cầu xanh mướt, tận mắt chiêm ngưỡng những quả mãng cầu trĩu nặng lúc lỉu bám sát vào thân cây. • Tự tay thu hoạch trái chín tại vườn: Được chủ vườn hướng dẫn cách chọn những quả mãng cầu đã "mở mắt" chín tới, tự tay cắt cuống quả và thưởng thức vị ngọt thơm mát lành ngay dưới bóng cây. • Trò chuyện cùng nông dân bản địa: Nghe bà con người Kinh và Khmer chia sẻ về kỹ thuật thụ phấn hoa mãng cầu thủ công bằng tay từ tờ mờ sáng và cách giữ gìn nguồn nước tưới trên vách núi đá khô cằn.  3. Mùa Vụ Thu Hoạch &amp; Mua Làm Quà • Mùa thu hoạch rộ: Mãng cầu Núi Tô cho trái ngon nhất từ tháng 6 đến tháng 9 hàng năm (mùa mưa) và một vụ rải rác phục vụ dịp Tết Nguyên Đán. • Thức quà quý Bảy Núi: Mãng cầu ta Núi Tô được đóng thùng cẩn thận là món quà biếu ý nghĩa, mang đậm phong vị thiên nhiên trù phú của vùng đất An Giang cho người thân và bạn bè.  4. Hướng Dẫn Khung Giờ &amp; Check-in • Khung giờ lý tưởng: 07:30 – 10:00 sáng hoặc 15:00 – 17:00 chiều để tránh nắng gắt khi leo triền dốc. • Góc chụp sống ảo: Đứng giữa các tầng cây mãng cầu trĩu quả với hậu cảnh là những tảng đá granite khổng lồ và toàn cảnh cánh đồng Tà Pạ thấp thoáng bên dưới.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Trang phục: Đường vườn dốc đá thoai thoải, du khách nên đi giày thể thao có độ ma sát cao để tránh trơn trượt. • Mua trái cây tại vườn: Giá mãng cầu mua trực tiếp tại vườn dao động từ 35.000đ – 60.000đ/kg tùy loại và thời điểm mùa vụ.</t>
+          <t>Để đáp ứng quy mô lễ hội ngày càng lớn mạnh (Di sản văn hóa phi vật thể Quốc gia), huyện Tri Tôn và tỉnh An Giang đã đầu tư sân đua bò chuyên dụng tại chân đồi Tà Pạ - Hồ Soài Chek với khán đài, bờ bao an toàn và đường đua bùn lầy đạt chuẩn 120m (gồm 1 vòng hô và 1 vòng thả về đích kịch tính).</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr"/>
       <c r="P37" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.408,105.021</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.4215,105.0085</t>
         </is>
       </c>
     </row>
@@ -17358,36 +17425,36 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>dinh-than-cau-dai</t>
+          <t>30ac578e-vườn-mãng-cầu-núi-tô</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Đình Thần Cầu Dài (Xã Vĩnh Gia)</t>
+          <t>Vườn Mãng Cầu Ta Núi Tô</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Xã Vĩnh Gia</t>
+          <t>Xã Núi Tô</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>worship</t>
+          <t>Nông trại</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>10.495, 104.92</t>
+          <t>10.408, 105.021</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Tỉnh lộ ĐT955A (gần Cầu Dài), Xã Vĩnh Gia, Tri Tôn, An Giang</t>
+          <t>Vườn mãng cầu sườn Núi Tô, Ấp Tô Thuận, Xã Núi Tô, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr"/>
@@ -17403,18 +17470,18 @@
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>Khám phá Đình thần Cầu Dài - điểm hẹn văn hóa tâm linh giữa lòng Bảy Núi hùng vĩ.</t>
+          <t>Nhà vườn sinh thái chuyên trồng giống mãng cầu ta (na Bảy Núi) thơm ngọt, trái to vỏ mỏng trên sườn đá bazan chân đồi Tà Pạ, xã Núi Tô.</t>
         </is>
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>Đình Thần Cầu Dài – Nét đẹp văn hóa tâm linh vùng biên giới  1. Nét văn hóa truyền thống: • Đình thần Cầu Dài là nơi thờ cúng các bậc tiền hiền có công khai hoang lập ấp vùng đất biên thùy Tây Nam. • Hằng năm vào dịp lễ hội Kỳ Yên 15/2 âm lịch, bà con tổ chức cúng tế trang nghiêm thu hút đông đảo phật tử và du khách thập phương.</t>
+          <t>Vườn Mãng Cầu Triền Đá Núi Tô – Trải Nghiệm Miệt Vườn Cây Ăn Trái Độc Đáo Bám Rễ Đá Granit  Trải dài trên các triền dốc đá thoai thoải của Núi Tô (Phụng Hoàng Sơn) thuộc Xã Núi Tô, Vườn Mãng Cầu Triền Đá là một điểm đến trải nghiệm nông nghiệp sinh thái đặc sắc mang đậm dấu ấn thích nghi kỳ diệu của người dân Bảy Núi. Từng gốc mãng cầu bám rễ sâu vào các kẽ đá hoa cương, chắt chiu dòng khoáng chất tinh khiết của đất núi để cho ra đời những trái mãng cầu dai ngọt lịm, vỏ mỏng, thịt chắc thơm nồng nàn không nơi nào sánh bằng.  1. Vị Trí &amp; Nghề Trồng Cây Ăn Trái Trên Đá • Vị trí hành chính: Triền dốc Núi Tô, Xã Núi Tô, tỉnh An Giang. • Thổ nhưỡng đá granite đặc thù: Núi Tô có cấu tạo địa chất chủ yếu là đá hoa cương xám. Người dân địa phương qua nhiều thế hệ đã cần mẫn đục đá, be đất trên sườn dốc để trồng mãng cầu ta (mãng cầu dai) và các loại cây ăn trái như xoài bưởi, bơ núi. • Hương vị đặc hữu: Nhờ sinh trưởng trên nền đất đá thoát nước tốt và hấp thụ khoáng chất tự nhiên từ đá granit, quả mãng cầu Núi Tô có mắt nở to đều, vỏ mỏng, cùi dày ít hạt, vị ngọt đậm đà và có mùi thơm thoang thoảng của hương rừng Bảy Núi.  2. Trải Nghiệm Khám Phá Miệt Vườn Triền Dốc • Dạo bước dưới tán vườn xanh mát: Du khách sẽ được leo men theo các lối mòn lát đá uốn lượn qua từng tầng vườn mãng cầu xanh mướt, tận mắt chiêm ngưỡng những quả mãng cầu trĩu nặng lúc lỉu bám sát vào thân cây. • Tự tay thu hoạch trái chín tại vườn: Được chủ vườn hướng dẫn cách chọn những quả mãng cầu đã "mở mắt" chín tới, tự tay cắt cuống quả và thưởng thức vị ngọt thơm mát lành ngay dưới bóng cây. • Trò chuyện cùng nông dân bản địa: Nghe bà con người Kinh và Khmer chia sẻ về kỹ thuật thụ phấn hoa mãng cầu thủ công bằng tay từ tờ mờ sáng và cách giữ gìn nguồn nước tưới trên vách núi đá khô cằn.  3. Mùa Vụ Thu Hoạch &amp; Mua Làm Quà • Mùa thu hoạch rộ: Mãng cầu Núi Tô cho trái ngon nhất từ tháng 6 đến tháng 9 hàng năm (mùa mưa) và một vụ rải rác phục vụ dịp Tết Nguyên Đán. • Thức quà quý Bảy Núi: Mãng cầu ta Núi Tô được đóng thùng cẩn thận là món quà biếu ý nghĩa, mang đậm phong vị thiên nhiên trù phú của vùng đất An Giang cho người thân và bạn bè.  4. Hướng Dẫn Khung Giờ &amp; Check-in • Khung giờ lý tưởng: 07:30 – 10:00 sáng hoặc 15:00 – 17:00 chiều để tránh nắng gắt khi leo triền dốc. • Góc chụp sống ảo: Đứng giữa các tầng cây mãng cầu trĩu quả với hậu cảnh là những tảng đá granite khổng lồ và toàn cảnh cánh đồng Tà Pạ thấp thoáng bên dưới.  5. Lưu Ý Thực Địa Dành Cho Du Khách • Trang phục: Đường vườn dốc đá thoai thoải, du khách nên đi giày thể thao có độ ma sát cao để tránh trơn trượt. • Mua trái cây tại vườn: Giá mãng cầu mua trực tiếp tại vườn dao động từ 35.000đ – 60.000đ/kg tùy loại và thời điểm mùa vụ.</t>
         </is>
       </c>
       <c r="O38" s="7" t="inlineStr"/>
       <c r="P38" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.495,104.92</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.408,105.021</t>
         </is>
       </c>
     </row>
@@ -17424,23 +17491,23 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ho-o-thum</t>
+          <t>dinh-than-cau-dai</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Hồ Ô Thum</t>
+          <t>Đình Thần Cầu Dài (Xã Vĩnh Gia)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm</t>
+          <t>Xã Vĩnh Gia</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Hồ nước nhân tạo</t>
+          <t>worship</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
@@ -17448,12 +17515,12 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>10.3765, 104.9875</t>
+          <t>10.495, 104.92</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm, huyện Tri Tôn, An Giang</t>
+          <t>Tỉnh lộ ĐT955A (gần Cầu Dài), Xã Vĩnh Gia, Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
@@ -17469,18 +17536,18 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Hồ Ô Thum là hồ nước ngọt nhân tạo dưới chân đồi Bảy Núi, thủ phủ ẩm thực Gà Đốt trứ danh tại Xã Ô Lâm, Tri Tôn.</t>
+          <t>Khám phá Đình thần Cầu Dài - điểm hẹn văn hóa tâm linh giữa lòng Bảy Núi hùng vĩ.</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Quán Gà Đốt Ai Đó Ô Thum – Mỏm Đất Nhô Giữa Lòng Hồ Với View Nước 360 Độ Tuyệt Mỹ  Tọa lạc trên một mỏm đất tự nhiên nhô hẳn ra giữa lòng hồ Ô Thum tựa như một ốc đảo xanh thu nhỏ, Quán Gà Đốt Ốc Đảo mang lại trải nghiệm ẩm thực độc nhất vô nhị với tầm nhìn 360 độ ngắm trọn mặt nước xanh biếc và dãy đồi núi Ô Lâm trập trùng bao quanh.  1. Vị Trí "Ốc Đảo" Độc Nhất Vô Nhị • Vị trí hành chính: Bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Địa thế ốc đảo xanh: Quán được bao bọc ba mặt bởi làn nước hồ trong vắt, gió thổi lồng lộng quanh năm mang lại không khí mát lạnh tự nhiên không cần quạt máy.  2. Món Gà Đốt Nồi Đất Vàng Giòn • Kỹ thuật đốt gà đỉnh cao: Gà được đốt trong nồi gang đất dày trên than hồng, da gà xém vàng giòn rụm thơm nức mũi mùi lá chúc, thịt bên trong mềm ngọt mọng nước. • Phục vụ đa dạng: Ngoài gà đốt còn có các món cá lóc nướng trui, lẩu cá lăng nấu măng chua, xôi bắp thốt nốt.  3. Trải Nghiệm Ngắm Hoàng Hôn 360 Độ • Khung giờ vàng: 16:30 – 17:45 là khoảnh khắc đẹp nhất khi ánh hoàng hôn nhuộm đỏ cả mặt hồ bao quanh quán.  4. Thông Tin Đặt Chỗ • Giờ mở cửa: 08:00 – 19:00 hàng ngày. • Giá bán: 250.000đ – 320.000đ / con.</t>
+          <t>Đình Thần Cầu Dài – Nét đẹp văn hóa tâm linh vùng biên giới  1. Nét văn hóa truyền thống: • Đình thần Cầu Dài là nơi thờ cúng các bậc tiền hiền có công khai hoang lập ấp vùng đất biên thùy Tây Nam. • Hằng năm vào dịp lễ hội Kỳ Yên 15/2 âm lịch, bà con tổ chức cúng tế trang nghiêm thu hút đông đảo phật tử và du khách thập phương.</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr"/>
       <c r="P39" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3765,104.9875</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.495,104.92</t>
         </is>
       </c>
     </row>
@@ -17490,12 +17557,12 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>lang-gom-dat-nung-o-lam</t>
+          <t>ho-o-thum</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Làng Nghề Gốm Đất Nung &amp; Bếp Cà Ràng Cổ Truyền Ô Lâm</t>
+          <t>Hồ Ô Thum</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr"/>
@@ -17504,18 +17571,22 @@
           <t>Xã Ô Lâm</t>
         </is>
       </c>
-      <c r="F40" s="7" t="n"/>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Hồ nước nhân tạo</t>
+        </is>
+      </c>
       <c r="G40" s="6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>10.375, 104.992</t>
+          <t>10.3765, 104.9875</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Xã Ô Lâm, Tri Tôn, An Giang</t>
+          <t>Xã Ô Lâm, huyện Tri Tôn, An Giang</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr"/>
@@ -17531,23 +17602,85 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>Làng gốm thủ công mộc mạc của người Khmer chuyên chế tác bếp cà-ràng, nồi đất đun củi và niêu đất nướng gà đốt trứ danh bên sườn núi Cô Tô.</t>
+          <t>Hồ Ô Thum là hồ nước ngọt nhân tạo dưới chân đồi Bảy Núi, thủ phủ ẩm thực Gà Đốt trứ danh tại Xã Ô Lâm, Tri Tôn.</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Sử dụng đất sét mịn đặc trưng lấy từ lòng đất Bảy Núi, các nghệ nhân Khmer nhào nặn hoàn toàn bằng tay không dùng bàn xoay, sau đó nung lộ thiên bằng rơm rạ. Chiếc bếp cà-ràng hình số 3 nổi tiếng là vật dụng gắn liền với đời sống sông nước và ẩm thực Bảy Núi hàng trăm năm qua.</t>
+          <t>Quán Gà Đốt Ai Đó Ô Thum – Mỏm Đất Nhô Giữa Lòng Hồ Với View Nước 360 Độ Tuyệt Mỹ  Tọa lạc trên một mỏm đất tự nhiên nhô hẳn ra giữa lòng hồ Ô Thum tựa như một ốc đảo xanh thu nhỏ, Quán Gà Đốt Ốc Đảo mang lại trải nghiệm ẩm thực độc nhất vô nhị với tầm nhìn 360 độ ngắm trọn mặt nước xanh biếc và dãy đồi núi Ô Lâm trập trùng bao quanh.  1. Vị Trí "Ốc Đảo" Độc Nhất Vô Nhị • Vị trí hành chính: Bờ Hồ Ô Thum, Xã Ô Lâm, tỉnh An Giang. • Địa thế ốc đảo xanh: Quán được bao bọc ba mặt bởi làn nước hồ trong vắt, gió thổi lồng lộng quanh năm mang lại không khí mát lạnh tự nhiên không cần quạt máy.  2. Món Gà Đốt Nồi Đất Vàng Giòn • Kỹ thuật đốt gà đỉnh cao: Gà được đốt trong nồi gang đất dày trên than hồng, da gà xém vàng giòn rụm thơm nức mũi mùi lá chúc, thịt bên trong mềm ngọt mọng nước. • Phục vụ đa dạng: Ngoài gà đốt còn có các món cá lóc nướng trui, lẩu cá lăng nấu măng chua, xôi bắp thốt nốt.  3. Trải Nghiệm Ngắm Hoàng Hôn 360 Độ • Khung giờ vàng: 16:30 – 17:45 là khoảnh khắc đẹp nhất khi ánh hoàng hôn nhuộm đỏ cả mặt hồ bao quanh quán.  4. Thông Tin Đặt Chỗ • Giờ mở cửa: 08:00 – 19:00 hàng ngày. • Giá bán: 250.000đ – 320.000đ / con.</t>
         </is>
       </c>
       <c r="O40" s="7" t="inlineStr"/>
       <c r="P40" s="8" t="inlineStr">
         <is>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=10.3765,104.9875</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>lang-gom-dat-nung-o-lam</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Làng Nghề Gốm Đất Nung &amp; Bếp Cà Ràng Cổ Truyền Ô Lâm</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Xã Ô Lâm</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>10.375, 104.992</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Xã Ô Lâm, Tri Tôn, An Giang</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Miễn phí</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>07:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>Làng gốm thủ công mộc mạc của người Khmer chuyên chế tác bếp cà-ràng, nồi đất đun củi và niêu đất nướng gà đốt trứ danh bên sườn núi Cô Tô.</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>Sử dụng đất sét mịn đặc trưng lấy từ lòng đất Bảy Núi, các nghệ nhân Khmer nhào nặn hoàn toàn bằng tay không dùng bàn xoay, sau đó nung lộ thiên bằng rơm rạ. Chiếc bếp cà-ràng hình số 3 nổi tiếng là vật dụng gắn liền với đời sống sông nước và ẩm thực Bảy Núi hàng trăm năm qua.</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr">
+        <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=10.375,104.992</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P40"/>
+  <autoFilter ref="A2:P41"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -17590,6 +17723,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P41" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19871,10 +20005,10 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>26</v>
@@ -19892,7 +20026,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
